--- a/docs/project/requirements/Project Odyssey - MVP Backlog - Copy.xlsx
+++ b/docs/project/requirements/Project Odyssey - MVP Backlog - Copy.xlsx
@@ -654,11 +654,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Working tracker for developers. The source of truth is Project Odyssey.docx v2.0, chapter 12; this workbook is generated from the same data. Updated 2026-10-01: M7-M9 added (D-34); statuses of built stories set to Done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Working tracker for developers. The source of truth is Project Odyssey.docx v2.4, chapter 12; this workbook is generated from the same data. Updated 2026-10-01: M8d split into M8d and M8e (D-43); D-06 decided.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="15.75" customHeight="1" s="20">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -701,7 +700,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15.75" customHeight="1" s="20">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -796,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -820,7 +818,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15.75" customHeight="1" s="20">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -835,7 +832,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="15.75" customHeight="1" s="20">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -1072,17 +1068,17 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Two pillars playable at region scale: Trade (barter and debts) and Religion (sacred fire and followers). The other four are shown as locked 'later Ages'.</t>
+          <t>Four pillars playable at region scale: Trade, Religion, Politics (D-40) and Technology (tech tree, research, workshops, espionage, the Ember Strand; D-41). Military and Ideology are shown as locked 'later Ages'.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>PIL-02, PIL-04, ENV-10</t>
+          <t>PIL-02, PIL-03, PIL-04, PIL-05, PIL-08, PIL-09, ENV-10</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1095,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Win: your clan leads the region (Dominion 60% in Trade or Religion, or 50% combined). Lose: your hero dies before the Mantle moment, or your clan disbands.</t>
+          <t>Win: Dominion 60% in Trade, Religion or Politics; or the Ember Strand held with a 60% Technology share; or the four pillars averaging 50% (values in Game Rules). Lose: your hero dies before the Mantle moment, or your clan disbands.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1153,7 +1149,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Layered 32 x 48 sprites with 3 outfits per body; programmer or placeholder art allowed; minimal sound effects.</t>
+          <t>Layered 32 x 48 sprites with 3 outfits per body; programmer or placeholder art allowed; minimal sound effects. From M8b: 960x540 on the SDL_GPU renderer with global lighting and shadows (D-42).</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1248,185 +1244,239 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="20"/>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="23" ht="38.25" customHeight="1" s="20">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>MVP-15</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Authoring</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>The Editor is the authoring tool for quests, story events, entities, mechanics, game rules, routines and the region with its clans and people; every result is a readable file (D-40, 2026-10-01).</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>EDT-01..EDT-06, STO-04, STO-05, SDC-07, ADR-020</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="38.25" customHeight="1" s="20">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>MVP-16</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Buildings and light</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>960x540 on the GPU renderer; day, night, seasons and weather lighting; fire light; shadows from the sun, the moon and nearby fires; buildings from blueprints and pieces, built by the hero and the clans, with wear, repair, fire, interiors and Editor prefabs (D-42).</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>ENV-18..ENV-21, ARC-11, INT-07, INT-08, EDT-07, ADR-021</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1" s="20"/>
+    <row r="26" ht="63.75" customHeight="1" s="20">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Success and kill criteria (decided before building)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="51" customHeight="1" s="20">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="27" ht="38.25" customHeight="1" s="20">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>How measured</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="63.75" customHeight="1" s="20">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Voluntary play time</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>5 of 8 playtesters play 30+ minutes without being asked to continue</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Observation + local session log (US-092)</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38.25" customHeight="1" s="20">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Emergent story</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>3 of 8 can retell a story that came from the simulation, not from a script</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Post-play interview</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>M6</t>
         </is>
       </c>
     </row>
     <row r="28" ht="63.75" customHeight="1" s="20">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Chronicle interest (early)</t>
+          <t>Voluntary play time</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2 of 3 readers find a story in the console chronicle</t>
+          <t>5 of 8 playtesters play 30+ minutes without being asked to continue</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Show printed chronicle (M2: 3 readers, failed 2026-09-30; M2b retry: the owner reads and judges)</t>
+          <t>Observation + local session log (US-092)</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>M2, retried at M2b</t>
+          <t>M6</t>
         </is>
       </c>
     </row>
     <row r="29" ht="51" customHeight="1" s="20">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Frame rate</t>
+          <t>Emergent story</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>60 FPS with 500 simulated agents in the region on the minimum PC (OPEN-19)</t>
+          <t>3 of 8 can retell a story that came from the simulation, not from a script</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>FPS overlay (US-082)</t>
+          <t>Post-play interview</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
     </row>
     <row r="30" ht="51" customHeight="1" s="20">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Chronicle interest (early)</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Same seed + inputs give the same world hash after 10,000 ticks</t>
+          <t>2 of 3 readers find a story in the console chronicle</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Automated test in CI</t>
+          <t>Show printed chronicle (M2: 3 readers, failed 2026-09-30; M2b retry: the owner reads and judges)</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>M2 onwards</t>
+          <t>M2, retried at M2b</t>
         </is>
       </c>
     </row>
     <row r="31" ht="63.75" customHeight="1" s="20">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Frame rate</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>No crash in a 2-hour play session or a 100-year soak test</t>
+          <t>60 FPS with 500 simulated agents in the region on the minimum PC (OPEN-19)</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Soak test + crash log</t>
+          <t>FPS overlay (US-082)</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>M5, M6</t>
+          <t>M5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>Determinism</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Same seed + inputs give the same world hash after 10,000 ticks</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Automated test in CI</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>M2 onwards</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>No crash in a 2-hour play session or a 100-year soak test</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Soak test + crash log</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>M5, M6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
           <t>Kill / pivot rule</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>If M2 or M6 fails: stop adding content; redesign the simulation or the loop first</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Owner decision, recorded</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>M2, M6</t>
         </is>
@@ -1454,7 +1504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EY26"/>
+  <dimension ref="A1:JO36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="20" min="1" max="1"/>
@@ -1529,6 +1579,126 @@
     <col width="13" customWidth="1" style="20" min="153" max="153"/>
     <col width="13" customWidth="1" style="20" min="154" max="154"/>
     <col width="13" customWidth="1" style="20" min="155" max="155"/>
+    <col width="13" customWidth="1" style="20" min="156" max="156"/>
+    <col width="13" customWidth="1" style="20" min="157" max="157"/>
+    <col width="13" customWidth="1" style="20" min="158" max="158"/>
+    <col width="13" customWidth="1" style="20" min="159" max="159"/>
+    <col width="13" customWidth="1" style="20" min="160" max="160"/>
+    <col width="13" customWidth="1" style="20" min="161" max="161"/>
+    <col width="13" customWidth="1" style="20" min="162" max="162"/>
+    <col width="13" customWidth="1" style="20" min="163" max="163"/>
+    <col width="13" customWidth="1" style="20" min="164" max="164"/>
+    <col width="13" customWidth="1" style="20" min="165" max="165"/>
+    <col width="13" customWidth="1" style="20" min="166" max="166"/>
+    <col width="13" customWidth="1" style="20" min="167" max="167"/>
+    <col width="13" customWidth="1" style="20" min="168" max="168"/>
+    <col width="13" customWidth="1" style="20" min="169" max="169"/>
+    <col width="13" customWidth="1" style="20" min="170" max="170"/>
+    <col width="13" customWidth="1" style="20" min="171" max="171"/>
+    <col width="13" customWidth="1" style="20" min="172" max="172"/>
+    <col width="13" customWidth="1" style="20" min="173" max="173"/>
+    <col width="13" customWidth="1" style="20" min="174" max="174"/>
+    <col width="13" customWidth="1" style="20" min="175" max="175"/>
+    <col width="13" customWidth="1" style="20" min="176" max="176"/>
+    <col width="13" customWidth="1" style="20" min="177" max="177"/>
+    <col width="13" customWidth="1" style="20" min="178" max="178"/>
+    <col width="13" customWidth="1" style="20" min="179" max="179"/>
+    <col width="13" customWidth="1" style="20" min="180" max="180"/>
+    <col width="13" customWidth="1" style="20" min="181" max="181"/>
+    <col width="13" customWidth="1" style="20" min="182" max="182"/>
+    <col width="13" customWidth="1" style="20" min="183" max="183"/>
+    <col width="13" customWidth="1" style="20" min="184" max="184"/>
+    <col width="13" customWidth="1" style="20" min="185" max="185"/>
+    <col width="13" customWidth="1" style="20" min="186" max="186"/>
+    <col width="13" customWidth="1" style="20" min="187" max="187"/>
+    <col width="13" customWidth="1" style="20" min="188" max="188"/>
+    <col width="13" customWidth="1" style="20" min="189" max="189"/>
+    <col width="13" customWidth="1" style="20" min="190" max="190"/>
+    <col width="13" customWidth="1" style="20" min="191" max="191"/>
+    <col width="13" customWidth="1" style="20" min="192" max="192"/>
+    <col width="13" customWidth="1" style="20" min="193" max="193"/>
+    <col width="13" customWidth="1" style="20" min="194" max="194"/>
+    <col width="13" customWidth="1" style="20" min="195" max="195"/>
+    <col width="13" customWidth="1" style="20" min="196" max="196"/>
+    <col width="13" customWidth="1" style="20" min="197" max="197"/>
+    <col width="13" customWidth="1" style="20" min="198" max="198"/>
+    <col width="13" customWidth="1" style="20" min="199" max="199"/>
+    <col width="13" customWidth="1" style="20" min="200" max="200"/>
+    <col width="13" customWidth="1" style="20" min="201" max="201"/>
+    <col width="13" customWidth="1" style="20" min="202" max="202"/>
+    <col width="13" customWidth="1" style="20" min="203" max="203"/>
+    <col width="13" customWidth="1" style="20" min="204" max="204"/>
+    <col width="13" customWidth="1" style="20" min="205" max="205"/>
+    <col width="13" customWidth="1" style="20" min="206" max="206"/>
+    <col width="13" customWidth="1" style="20" min="207" max="207"/>
+    <col width="13" customWidth="1" style="20" min="208" max="208"/>
+    <col width="13" customWidth="1" style="20" min="209" max="209"/>
+    <col width="13" customWidth="1" style="20" min="210" max="210"/>
+    <col width="13" customWidth="1" style="20" min="211" max="211"/>
+    <col width="13" customWidth="1" style="20" min="212" max="212"/>
+    <col width="13" customWidth="1" style="20" min="213" max="213"/>
+    <col width="13" customWidth="1" style="20" min="214" max="214"/>
+    <col width="13" customWidth="1" style="20" min="215" max="215"/>
+    <col width="13" customWidth="1" style="20" min="216" max="216"/>
+    <col width="13" customWidth="1" style="20" min="217" max="217"/>
+    <col width="13" customWidth="1" style="20" min="218" max="218"/>
+    <col width="13" customWidth="1" style="20" min="219" max="219"/>
+    <col width="13" customWidth="1" style="20" min="220" max="220"/>
+    <col width="13" customWidth="1" style="20" min="221" max="221"/>
+    <col width="13" customWidth="1" style="20" min="222" max="222"/>
+    <col width="13" customWidth="1" style="20" min="223" max="223"/>
+    <col width="13" customWidth="1" style="20" min="224" max="224"/>
+    <col width="13" customWidth="1" style="20" min="225" max="225"/>
+    <col width="13" customWidth="1" style="20" min="226" max="226"/>
+    <col width="13" customWidth="1" style="20" min="227" max="227"/>
+    <col width="13" customWidth="1" style="20" min="228" max="228"/>
+    <col width="13" customWidth="1" style="20" min="229" max="229"/>
+    <col width="13" customWidth="1" style="20" min="230" max="230"/>
+    <col width="13" customWidth="1" style="20" min="231" max="231"/>
+    <col width="13" customWidth="1" style="20" min="232" max="232"/>
+    <col width="13" customWidth="1" style="20" min="233" max="233"/>
+    <col width="13" customWidth="1" style="20" min="234" max="234"/>
+    <col width="13" customWidth="1" style="20" min="235" max="235"/>
+    <col width="13" customWidth="1" style="20" min="236" max="236"/>
+    <col width="13" customWidth="1" style="20" min="237" max="237"/>
+    <col width="13" customWidth="1" style="20" min="238" max="238"/>
+    <col width="13" customWidth="1" style="20" min="239" max="239"/>
+    <col width="13" customWidth="1" style="20" min="240" max="240"/>
+    <col width="13" customWidth="1" style="20" min="241" max="241"/>
+    <col width="13" customWidth="1" style="20" min="242" max="242"/>
+    <col width="13" customWidth="1" style="20" min="243" max="243"/>
+    <col width="13" customWidth="1" style="20" min="244" max="244"/>
+    <col width="13" customWidth="1" style="20" min="245" max="245"/>
+    <col width="13" customWidth="1" style="20" min="246" max="246"/>
+    <col width="13" customWidth="1" style="20" min="247" max="247"/>
+    <col width="13" customWidth="1" style="20" min="248" max="248"/>
+    <col width="13" customWidth="1" style="20" min="249" max="249"/>
+    <col width="13" customWidth="1" style="20" min="250" max="250"/>
+    <col width="13" customWidth="1" style="20" min="251" max="251"/>
+    <col width="13" customWidth="1" style="20" min="252" max="252"/>
+    <col width="13" customWidth="1" style="20" min="253" max="253"/>
+    <col width="13" customWidth="1" style="20" min="254" max="254"/>
+    <col width="13" customWidth="1" style="20" min="255" max="255"/>
+    <col width="13" customWidth="1" style="20" min="256" max="256"/>
+    <col width="13" customWidth="1" style="20" min="257" max="257"/>
+    <col width="13" customWidth="1" style="20" min="258" max="258"/>
+    <col width="13" customWidth="1" style="20" min="259" max="259"/>
+    <col width="13" customWidth="1" style="20" min="260" max="260"/>
+    <col width="13" customWidth="1" style="20" min="261" max="261"/>
+    <col width="13" customWidth="1" style="20" min="262" max="262"/>
+    <col width="13" customWidth="1" style="20" min="263" max="263"/>
+    <col width="13" customWidth="1" style="20" min="264" max="264"/>
+    <col width="13" customWidth="1" style="20" min="265" max="265"/>
+    <col width="13" customWidth="1" style="20" min="266" max="266"/>
+    <col width="13" customWidth="1" style="20" min="267" max="267"/>
+    <col width="13" customWidth="1" style="20" min="268" max="268"/>
+    <col width="13" customWidth="1" style="20" min="269" max="269"/>
+    <col width="13" customWidth="1" style="20" min="270" max="270"/>
+    <col width="13" customWidth="1" style="20" min="271" max="271"/>
+    <col width="13" customWidth="1" style="20" min="272" max="272"/>
+    <col width="13" customWidth="1" style="20" min="273" max="273"/>
+    <col width="13" customWidth="1" style="20" min="274" max="274"/>
+    <col width="13" customWidth="1" style="20" min="275" max="275"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="20">
@@ -1545,7 +1715,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1556,7 +1725,6 @@
         <v>46300</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="38.25" customHeight="1" s="20">
       <c r="A6" s="6" t="inlineStr">
         <is>
@@ -2048,6 +2216,366 @@
       <c r="EY6" s="12" t="n">
         <v>140</v>
       </c>
+      <c r="EZ6" s="12" t="n">
+        <v>141</v>
+      </c>
+      <c r="FA6" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="FB6" s="12" t="n">
+        <v>143</v>
+      </c>
+      <c r="FC6" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="FD6" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="FE6" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="FF6" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="FG6" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="FH6" s="12" t="n">
+        <v>149</v>
+      </c>
+      <c r="FI6" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="FJ6" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="FK6" s="12" t="n">
+        <v>152</v>
+      </c>
+      <c r="FL6" s="12" t="n">
+        <v>153</v>
+      </c>
+      <c r="FM6" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="FN6" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="FO6" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="FP6" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="FQ6" s="12" t="n">
+        <v>158</v>
+      </c>
+      <c r="FR6" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="FS6" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="FT6" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="FU6" s="12" t="n">
+        <v>162</v>
+      </c>
+      <c r="FV6" s="12" t="n">
+        <v>163</v>
+      </c>
+      <c r="FW6" s="12" t="n">
+        <v>164</v>
+      </c>
+      <c r="FX6" s="12" t="n">
+        <v>165</v>
+      </c>
+      <c r="FY6" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="FZ6" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="GA6" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="GB6" s="12" t="n">
+        <v>169</v>
+      </c>
+      <c r="GC6" s="12" t="n">
+        <v>170</v>
+      </c>
+      <c r="GD6" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="GE6" s="12" t="n">
+        <v>172</v>
+      </c>
+      <c r="GF6" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="GG6" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="GH6" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="GI6" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="GJ6" s="12" t="n">
+        <v>177</v>
+      </c>
+      <c r="GK6" s="12" t="n">
+        <v>178</v>
+      </c>
+      <c r="GL6" s="12" t="n">
+        <v>179</v>
+      </c>
+      <c r="GM6" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="GN6" s="12" t="n">
+        <v>181</v>
+      </c>
+      <c r="GO6" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="GP6" s="12" t="n">
+        <v>183</v>
+      </c>
+      <c r="GQ6" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="GR6" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="GS6" s="12" t="n">
+        <v>186</v>
+      </c>
+      <c r="GT6" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="GU6" s="12" t="n">
+        <v>188</v>
+      </c>
+      <c r="GV6" s="12" t="n">
+        <v>189</v>
+      </c>
+      <c r="GW6" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="GX6" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="GY6" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="GZ6" s="12" t="n">
+        <v>193</v>
+      </c>
+      <c r="HA6" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="HB6" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="HC6" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="HD6" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="HE6" s="12" t="n">
+        <v>198</v>
+      </c>
+      <c r="HF6" s="12" t="n">
+        <v>199</v>
+      </c>
+      <c r="HG6" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="HH6" s="12" t="n">
+        <v>201</v>
+      </c>
+      <c r="HI6" s="12" t="n">
+        <v>202</v>
+      </c>
+      <c r="HJ6" s="12" t="n">
+        <v>203</v>
+      </c>
+      <c r="HK6" s="12" t="n">
+        <v>204</v>
+      </c>
+      <c r="HL6" s="12" t="n">
+        <v>205</v>
+      </c>
+      <c r="HM6" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="HN6" s="12" t="n">
+        <v>207</v>
+      </c>
+      <c r="HO6" s="12" t="n">
+        <v>208</v>
+      </c>
+      <c r="HP6" s="12" t="n">
+        <v>209</v>
+      </c>
+      <c r="HQ6" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="HR6" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="HS6" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="HT6" s="12" t="n">
+        <v>213</v>
+      </c>
+      <c r="HU6" s="12" t="n">
+        <v>214</v>
+      </c>
+      <c r="HV6" s="12" t="n">
+        <v>215</v>
+      </c>
+      <c r="HW6" s="12" t="n">
+        <v>216</v>
+      </c>
+      <c r="HX6" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="HY6" s="12" t="n">
+        <v>218</v>
+      </c>
+      <c r="HZ6" s="12" t="n">
+        <v>219</v>
+      </c>
+      <c r="IA6" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="IB6" s="12" t="n">
+        <v>221</v>
+      </c>
+      <c r="IC6" s="12" t="n">
+        <v>222</v>
+      </c>
+      <c r="ID6" s="12" t="n">
+        <v>223</v>
+      </c>
+      <c r="IE6" s="12" t="n">
+        <v>224</v>
+      </c>
+      <c r="IF6" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="IG6" s="12" t="n">
+        <v>226</v>
+      </c>
+      <c r="IH6" s="12" t="n">
+        <v>227</v>
+      </c>
+      <c r="II6" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="IJ6" s="12" t="n">
+        <v>229</v>
+      </c>
+      <c r="IK6" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="IL6" s="12" t="n">
+        <v>231</v>
+      </c>
+      <c r="IM6" s="12" t="n">
+        <v>232</v>
+      </c>
+      <c r="IN6" s="12" t="n">
+        <v>233</v>
+      </c>
+      <c r="IO6" s="12" t="n">
+        <v>234</v>
+      </c>
+      <c r="IP6" s="12" t="n">
+        <v>235</v>
+      </c>
+      <c r="IQ6" s="12" t="n">
+        <v>236</v>
+      </c>
+      <c r="IR6" s="12" t="n">
+        <v>237</v>
+      </c>
+      <c r="IS6" s="12" t="n">
+        <v>238</v>
+      </c>
+      <c r="IT6" s="12" t="n">
+        <v>239</v>
+      </c>
+      <c r="IU6" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="IV6" s="12" t="n">
+        <v>241</v>
+      </c>
+      <c r="IW6" s="12" t="n">
+        <v>242</v>
+      </c>
+      <c r="IX6" s="12" t="n">
+        <v>243</v>
+      </c>
+      <c r="IY6" s="12" t="n">
+        <v>244</v>
+      </c>
+      <c r="IZ6" s="12" t="n">
+        <v>245</v>
+      </c>
+      <c r="JA6" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="JB6" s="12" t="n">
+        <v>247</v>
+      </c>
+      <c r="JC6" s="12" t="n">
+        <v>248</v>
+      </c>
+      <c r="JD6" s="12" t="n">
+        <v>249</v>
+      </c>
+      <c r="JE6" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="JF6" s="12" t="n">
+        <v>251</v>
+      </c>
+      <c r="JG6" s="12" t="n">
+        <v>252</v>
+      </c>
+      <c r="JH6" s="12" t="n">
+        <v>253</v>
+      </c>
+      <c r="JI6" s="12" t="n">
+        <v>254</v>
+      </c>
+      <c r="JJ6" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="JK6" s="12" t="n">
+        <v>256</v>
+      </c>
+      <c r="JL6" s="12" t="n">
+        <v>257</v>
+      </c>
+      <c r="JM6" s="12" t="n">
+        <v>258</v>
+      </c>
+      <c r="JN6" s="12" t="n">
+        <v>259</v>
+      </c>
+      <c r="JO6" s="12" t="n">
+        <v>260</v>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1" s="20">
       <c r="A7" s="7" t="inlineStr">
@@ -2771,12 +3299,12 @@
     <row r="19" ht="25.5" customHeight="1" s="20">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>M8b</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Interaction and dialogue editor</t>
+          <t>Resolution and GPU renderer</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -2785,10 +3313,10 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F19" s="9">
         <f>ROUND((D19+E19)/2,0)</f>
@@ -2824,19 +3352,19 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>The owner opens any dialogue or interaction in the Editor as a graph, edits it, test-plays it and saves it, and the file still reads well in a text editor.</t>
+          <t>The game renders at 960x540 through Luna's SDL_GPU renderer (with the old renderer as fallback) and looks the same at 2x camera zoom; windowed sizes, borderless and exclusive full screen work; every screen and editor panel is laid out for the new size; the frame budget holds.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25.5" customHeight="1" s="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M8c</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Playtest and go/no-go (KILL GATE 2)</t>
+          <t>Lighting and shadows</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -2845,10 +3373,10 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F20" s="9">
         <f>ROUND((D20+E20)/2,0)</f>
@@ -2884,116 +3412,657 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>8 outside playtesters play; success criteria measured; go/no-go decision recorded. Held after M9 (owner, 2026-10-01, D-34).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" s="20">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="inlineStr">
+          <t>The world is lit by the sun and moon through the day and the seasons, by fires, torches and effects at night, and dimmed by weather; sprites are shaded with generated normal maps; characters, plants and buildings cast shadows from the sun, the moon and nearby fires; the Editor previews any time of day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25.5" customHeight="1" s="20">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>M8d</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F21" s="9">
+        <f>ROUND((D21+E21)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="9">
+        <f>H20+1</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>G21+F21-1</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>$B$4+(G21-1)*7</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>$B$4+H21*7-1</f>
+        <v/>
+      </c>
+      <c r="K21" s="14">
+        <f>$B$4+SUM($D$7:D21)*7-1</f>
+        <v/>
+      </c>
+      <c r="L21" s="14">
+        <f>$B$4+SUM($E$7:E21)*7-1</f>
+        <v/>
+      </c>
+      <c r="M21" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A21,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A21,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>The hero builds from blueprints and piece by piece on a building grid, and rooms form; the owner composes prefabs from pieces in the Editor and places them in levels; prefabs marked buildable are offered as blueprints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25.5" customHeight="1" s="20">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>M8e</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Building life</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" s="9">
+        <f>ROUND((D22+E22)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="9">
+        <f>H21+1</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>G22+F22-1</f>
+        <v/>
+      </c>
+      <c r="I22" s="14">
+        <f>$B$4+(G22-1)*7</f>
+        <v/>
+      </c>
+      <c r="J22" s="14">
+        <f>$B$4+H22*7-1</f>
+        <v/>
+      </c>
+      <c r="K22" s="14">
+        <f>$B$4+SUM($D$7:D22)*7-1</f>
+        <v/>
+      </c>
+      <c r="L22" s="14">
+        <f>$B$4+SUM($E$7:E22)*7-1</f>
+        <v/>
+      </c>
+      <c r="M22" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A22,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A22,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>Clan members help build and rival clans build; each building fades its roof or opens an interior map as set in the Editor; buildings wear, are repaired, take damage, burn and fall; they shelter, warm and store for the clan and are saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25.5" customHeight="1" s="20">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Interaction and dialogue editor</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" s="9">
+        <f>ROUND((D23+E23)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="9">
+        <f>H22+1</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>G23+F23-1</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>$B$4+(G23-1)*7</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>$B$4+H23*7-1</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>$B$4+SUM($D$7:D23)*7-1</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>$B$4+SUM($E$7:E23)*7-1</f>
+        <v/>
+      </c>
+      <c r="M23" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A23,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A23,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>The owner opens any dialogue or interaction in the Editor as a graph, edits it, test-plays it and saves it, and the file still reads well in a text editor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25.5" customHeight="1" s="20">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Quests and story authoring</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F24" s="9">
+        <f>ROUND((D24+E24)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="9">
+        <f>H23+1</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>G24+F24-1</f>
+        <v/>
+      </c>
+      <c r="I24" s="14">
+        <f>$B$4+(G24-1)*7</f>
+        <v/>
+      </c>
+      <c r="J24" s="14">
+        <f>$B$4+H24*7-1</f>
+        <v/>
+      </c>
+      <c r="K24" s="14">
+        <f>$B$4+SUM($D$7:D24)*7-1</f>
+        <v/>
+      </c>
+      <c r="L24" s="14">
+        <f>$B$4+SUM($E$7:E24)*7-1</f>
+        <v/>
+      </c>
+      <c r="M24" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A24,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A24,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>The owner writes a quest in the Editor's graph (or offline in JSON), test-plays it with the debugger and saves it; a player gets it from an NPC, follows it in the journal, tracker and markers, and finishes it; the elder tutorial is a quest and crossroads events are edited as story events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25.5" customHeight="1" s="20">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Data editors</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F25" s="9">
+        <f>ROUND((D25+E25)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="9">
+        <f>H24+1</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>G25+F25-1</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>$B$4+(G25-1)*7</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>$B$4+H25*7-1</f>
+        <v/>
+      </c>
+      <c r="K25" s="14">
+        <f>$B$4+SUM($D$7:D25)*7-1</f>
+        <v/>
+      </c>
+      <c r="L25" s="14">
+        <f>$B$4+SUM($E$7:E25)*7-1</f>
+        <v/>
+      </c>
+      <c r="M25" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A25,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A25,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t>Every data file has a schema; the owner edits any entity, mechanic, story tuning value, game rule and daily routine in Editor forms with pickers and validation, and the running game reloads it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25.5" customHeight="1" s="20">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>World editing</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="9">
+        <f>ROUND((D26+E26)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="9">
+        <f>H25+1</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>G26+F26-1</f>
+        <v/>
+      </c>
+      <c r="I26" s="14">
+        <f>$B$4+(G26-1)*7</f>
+        <v/>
+      </c>
+      <c r="J26" s="14">
+        <f>$B$4+H26*7-1</f>
+        <v/>
+      </c>
+      <c r="K26" s="14">
+        <f>$B$4+SUM($D$7:D26)*7-1</f>
+        <v/>
+      </c>
+      <c r="L26" s="14">
+        <f>$B$4+SUM($E$7:E26)*7-1</f>
+        <v/>
+      </c>
+      <c r="M26" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A26,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A26,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>The owner opens the procedural region in the Editor, tunes the generator with a live preview, paints terrain, water and mountains, places things, people and camps, and edits each clan's and person's relations, economy, routines and actions; edits are saved on top of the seed and a new game plays them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25.5" customHeight="1" s="20">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F27" s="9">
+        <f>ROUND((D27+E27)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9">
+        <f>H26+1</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>G27+F27-1</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>$B$4+(G27-1)*7</f>
+        <v/>
+      </c>
+      <c r="J27" s="14">
+        <f>$B$4+H27*7-1</f>
+        <v/>
+      </c>
+      <c r="K27" s="14">
+        <f>$B$4+SUM($D$7:D27)*7-1</f>
+        <v/>
+      </c>
+      <c r="L27" s="14">
+        <f>$B$4+SUM($E$7:E27)*7-1</f>
+        <v/>
+      </c>
+      <c r="M27" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A27,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A27,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N27" s="9" t="inlineStr">
+        <is>
+          <t>Clans form alliances and vassal oaths, hold elders' councils, bind themselves by marriage, challenge leaders and use trade and craft knowledge as levers; the player can win the region through Politics; every political rule is editable in the Editor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25.5" customHeight="1" s="20">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" s="9">
+        <f>ROUND((D28+E28)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9">
+        <f>H27+1</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>G28+F28-1</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>$B$4+(G28-1)*7</f>
+        <v/>
+      </c>
+      <c r="J28" s="14">
+        <f>$B$4+H28*7-1</f>
+        <v/>
+      </c>
+      <c r="K28" s="14">
+        <f>$B$4+SUM($D$7:D28)*7-1</f>
+        <v/>
+      </c>
+      <c r="L28" s="14">
+        <f>$B$4+SUM($E$7:E28)*7-1</f>
+        <v/>
+      </c>
+      <c r="M28" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A28,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A28,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t>Clans research by doing in workshops with inventors, pass knowledge by teaching, steal and guard secrets, and unlock recipes, interactions and professions from an editable tech tree; the player can win by forging the Ember Strand while leading in known technologies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25.5" customHeight="1" s="20">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Playtest and go/no-go (KILL GATE 2)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="9">
+        <f>ROUND((D29+E29)/2,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9">
+        <f>H28+1</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>G29+F29-1</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>$B$4+(G29-1)*7</f>
+        <v/>
+      </c>
+      <c r="J29" s="14">
+        <f>$B$4+H29*7-1</f>
+        <v/>
+      </c>
+      <c r="K29" s="14">
+        <f>$B$4+SUM($D$7:D29)*7-1</f>
+        <v/>
+      </c>
+      <c r="L29" s="14">
+        <f>$B$4+SUM($E$7:E29)*7-1</f>
+        <v/>
+      </c>
+      <c r="M29" s="9">
+        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A29,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A29,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="N29" s="9" t="inlineStr">
+        <is>
+          <t>8 outside playtesters play; success criteria measured; go/no-go decision recorded. Held after M14 (owner, 2026-10-01, D-41).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" s="20">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>MVP total</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7">
-        <f>SUM(D7:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="7">
-        <f>SUM(E7:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="7">
-        <f>SUM(F7:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7">
-        <f>H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="15">
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7">
+        <f>SUM(D7:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="7">
+        <f>SUM(E7:E29)</f>
+        <v/>
+      </c>
+      <c r="F30" s="7">
+        <f>SUM(F7:F29)</f>
+        <v/>
+      </c>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7">
+        <f>H29</f>
+        <v/>
+      </c>
+      <c r="I30" s="15">
         <f>I7</f>
         <v/>
       </c>
-      <c r="J21" s="15">
-        <f>J20</f>
-        <v/>
-      </c>
-      <c r="K21" s="15">
-        <f>K20</f>
-        <v/>
-      </c>
-      <c r="L21" s="15">
-        <f>L20</f>
-        <v/>
-      </c>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="J30" s="15">
+        <f>J29</f>
+        <v/>
+      </c>
+      <c r="K30" s="15">
+        <f>K29</f>
+        <v/>
+      </c>
+      <c r="L30" s="15">
+        <f>L29</f>
+        <v/>
+      </c>
+      <c r="M30" s="7" t="n"/>
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Months (likely) = weeks / 4.33</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="27.95" customHeight="1" s="20">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="inlineStr">
+    <row r="31" ht="27.95" customHeight="1" s="20">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>In months</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7">
-        <f>ROUND(D21/4.33,1)</f>
-        <v/>
-      </c>
-      <c r="E22" s="7">
-        <f>ROUND(E21/4.33,1)</f>
-        <v/>
-      </c>
-      <c r="F22" s="7">
-        <f>ROUND(F21/4.33,1)</f>
-        <v/>
-      </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="27.95" customHeight="1" s="20"/>
-    <row r="24" ht="27.95" customHeight="1" s="20">
-      <c r="B24" s="19" t="inlineStr">
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7">
+        <f>ROUND(D30/4.33,1)</f>
+        <v/>
+      </c>
+      <c r="E31" s="7">
+        <f>ROUND(E30/4.33,1)</f>
+        <v/>
+      </c>
+      <c r="F31" s="7">
+        <f>ROUND(F30/4.33,1)</f>
+        <v/>
+      </c>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
+    </row>
+    <row r="32" ht="27.95" customHeight="1" s="20"/>
+    <row r="33" ht="27.95" customHeight="1" s="20">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>Why the estimate grew: the learning path (requirements, section 8.3) estimated 9-13 months top-down. The bottom-up sum of the MVP stories is higher; this sheet uses the bottom-up figure.</t>
         </is>
       </c>
     </row>
-    <row r="25" s="20">
-      <c r="B25" s="19" t="inlineStr">
+    <row r="34" s="20">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>Buffer: the 'Should' stories are the cut list if time runs short. Cutting all of them saves about 5-11 weeks.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="102" customHeight="1" s="20">
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>Kill gates: M2 (is the console chronicle interesting? failed 2026-09-30, passed at the M2b retry) and M6 (do playtesters stay?), held after M9 (D-34). Critical path: M0 &gt; M1 &gt; M1b &gt; M2 &gt; M2b &gt; M2c &gt; M2d &gt; M3 &gt; M4 &gt; M5 &gt; M7 &gt; M8 &gt; M9 &gt; M6. Dates of M2c onwards are not re-planned yet.</t>
-        </is>
-      </c>
-    </row>
+    <row r="35" ht="102" customHeight="1" s="20">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Kill gates: M2 (failed 2026-09-30, passed at the M2b retry) and M6 (do playtesters stay?), held after M14 (D-41). Critical path: M0 &gt; M1 &gt; M1b &gt; M2 &gt; M2b &gt; M2c &gt; M2d &gt; M3 &gt; M4 &gt; M5 &gt; M7 &gt; M8 &gt; M8b &gt; M8c &gt; M8d &gt; M8e &gt; M9 &gt; M10 &gt; M11 &gt; M12 &gt; M13 &gt; M14 &gt; M6. Dates of M2c onwards are not re-planned yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B25:N25"/>
-    <mergeCell ref="B24:N24"/>
-    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B33:N33"/>
   </mergeCells>
-  <conditionalFormatting sqref="P7:EY20">
+  <conditionalFormatting sqref="P7:JO29">
     <cfRule type="expression" priority="1" dxfId="10">
       <formula>AND(P$6&gt;=$G7,P$6&lt;=$H7)</formula>
     </cfRule>
@@ -3008,7 +4077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="20" min="1" max="1"/>
@@ -3034,7 +4103,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -3265,7 +4333,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Minimum PC spec (OPEN-19)</t>
+          <t>Minimum PC spec (OPEN-19). Mid-range PC (owner, 2026-10-01): 6-core CPU, 16 GB RAM, RX 6600 / RTX 3060 class GPU (8 GB) with DirectX 12, Windows 10/11; 60 FPS at 1080p on High lighting, Low for weaker PCs. Development PC: RX 7900 XTX, 32 GB RAM, 6-core CPU.</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -3275,12 +4343,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M8b</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>US-082</t>
+          <t>US-082, US-234</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -3290,7 +4358,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Decided</t>
         </is>
       </c>
     </row>
@@ -3598,7 +4666,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Technical chain: M0 &gt; M1 &gt; M1b &gt; M2 &gt; M2b &gt; M2c &gt; M2d &gt; M3 &gt; M4 &gt; M5 &gt; M7 &gt; M8 &gt; M9 &gt; M6 (each milestone needs the previous one)</t>
+          <t>Technical chain: M0 &gt; M1 &gt; M1b &gt; M2 &gt; M2b &gt; M2c &gt; M2d &gt; M3 &gt; M4 &gt; M5 &gt; M7 &gt; M8 &gt; M8b &gt; M8c &gt; M8d &gt; M8e &gt; M9 &gt; M10 &gt; M11 &gt; M12 &gt; M13 &gt; M14 &gt; M6 (each milestone needs the previous one)</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -3881,6 +4949,154 @@
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25.5" customHeight="1" s="20">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>D-40</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (Round 14): M10 Quests (authored only, JSON + quest graph, flat with prerequisites, journal + tracker + markers, tutorial as a quest, story events), M11 Data editors (schema forms, Game Rules with system switches, daily routines), M12 World editing (generator settings with preview, overrides on the seed, per clan and person setup), M13 Politics (third pillar with victory); play-in-editor debugger; kill gate 2 after M13</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Design decision</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>US-180..US-216</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25.5" customHeight="1" s="20">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>D-41</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Technology pillar (M14: tech tree as data, research by doing, workshops and inventors, espionage and theft; victory = Ember held + 60% Technology share or the four-pillar 50% average); Politics victory confirmed (60% / 50%); Game Rules default standard.json, levels may name their own; M10-M14: Dominus decides design questions (delegated) and tests run at exit reviews; kill gate 2 after M14</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Design decision</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>US-180..US-226</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25.5" customHeight="1" s="20">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>D-42</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (Round 16): 960x540 with window modes, camera zoom, UI scale; SDL_GPU shaders; sun, moon, fire, torch and effect lights, seasonal day length, weather light; shadows from sun, moon and nearby fires; generated normal maps; buildings from blueprints and pieces, clans build, wear, repair, fire; interiors per building (roof fade or interior map); prefabs in the Editor; M8b, M8c, M8d right after M8</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Design decision</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>M8b</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>US-230..US-257</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="25.5" customHeight="1" s="20">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>D-43</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Assembly of M8b-M8e (Round 17): M8d split into M8d Buildings (US-250, 251, 252, 256) and M8e Building life (US-253, 254, 255, 257); US-256 no longer waits for US-254; M7-M9 assembly rules (D-35) apply; D-06 answered</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Design decision</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>M8b</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>US-230..US-257</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
@@ -3916,7 +5132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="20" min="1" max="1"/>
@@ -3944,7 +5160,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="25.5" customHeight="1" s="20">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4779,37 +5994,451 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="inlineStr">
+    <row r="22" ht="25.5" customHeight="1" s="20">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Quests</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>The owner writes quests in the Editor and offline; players get, follow and finish them with a journal, a tracker and markers.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="E22" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A22,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G22" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A22,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A22,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I22" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A22,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J22" s="17">
+        <f>IFERROR(I22/E22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="25.5" customHeight="1" s="20">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Data editors</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Every data file (entities, mechanics, story tuning, game rules, daily routines) is edited in the Editor through forms built from schemas.</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E23" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A23,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G23" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A23,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A23,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I23" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A23,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J23" s="17">
+        <f>IFERROR(I23/E23,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="25.5" customHeight="1" s="20">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>World editing</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>The owner shapes the procedural region and its clans, people, economy and relations in the Editor, on top of the seed.</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="E24" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A24,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G24" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A24,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A24,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I24" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A24,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J24" s="17">
+        <f>IFERROR(I24/E24,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="25.5" customHeight="1" s="20">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Clans ally, swear and break oaths, marry, vote and challenge leaders; the player can win the region through Politics.</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="E25" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A25,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G25" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A25,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A25,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I25" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A25,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>IFERROR(I25/E25,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="25.5" customHeight="1" s="20">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Clans discover, teach, guard and steal technologies; the player can win the region by forging the Ember Strand while leading in know-how.</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="E26" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A26,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G26" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A26,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A26,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I26" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A26,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J26" s="17">
+        <f>IFERROR(I26/E26,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="25.5" customHeight="1" s="20">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Resolution and GPU renderer</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>The game renders at 960x540 on Luna's new SDL_GPU renderer, in any window size or full screen, and every screen and editor has room to breathe.</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>M8b</t>
+        </is>
+      </c>
+      <c r="E27" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A27)</f>
+        <v/>
+      </c>
+      <c r="F27" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A27,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G27" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A27,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A27,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I27" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A27,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J27" s="17">
+        <f>IFERROR(I27/E27,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="25.5" customHeight="1" s="20">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Lighting and shadows</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Days and nights, seasons and weather light the world; fires glow; characters, plants and buildings cast shadows that move with the sun, the moon and nearby fires.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="E28" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A28)</f>
+        <v/>
+      </c>
+      <c r="F28" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A28,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G28" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A28,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A28,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I28" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A28,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J28" s="17">
+        <f>IFERROR(I28/E28,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="25.5" customHeight="1" s="20">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>The hero builds from whole blueprints and piece by piece; the owner composes pre-made buildings in the Editor and places them.</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>M8d</t>
+        </is>
+      </c>
+      <c r="E29" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A29)</f>
+        <v/>
+      </c>
+      <c r="F29" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A29,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G29" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A29,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A29,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I29" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A29,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J29" s="17">
+        <f>IFERROR(I29/E29,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="25.5" customHeight="1" s="20">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Building life</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Clans build together; interiors by roof fade or interior map; wear, repair, damage and fire; shelter, warmth and storage for the clan.</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>M8e</t>
+        </is>
+      </c>
+      <c r="E30" s="9">
+        <f>COUNTIF('User Stories'!$B$5:$B$200,A30)</f>
+        <v/>
+      </c>
+      <c r="F30" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A30,'User Stories'!$F$5:$F$200,"Must")</f>
+        <v/>
+      </c>
+      <c r="G30" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A30,'User Stories'!$H$5:$H$200)</f>
+        <v/>
+      </c>
+      <c r="H30" s="9">
+        <f>SUMIF('User Stories'!$B$5:$B$200,A30,'User Stories'!$I$5:$I$200)</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>COUNTIFS('User Stories'!$B$5:$B$200,A30,'User Stories'!$O$5:$O$200,"Done")</f>
+        <v/>
+      </c>
+      <c r="J30" s="17">
+        <f>IFERROR(I30/E30,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7">
-        <f>SUM(E5:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="7">
-        <f>SUM(F5:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="7">
-        <f>SUM(G5:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="7">
-        <f>SUM(H5:H21)</f>
-        <v/>
-      </c>
-      <c r="I22" s="7">
-        <f>SUM(I5:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="18">
-        <f>IFERROR(I22/E22,0)</f>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7">
+        <f>SUM(E5:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="7">
+        <f>SUM(F5:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="7">
+        <f>SUM(G5:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="7">
+        <f>SUM(H5:H30)</f>
+        <v/>
+      </c>
+      <c r="I31" s="7">
+        <f>SUM(I5:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="18">
+        <f>IFERROR(I31/E31,0)</f>
         <v/>
       </c>
     </row>
@@ -4824,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="20" min="1" max="1"/>
@@ -4857,7 +6486,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="25.5" customHeight="1" s="20">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -11053,7 +12681,7 @@
       </c>
       <c r="O79" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11139,7 +12767,7 @@
       </c>
       <c r="O80" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11225,7 +12853,7 @@
       </c>
       <c r="O81" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11311,7 +12939,7 @@
       </c>
       <c r="O82" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11397,7 +13025,7 @@
       </c>
       <c r="O83" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11483,7 +13111,7 @@
       </c>
       <c r="O84" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11569,7 +13197,7 @@
       </c>
       <c r="O85" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11655,7 +13283,7 @@
       </c>
       <c r="O86" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11741,7 +13369,7 @@
       </c>
       <c r="O87" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -11827,7 +13455,7 @@
       </c>
       <c r="O88" s="16" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -12600,6 +14228,4994 @@
         </is>
       </c>
       <c r="O97" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="124.15" customHeight="1" s="20">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>US-180</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Quest data and runtime</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want quests as JSON files with steps, objectives, conditions, rewards and prerequisites, so that I can write quests offline and the game runs them.</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Load
+Given a quest file with two steps, a branch and a reward
+When the game starts
+Then the quest is available once its prerequisites hold
+Scenario: Progress
+Given an active quest
+When its step's objective is met
+Then the next step starts and the reward is given at the end
+Scenario: Error
+Given a quest whose step points to a missing step on line 14
+When the data loads
+Then the error reads 'quests/&lt;file&gt;.json:14: unknown step' and the rest loads</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H98" s="9">
+        <f>VLOOKUP(G98,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I98" s="9">
+        <f>VLOOKUP(G98,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>US-150, US-164, D-40</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>STO-04, ADR-019</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr">
+        <is>
+          <t>State machines over data; saving progress</t>
+        </is>
+      </c>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O98" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="124.15" customHeight="1" s="20">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>US-181</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Objectives from world events</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want my actions in the world to count toward quests, so that quests follow what I really do.</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Count
+Given an objective 'gather 5 berries'
+When the hero gathers 5 berries
+Then the objective is complete
+Scenario: Kinds
+Given objectives talk, go to, gather, give, craft, interact, defeat, wait and flag
+When each happens
+Then each is detected
+Scenario: Not mine
+Given an NPC gathering berries
+When it happens
+Then the hero's quest does not count it</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H99" s="9">
+        <f>VLOOKUP(G99,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I99" s="9">
+        <f>VLOOKUP(G99,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>US-180</t>
+        </is>
+      </c>
+      <c r="L99" s="9" t="inlineStr">
+        <is>
+          <t>STO-04, INT-01</t>
+        </is>
+      </c>
+      <c r="M99" s="9" t="inlineStr">
+        <is>
+          <t>An event bus (observer pattern)</t>
+        </is>
+      </c>
+      <c r="N99" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O99" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="124.15" customHeight="1" s="20">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>US-182</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Getting and handing in quests</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want NPCs to offer quests in conversation and take them back when done, so that quests belong to people.</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Offer
+Given an NPC with an available quest
+When the hero is near
+Then a quest sign shows over the NPC and Talk offers the quest
+Scenario: Accept
+Given the offer in a .dlg choice with {quest start &lt;id&gt;}
+When the player picks it
+Then the quest is active
+Scenario: Hand in
+Given a finished quest and its giver
+When the player talks to the giver
+Then the turn-in line plays and the reward is given</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H100" s="9">
+        <f>VLOOKUP(G100,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I100" s="9">
+        <f>VLOOKUP(G100,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>US-180, US-161</t>
+        </is>
+      </c>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>STO-04, SDC-03</t>
+        </is>
+      </c>
+      <c r="M100" s="9" t="inlineStr">
+        <is>
+          <t>Linking two data systems through ids</t>
+        </is>
+      </c>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O100" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="124.15" customHeight="1" s="20">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>US-183</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Journal, tracker and markers</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want a journal, an on-screen tracker and markers over targets, so that I always know what to do next.</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Journal
+Given two active, one done and one failed quest
+When the player opens the journal
+Then they are listed in their groups with each step's text and log
+Scenario: Tracker
+Given an active quest
+When its step changes
+Then the tracker shows the new step at once
+Scenario: Markers
+Given markers on in settings
+When a step targets a person or place
+Then a marker shows over it; with markers off, none shows</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H101" s="9">
+        <f>VLOOKUP(G101,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I101" s="9">
+        <f>VLOOKUP(G101,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>US-180</t>
+        </is>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>STO-04</t>
+        </is>
+      </c>
+      <c r="M101" s="9" t="inlineStr">
+        <is>
+          <t>Immediate-mode UI lists</t>
+        </is>
+      </c>
+      <c r="N101" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O101" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="124.15" customHeight="1" s="20">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>US-184</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Quest graph editor</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to build quests as graphs in the Editor, so that I can see and change their steps, branches and prerequisites.</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Steps
+Given a quest open in the Editor
+When the owner adds a step and wires a branch
+Then the graph and the saved JSON show them
+Scenario: Blocks
+Given a step selected
+When the owner adds an objective, a condition and a reward
+Then pickers offer items, people, places, tags and quests
+Scenario: Prerequisites
+Given the quest list view
+When the owner links quest B after quest A
+Then B's prerequisites name A and the view draws the link</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H102" s="9">
+        <f>VLOOKUP(G102,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I102" s="9">
+        <f>VLOOKUP(G102,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>US-180, US-170</t>
+        </is>
+      </c>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>STO-04, EDT-01</t>
+        </is>
+      </c>
+      <c r="M102" s="9" t="inlineStr">
+        <is>
+          <t>Reusing a generic widget for a new data type</t>
+        </is>
+      </c>
+      <c r="N102" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O102" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="124.15" customHeight="1" s="20">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>US-185</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>The tutorial as a quest; story events</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want the elder tutorial rebuilt as the first quest and the crossroads events edited as story events, so that all story content is authored in one place.</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Tutorial
+Given a new game with the tutorial on
+When the player starts
+Then the elder quest guides gather, eat and tend the fire as before, with the hint after 2 minutes
+Scenario: Story events
+Given a crossroads event
+When the owner opens it in the Editor
+Then its trigger, text and options with effects are edited and saved
+Scenario: Same game
+Given the M5 and M6 tests
+When they run
+Then they pass</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H103" s="9">
+        <f>VLOOKUP(G103,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I103" s="9">
+        <f>VLOOKUP(G103,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="inlineStr">
+        <is>
+          <t>US-184, US-090</t>
+        </is>
+      </c>
+      <c r="L103" s="9" t="inlineStr">
+        <is>
+          <t>STO-05, EDT-01</t>
+        </is>
+      </c>
+      <c r="M103" s="9" t="inlineStr">
+        <is>
+          <t>Migrating data without changing behaviour</t>
+        </is>
+      </c>
+      <c r="N103" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O103" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="124.15" customHeight="1" s="20">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>US-186</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Play-in-editor debugger</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to play from any spot in the Editor with a debug panel, so that I can test quests and content in minutes.</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Play here
+Given the Editor open
+When the owner chooses Play here
+Then the hero starts at the cursor and Esc returns to the Editor unchanged
+Scenario: Control
+Given the debug panel
+When the owner starts, completes or resets a quest, sets a flag, an item or an opinion, jumps time or teleports
+Then the game reflects it at once
+Scenario: Why not
+Given a quest step that does not complete
+When the owner selects it in the panel
+Then the failing condition and its current values are shown</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H104" s="9">
+        <f>VLOOKUP(G104,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I104" s="9">
+        <f>VLOOKUP(G104,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="K104" s="9" t="inlineStr">
+        <is>
+          <t>US-180</t>
+        </is>
+      </c>
+      <c r="L104" s="9" t="inlineStr">
+        <is>
+          <t>EDT-06</t>
+        </is>
+      </c>
+      <c r="M104" s="9" t="inlineStr">
+        <is>
+          <t>Debug-only code paths</t>
+        </is>
+      </c>
+      <c r="N104" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O104" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="124.15" customHeight="1" s="20">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>US-187</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Quest validation</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want broken quests found before players see them, so that no quest can get stuck.</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Unreachable
+Given a step no branch leads to
+When validation runs
+Then it is listed and clicking it selects it
+Scenario: Impossible
+Given an objective naming an unknown item, person or place
+When validation runs
+Then it is listed
+Scenario: Cycle
+Given quests that require each other
+When validation runs
+Then the prerequisite cycle is listed</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H105" s="9">
+        <f>VLOOKUP(G105,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I105" s="9">
+        <f>VLOOKUP(G105,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="inlineStr">
+        <is>
+          <t>US-184</t>
+        </is>
+      </c>
+      <c r="L105" s="9" t="inlineStr">
+        <is>
+          <t>STO-04, EDT-01</t>
+        </is>
+      </c>
+      <c r="M105" s="9" t="inlineStr">
+        <is>
+          <t>Cycle detection in a graph</t>
+        </is>
+      </c>
+      <c r="N105" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O105" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="124.15" customHeight="1" s="20">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>US-190</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Schemas for every data file</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want every data file described by a schema with types, ranges, choices, links and help text, so that the Editor and the validator know what each field means.</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Coverage
+Given every file under assets/data/
+When the schema check runs in CI
+Then each file has a schema and passes it
+Scenario: Errors
+Given a value out of its range
+When the game loads it
+Then the error names file, line, field and the allowed range
+Scenario: Links
+Given a recipe naming an item no catalog has
+When the check runs
+Then the broken link is listed</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H106" s="9">
+        <f>VLOOKUP(G106,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I106" s="9">
+        <f>VLOOKUP(G106,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>US-150</t>
+        </is>
+      </c>
+      <c r="L106" s="9" t="inlineStr">
+        <is>
+          <t>EDT-02, ADR-020</t>
+        </is>
+      </c>
+      <c r="M106" s="9" t="inlineStr">
+        <is>
+          <t>Describing data with data (a schema interpreter)</t>
+        </is>
+      </c>
+      <c r="N106" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O106" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="124.15" customHeight="1" s="20">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>US-191</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Schema-driven form editor</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want a Data tab where any file opens as forms built from its schema, so that I can edit everything without touching JSON.</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Open
+Given weapons.json
+When the owner opens it in the Data tab
+Then entries are listed with search, and a form shows the selected entry's fields with help text
+Scenario: Edit
+Given a damage value changed and Ctrl+S
+When the file is saved
+Then only that value changes in the file, note fields stay, and the running game uses it
+Scenario: Undo
+Given five form edits
+When Ctrl+Z five times
+Then the data is as before</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H107" s="9">
+        <f>VLOOKUP(G107,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I107" s="9">
+        <f>VLOOKUP(G107,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>US-190, US-121</t>
+        </is>
+      </c>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>EDT-02</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>Building UI from a description at run time</t>
+        </is>
+      </c>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O107" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="124.15" customHeight="1" s="20">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>US-192</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Picture pickers and cutting frames</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to pick sprites, animations and effects by picture and cut new frames from my sheets in the Editor, so that new content gets its art without the command line.</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Pick
+Given a field holding an atlas frame
+When the owner opens its picker
+Then frames are shown as pictures and the choice is saved
+Scenario: Preview
+Given an effect or an animation
+When it is selected
+Then it plays in the form
+Scenario: Cut
+Given a sheet in assets/sprites/
+When the owner draws a rectangle and names it
+Then cuts.json gains the cut and the atlas is rebuilt</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H108" s="9">
+        <f>VLOOKUP(G108,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I108" s="9">
+        <f>VLOOKUP(G108,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>US-191, US-120</t>
+        </is>
+      </c>
+      <c r="L108" s="9" t="inlineStr">
+        <is>
+          <t>EDT-02, D-05</t>
+        </is>
+      </c>
+      <c r="M108" s="9" t="inlineStr">
+        <is>
+          <t>Image regions and previews</t>
+        </is>
+      </c>
+      <c r="N108" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O108" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="124.15" customHeight="1" s="20">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>US-193</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Entity editor</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to create, copy, rename and delete kinds of weapons, plants, animals, characters, objects and items, with their tags, states and interactions, so that new entities need no code.</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Create
+Given the plants catalog
+When the owner copies a bush, renames it and changes its tags
+Then the new plant appears in the Editor palette and offers its interactions
+Scenario: Rename
+Given an item used by recipes and quests
+When the owner renames it
+Then every reference is updated and listed
+Scenario: Delete
+Given a kind that is still used
+When the owner deletes it
+Then the uses are listed and the delete waits for confirmation</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H109" s="9">
+        <f>VLOOKUP(G109,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I109" s="9">
+        <f>VLOOKUP(G109,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>US-191, US-172</t>
+        </is>
+      </c>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>EDT-02, INT-02</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>Keeping references consistent (rename refactoring)</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O109" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="124.15" customHeight="1" s="20">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>US-194</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Mechanics and story tuning with a quick check</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want needs, actions, life, social, story, calendar, professions, recipes and hero data in forms, and a quick headless run to see the effect, so that I can tune mechanics safely.</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Forms
+Given every mechanics and story file
+When the owner opens it
+Then it shows as forms
+Scenario: Quick check
+Given a changed hunger rate
+When the owner runs the 20-year check
+Then a summary shows population, deaths by cause and episodes, next to the last run
+Scenario: Determinism
+Given the same data and seed
+When the check runs twice
+Then the summaries are the same</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H110" s="9">
+        <f>VLOOKUP(G110,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I110" s="9">
+        <f>VLOOKUP(G110,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="K110" s="9" t="inlineStr">
+        <is>
+          <t>US-191</t>
+        </is>
+      </c>
+      <c r="L110" s="9" t="inlineStr">
+        <is>
+          <t>EDT-02, STO-02</t>
+        </is>
+      </c>
+      <c r="M110" s="9" t="inlineStr">
+        <is>
+          <t>Running the simulation headless from the game</t>
+        </is>
+      </c>
+      <c r="N110" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O110" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="124.15" customHeight="1" s="20">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>US-195</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Game Rules page</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want one page for New Game presets, comfort, victory thresholds and switches for whole systems, so that I can set up how a game plays.</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Switches
+Given weather, combat, rival clans, tutorial, markers, chronicle and politics switches
+When the owner turns weather off and starts a game
+Then no weather happens
+Scenario: Rules sets
+Given two rules files
+When a new game or a level picks one
+Then its values are used
+Scenario: Thresholds
+Given a victory threshold changed
+When a game reaches it
+Then victory follows the new value</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H111" s="9">
+        <f>VLOOKUP(G111,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I111" s="9">
+        <f>VLOOKUP(G111,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="inlineStr">
+        <is>
+          <t>US-191</t>
+        </is>
+      </c>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>EDT-03, MVP-09</t>
+        </is>
+      </c>
+      <c r="M111" s="9" t="inlineStr">
+        <is>
+          <t>Feature flags read once at start</t>
+        </is>
+      </c>
+      <c r="N111" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O111" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="124.15" customHeight="1" s="20">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>US-196</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Daily routines as data</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want daily routines per role and per person (sleep, work, meals, gatherings at the fire), so that clan life has a rhythm I can shape.</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Routine
+Given the hunters' routine with work from 6 to 14
+When a day passes
+Then hunters choose work interactions in that block more often than at other times
+Scenario: Edit
+Given the Routines editor
+When the owner drags a block on the day timeline
+Then the routine file is saved and used
+Scenario: Needs win
+Given a starving hunter in a work block
+When time passes
+Then they eat first</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H112" s="9">
+        <f>VLOOKUP(G112,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I112" s="9">
+        <f>VLOOKUP(G112,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
+          <t>US-154, US-191</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="inlineStr">
+        <is>
+          <t>SDC-07, INT-05</t>
+        </is>
+      </c>
+      <c r="M112" s="9" t="inlineStr">
+        <is>
+          <t>Time blocks and weighting a utility AI</t>
+        </is>
+      </c>
+      <c r="N112" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O112" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="124.15" customHeight="1" s="20">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>US-200</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>The region in the Editor</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to open the procedural region in the Editor with a zoomable map, so that I can work on the whole world.</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Open
+Given a seed
+When the owner opens the region
+Then it shows at any zoom from the whole 256 x 256 map to single tiles, at a smooth frame rate
+Scenario: Layers
+Given the layer switches
+When the owner hides plants and people
+Then only terrain shows
+Scenario: Same world
+Given the region opened in the Editor
+When it is compared to the game's
+Then they are identical</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H113" s="9">
+        <f>VLOOKUP(G113,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I113" s="9">
+        <f>VLOOKUP(G113,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="K113" s="9" t="inlineStr">
+        <is>
+          <t>US-040, US-123</t>
+        </is>
+      </c>
+      <c r="L113" s="9" t="inlineStr">
+        <is>
+          <t>EDT-04</t>
+        </is>
+      </c>
+      <c r="M113" s="9" t="inlineStr">
+        <is>
+          <t>Streaming chunks and level of detail</t>
+        </is>
+      </c>
+      <c r="N113" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O113" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="124.15" customHeight="1" s="20">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>US-201</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Generator settings with live preview</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want every generator setting in forms with a preview map, so that I can shape a region before committing to it.</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Preview
+Given the biome mix changed
+When the owner presses Preview
+Then a new map shows within a few seconds beside the old one
+Scenario: Apply
+Given a preview the owner likes
+When Apply
+Then the region and region.json use the new settings
+Scenario: Keep edits
+Given hand edits on the region
+When the settings change
+Then the edits stay and conflicts are listed</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H114" s="9">
+        <f>VLOOKUP(G114,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I114" s="9">
+        <f>VLOOKUP(G114,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>US-200, US-191</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="inlineStr">
+        <is>
+          <t>EDT-04</t>
+        </is>
+      </c>
+      <c r="M114" s="9" t="inlineStr">
+        <is>
+          <t>Pure functions of a seed</t>
+        </is>
+      </c>
+      <c r="N114" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O114" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="124.15" customHeight="1" s="20">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>US-202</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Hand edits on top of the seed</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to paint terrain and biomes on the region and keep them on top of the seed, so that the world is generated and hand-made at once.</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Paint
+Given the brush on the region
+When the owner paints a meadow into a forest
+Then the change shows and is saved as an override of those chunks
+Scenario: Small saves
+Given 100 painted tiles
+When the region is saved
+Then the file holds the seed plus the changed tiles, not the whole map
+Scenario: Undo
+Given region edits
+When Ctrl+Z
+Then they are undone as in the level editor</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H115" s="9">
+        <f>VLOOKUP(G115,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I115" s="9">
+        <f>VLOOKUP(G115,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="K115" s="9" t="inlineStr">
+        <is>
+          <t>US-200</t>
+        </is>
+      </c>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>EDT-04, ADR-010</t>
+        </is>
+      </c>
+      <c r="M115" s="9" t="inlineStr">
+        <is>
+          <t>Storing differences (overlays) instead of copies</t>
+        </is>
+      </c>
+      <c r="N115" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O115" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="124.15" customHeight="1" s="20">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>US-203</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>Water and mountains</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to draw and remove rivers, lakes, cliffs and caves, so that I can shape the land.</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: River
+Given the river tool
+When the owner draws a river
+Then it flows from start to end and blocks walking except at fords
+Scenario: Cave
+Given a cliff
+When the owner places a cave mouth
+Then the cave can be entered in the game
+Scenario: Remove
+Given a generated lake
+When the owner removes it
+Then land replaces it and the change is an override</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H116" s="9">
+        <f>VLOOKUP(G116,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I116" s="9">
+        <f>VLOOKUP(G116,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>US-202</t>
+        </is>
+      </c>
+      <c r="L116" s="9" t="inlineStr">
+        <is>
+          <t>EDT-04</t>
+        </is>
+      </c>
+      <c r="M116" s="9" t="inlineStr">
+        <is>
+          <t>Path tools and connected areas</t>
+        </is>
+      </c>
+      <c r="N116" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O116" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="124.15" customHeight="1" s="20">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>US-204</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Things, people and places in the region</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to place plants, animals, objects, people and named places in the region, so that quests and stories have their spots.</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Place
+Given the palettes
+When the owner places a fire pit and an NPC
+Then they are saved as region overrides and appear in the game
+Scenario: Places
+Given a named place 'Red Cliff'
+When a quest step targets it
+Then the quest marker points to it
+Scenario: Pickers
+Given a quest or dialogue field
+When the owner picks a person or place
+Then region people and places are offered</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H117" s="9">
+        <f>VLOOKUP(G117,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I117" s="9">
+        <f>VLOOKUP(G117,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="K117" s="9" t="inlineStr">
+        <is>
+          <t>US-202, US-155</t>
+        </is>
+      </c>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>EDT-04, STO-04</t>
+        </is>
+      </c>
+      <c r="M117" s="9" t="inlineStr">
+        <is>
+          <t>Ids that survive regeneration</t>
+        </is>
+      </c>
+      <c r="N117" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O117" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="124.15" customHeight="1" s="20">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>US-205</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>Camps and resources</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to move the player and rival camps and set resource spots and amounts, so that I control the region's balance.</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Camps
+Given a rival camp
+When the owner moves it
+Then the rival clan lives there in the game
+Scenario: Resources
+Given a flint spot
+When the owner sets it to 50
+Then 50 flint can be taken there
+Scenario: Rules
+Given a camp placed in water
+When the owner tries
+Then it is refused with the reason</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H118" s="9">
+        <f>VLOOKUP(G118,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I118" s="9">
+        <f>VLOOKUP(G118,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="K118" s="9" t="inlineStr">
+        <is>
+          <t>US-202, US-041</t>
+        </is>
+      </c>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>EDT-04, MVP-10</t>
+        </is>
+      </c>
+      <c r="M118" s="9" t="inlineStr">
+        <is>
+          <t>Validating placements against rules</t>
+        </is>
+      </c>
+      <c r="N118" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O118" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="124.15" customHeight="1" s="20">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>US-206</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>Clans and people inspector</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to edit each clan and person in the world: members, kinship, leader, opinions and grudges, rival stance, owned items, stores, debts, trade partners, routine and allowed actions, so that I set up the social, economic and political world.</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Social
+Given two people selected
+When the owner sets their opinion to -50 and adds a grudge with a reason
+Then the game starts with that grudge and the chronicle can tell it
+Scenario: Economy
+Given a clan selected
+When the owner fills its store and adds a debt to a rival
+Then the game starts with that store and debt
+Scenario: Overrides
+Given a person selected
+When the owner removes Barter from their actions and changes their HP
+Then only that person changes</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H119" s="9">
+        <f>VLOOKUP(G119,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I119" s="9">
+        <f>VLOOKUP(G119,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>US-204, US-196, US-173</t>
+        </is>
+      </c>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>EDT-05, SDC-07, PIL-08</t>
+        </is>
+      </c>
+      <c r="M119" s="9" t="inlineStr">
+        <is>
+          <t>Editing a graph of relations safely</t>
+        </is>
+      </c>
+      <c r="N119" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O119" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="124.15" customHeight="1" s="20">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>US-207</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Play the edited region</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to start a new game on my edited region or play it from the Editor, so that my world is the game.</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: New game
+Given an edited region saved as a world file
+When the player starts a new game from it
+Then every edit is there
+Scenario: Play here
+Given the region in the Editor
+When the owner chooses Play here
+Then the game starts on the edited region at the cursor
+Scenario: Old saves
+Given a save from before region editing
+When it loads
+Then it still works</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H120" s="9">
+        <f>VLOOKUP(G120,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I120" s="9">
+        <f>VLOOKUP(G120,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="K120" s="9" t="inlineStr">
+        <is>
+          <t>US-206, US-186</t>
+        </is>
+      </c>
+      <c r="L120" s="9" t="inlineStr">
+        <is>
+          <t>EDT-04, EDT-06</t>
+        </is>
+      </c>
+      <c r="M120" s="9" t="inlineStr">
+        <is>
+          <t>Versioned save formats</t>
+        </is>
+      </c>
+      <c r="N120" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O120" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="124.15" customHeight="1" s="20">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>US-210</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>The political model</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want clans as political actors with relations, alliances, vassal ties and a Politics share of the region, all as editable data, so that politics is part of the simulation.</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Relations
+Given three clans
+When the simulation runs
+Then each pair has a stance from -100 to 100 that moves with events, with reasons
+Scenario: Share
+Given one rival a vassal of the player's clan
+When the dominion screen opens
+Then Politics shows that clan's share of the region's people
+Scenario: Data
+Given politics.json
+When the owner opens it in the Data tab
+Then every political rule is a form</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H121" s="9">
+        <f>VLOOKUP(G121,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I121" s="9">
+        <f>VLOOKUP(G121,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="K121" s="9" t="inlineStr">
+        <is>
+          <t>US-206, US-195</t>
+        </is>
+      </c>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>PIL-03, PIL-08</t>
+        </is>
+      </c>
+      <c r="M121" s="9" t="inlineStr">
+        <is>
+          <t>Modelling relations between groups</t>
+        </is>
+      </c>
+      <c r="N121" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O121" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="124.15" customHeight="1" s="20">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>US-211</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Alliances and vassal oaths</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want to ally with clans, take tribute and make them swear vassal oaths, which can break, so that I can bind the region to my clan.</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Alliance
+Given a rival with a good stance
+When the hero proposes an alliance
+Then it is accepted or refused with a reason
+Scenario: Oath
+Given an allied clan that is weaker and indebted
+When the hero asks for a vassal oath
+Then it swears and pays tribute each season
+Scenario: Break
+Given a vassal whose stance falls below its limit
+When a season passes
+Then it may break the oath, and the chronicle says why</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H122" s="9">
+        <f>VLOOKUP(G122,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I122" s="9">
+        <f>VLOOKUP(G122,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="K122" s="9" t="inlineStr">
+        <is>
+          <t>US-210</t>
+        </is>
+      </c>
+      <c r="L122" s="9" t="inlineStr">
+        <is>
+          <t>PIL-03, PIL-08</t>
+        </is>
+      </c>
+      <c r="M122" s="9" t="inlineStr">
+        <is>
+          <t>Contracts as data with conditions</t>
+        </is>
+      </c>
+      <c r="N122" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O122" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="124.15" customHeight="1" s="20">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>US-212</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>Elders' council</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want clan decisions voted by the elders and to sway them, so that leading a clan means persuading people.</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Vote
+Given a decision to move camp
+When the council meets
+Then each elder votes by needs, traits and opinion, and the result is shown
+Scenario: Sway
+Given the hero talks to an elder before the vote
+When a persuasion choice succeeds
+Then that elder's vote changes
+Scenario: Record
+Given a council decision
+When it is taken
+Then the chronicle records it with the votes</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H123" s="9">
+        <f>VLOOKUP(G123,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I123" s="9">
+        <f>VLOOKUP(G123,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="K123" s="9" t="inlineStr">
+        <is>
+          <t>US-210</t>
+        </is>
+      </c>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>PIL-08, SDC-02</t>
+        </is>
+      </c>
+      <c r="M123" s="9" t="inlineStr">
+        <is>
+          <t>Simple voting rules and weights</t>
+        </is>
+      </c>
+      <c r="N123" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O123" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="124.15" customHeight="1" s="20">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>US-213</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Marriage ties</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want marriages between clans to bind them, so that love and politics meet.</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Tie
+Given a courtship between two clans' members
+When they marry
+Then the clans' stance rises and a marriage tie is recorded
+Scenario: Alliance
+Given a marriage tie
+When an alliance is proposed
+Then acceptance is more likely
+Scenario: Parting
+Given a married couple parts
+When it happens
+Then the tie weakens and the stance falls</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H124" s="9">
+        <f>VLOOKUP(G124,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I124" s="9">
+        <f>VLOOKUP(G124,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="K124" s="9" t="inlineStr">
+        <is>
+          <t>US-210, US-113</t>
+        </is>
+      </c>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>PIL-08, SDC-02</t>
+        </is>
+      </c>
+      <c r="M124" s="9" t="inlineStr">
+        <is>
+          <t>Events that affect two systems</t>
+        </is>
+      </c>
+      <c r="N124" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O124" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="124.15" customHeight="1" s="20">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>US-214</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>Leadership challenges</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want leaders to be challenged when their people turn against them, and to challenge or back a leader myself, so that power can change hands.</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Challenge
+Given a leader whose clan opinion is below the limit
+When time passes
+Then a challenger rises and the council or a contest decides
+Scenario: Hero
+Given the hero with enough support
+When the hero challenges the leader
+Then the outcome follows the rules and the chronicle tells it
+Scenario: Succession
+Given a leader dies
+When it happens
+Then succession is contested between candidates with reasons</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H125" s="9">
+        <f>VLOOKUP(G125,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I125" s="9">
+        <f>VLOOKUP(G125,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="K125" s="9" t="inlineStr">
+        <is>
+          <t>US-212</t>
+        </is>
+      </c>
+      <c r="L125" s="9" t="inlineStr">
+        <is>
+          <t>PIL-08</t>
+        </is>
+      </c>
+      <c r="M125" s="9" t="inlineStr">
+        <is>
+          <t>State transitions with guards</t>
+        </is>
+      </c>
+      <c r="N125" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O125" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="124.15" customHeight="1" s="20">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>US-215</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Economic and technological levers</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want trade pacts, tribute in goods, embargoes and sharing crafts with allies as political tools, so that wealth and know-how buy influence.</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Pact
+Given two allied clans
+When a trade pact is made
+Then barter between them is cheaper and stance rises
+Scenario: Embargo
+Given a rival under embargo
+When it tries to trade with the hero's allies
+Then it is refused and stance falls
+Scenario: Know-how
+Given the hero teaches an ally a recipe
+When it happens
+Then the ally can craft it and its stance and dependence rise</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H126" s="9">
+        <f>VLOOKUP(G126,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I126" s="9">
+        <f>VLOOKUP(G126,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="K126" s="9" t="inlineStr">
+        <is>
+          <t>US-211, US-062</t>
+        </is>
+      </c>
+      <c r="L126" s="9" t="inlineStr">
+        <is>
+          <t>PIL-08, PIL-02</t>
+        </is>
+      </c>
+      <c r="M126" s="9" t="inlineStr">
+        <is>
+          <t>Interfaces between subsystems</t>
+        </is>
+      </c>
+      <c r="N126" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O126" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="124.15" customHeight="1" s="20">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>US-216</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>Political victory and diplomacy</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want to win the region through Politics and to do diplomacy in conversation, so that Politics is a full path to victory.</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Victory
+Given vassals holding 60% of the region's people (Game Rules value)
+When the share is reached
+Then the game ends in a Political victory with the chronicle
+Scenario: Combined
+Given Trade, Religion and Politics shares
+When they reach the combined threshold
+Then victory follows the Game Rules
+Scenario: Diplomacy
+Given a clan leader
+When the hero talks to them
+Then alliance, oath, pact and embargo choices are offered in the conversation</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H127" s="9">
+        <f>VLOOKUP(G127,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I127" s="9">
+        <f>VLOOKUP(G127,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="K127" s="9" t="inlineStr">
+        <is>
+          <t>US-211, US-195, US-161</t>
+        </is>
+      </c>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>PIL-03, PIL-08, MVP-08, MVP-09</t>
+        </is>
+      </c>
+      <c r="M127" s="9" t="inlineStr">
+        <is>
+          <t>Combining scores from several systems</t>
+        </is>
+      </c>
+      <c r="N127" s="9" t="inlineStr">
+        <is>
+          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
+        </is>
+      </c>
+      <c r="O127" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="124.15" customHeight="1" s="20">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>US-220</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>The tech tree as data</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want Age 1 technologies with prerequisites, discovery rules and unlocks in a data file shown as a tree in the Editor, so that I can design how know-how grows.</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Load
+Given technologies.json with fire mastery, hafted spears, sewing and ochre
+When the game starts
+Then each technology's prerequisites and unlocks (recipes, interactions, professions, objects) are known
+Scenario: Editor
+Given the tech tree view
+When the owner adds a technology and links it after another
+Then the tree and the saved file show it
+Scenario: Cycle
+Given two technologies that require each other
+When validation runs
+Then the cycle is listed</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H128" s="9">
+        <f>VLOOKUP(G128,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I128" s="9">
+        <f>VLOOKUP(G128,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>US-191, US-170, D-41</t>
+        </is>
+      </c>
+      <c r="L128" s="9" t="inlineStr">
+        <is>
+          <t>PIL-05, PIL-09, EDT-02</t>
+        </is>
+      </c>
+      <c r="M128" s="9" t="inlineStr">
+        <is>
+          <t>Directed acyclic graphs and topological order</t>
+        </is>
+      </c>
+      <c r="N128" s="9" t="inlineStr">
+        <is>
+          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
+        </is>
+      </c>
+      <c r="O128" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="124.15" customHeight="1" s="20">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>US-221</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Research by doing</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want my clan to discover technologies by using skills and materials, so that progress grows out of daily life.</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Discover
+Given a clan that knaps flint every day
+When enough research has built up
+Then the next flint technology is discovered and its recipes unlock
+Scenario: Chronicle
+Given a discovery
+When it happens
+Then the chronicle says who discovered it and how
+Scenario: Locked
+Given a technology whose prerequisite is unknown
+When the work happens
+Then it is not discovered</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H129" s="9">
+        <f>VLOOKUP(G129,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I129" s="9">
+        <f>VLOOKUP(G129,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="K129" s="9" t="inlineStr">
+        <is>
+          <t>US-220</t>
+        </is>
+      </c>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>PIL-09</t>
+        </is>
+      </c>
+      <c r="M129" s="9" t="inlineStr">
+        <is>
+          <t>Accumulators and thresholds</t>
+        </is>
+      </c>
+      <c r="N129" s="9" t="inlineStr">
+        <is>
+          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
+        </is>
+      </c>
+      <c r="O129" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="124.15" customHeight="1" s="20">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>US-222</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Workshops, inventors and teaching</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want workshops and inventive people to speed research and teaching to spread knowledge, so that who works where matters.</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Workshop
+Given knapping at a knapping stone versus in the open
+When a day passes
+Then the workshop gives more research, by the data's factor
+Scenario: Inventor
+Given an NPC with the inventive trait
+When they work
+Then they add research faster and can discover alone
+Scenario: Teach
+Given a known technology
+When a member teaches another clan's member (an ally)
+Then that clan knows it after the teaching time</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H130" s="9">
+        <f>VLOOKUP(G130,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I130" s="9">
+        <f>VLOOKUP(G130,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>US-221, US-155</t>
+        </is>
+      </c>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>PIL-09, US-215</t>
+        </is>
+      </c>
+      <c r="M130" s="9" t="inlineStr">
+        <is>
+          <t>Modifiers that stack in a defined order</t>
+        </is>
+      </c>
+      <c r="N130" s="9" t="inlineStr">
+        <is>
+          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
+        </is>
+      </c>
+      <c r="O130" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="124.15" customHeight="1" s="20">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>US-223</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Espionage, theft and secrets</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want rivals to steal or copy know-how and to guard my own, so that knowledge is power to protect.</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Steal
+Given a rival watching our workshop or trading with us
+When time passes
+Then it may learn one of our technologies, and stance falls if caught
+Scenario: Guard
+Given a technology marked secret
+When a rival tries to learn it
+Then the chance is lower and secret-keepers can catch the spy
+Scenario: Repeat
+Given the same seed and inputs
+When two runs
+Then the same thefts happen</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H131" s="9">
+        <f>VLOOKUP(G131,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I131" s="9">
+        <f>VLOOKUP(G131,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="K131" s="9" t="inlineStr">
+        <is>
+          <t>US-222, US-210</t>
+        </is>
+      </c>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>PIL-09, PIL-08</t>
+        </is>
+      </c>
+      <c r="M131" s="9" t="inlineStr">
+        <is>
+          <t>Probabilities from a seeded stream</t>
+        </is>
+      </c>
+      <c r="N131" s="9" t="inlineStr">
+        <is>
+          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
+        </is>
+      </c>
+      <c r="O131" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="124.15" customHeight="1" s="20">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>US-224</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Rival research and the Technology share</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want rival clans to research too and to see who leads in know-how, so that Technology is a race.</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Rivals
+Given two rival clans
+When a year passes
+Then each has discovered technologies by its own priorities
+Scenario: Share
+Given the dominion screen
+When the player opens it
+Then Technology shows each clan's share of the Age 1 technologies known
+Scenario: Data
+Given rival priorities
+When the owner edits them in forms
+Then rivals follow the new priorities</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H132" s="9">
+        <f>VLOOKUP(G132,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I132" s="9">
+        <f>VLOOKUP(G132,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="K132" s="9" t="inlineStr">
+        <is>
+          <t>US-221</t>
+        </is>
+      </c>
+      <c r="L132" s="9" t="inlineStr">
+        <is>
+          <t>PIL-09, ENV-10</t>
+        </is>
+      </c>
+      <c r="M132" s="9" t="inlineStr">
+        <is>
+          <t>Comparing scores across actors</t>
+        </is>
+      </c>
+      <c r="N132" s="9" t="inlineStr">
+        <is>
+          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
+        </is>
+      </c>
+      <c r="O132" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="124.15" customHeight="1" s="20">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>US-225</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>The Ember Strand and Technology victory</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want to forge the Ember Strand at the end of a long chain of discoveries and win when I hold it and lead in know-how, so that Technology is a full path to victory.</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Chain
+Given the Ember chain in technologies.json and recipes.json
+When the clan discovers every step and gathers the materials
+Then the Ember Strand can be forged at the sacred fire
+Scenario: Victory
+Given the Ember Strand held and a Technology share at or above the Game Rules value (60%)
+When both are true
+Then the game ends in a Technology victory with the chronicle
+Scenario: Rival forges
+Given a rival forges Ember first
+When it happens
+Then the chronicle tells it and the player can still win another way or take it</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H133" s="9">
+        <f>VLOOKUP(G133,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I133" s="9">
+        <f>VLOOKUP(G133,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="K133" s="9" t="inlineStr">
+        <is>
+          <t>US-224, US-195, US-062</t>
+        </is>
+      </c>
+      <c r="L133" s="9" t="inlineStr">
+        <is>
+          <t>PIL-05, PIL-09, MVP-08, MVP-09</t>
+        </is>
+      </c>
+      <c r="M133" s="9" t="inlineStr">
+        <is>
+          <t>Long multi-step goals as data</t>
+        </is>
+      </c>
+      <c r="N133" s="9" t="inlineStr">
+        <is>
+          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
+        </is>
+      </c>
+      <c r="O133" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="124.15" customHeight="1" s="20">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>US-226</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>The technology screen</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want a screen with what my clan knows, what is next and what each discovery unlocks, so that I can plan research.</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Tree
+Given a clan with some technologies
+When the player opens the screen
+Then known, reachable and locked technologies are shown as a tree
+Scenario: Detail
+Given a technology selected
+When it is shown
+Then its discovery rule, progress and unlocks are listed
+Scenario: Secrets
+Given a technology marked secret
+When it is shown
+Then who else is known to have it is listed</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H134" s="9">
+        <f>VLOOKUP(G134,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I134" s="9">
+        <f>VLOOKUP(G134,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="K134" s="9" t="inlineStr">
+        <is>
+          <t>US-220</t>
+        </is>
+      </c>
+      <c r="L134" s="9" t="inlineStr">
+        <is>
+          <t>PIL-09, PIL-07</t>
+        </is>
+      </c>
+      <c r="M134" s="9" t="inlineStr">
+        <is>
+          <t>Laying out a tree for reading</t>
+        </is>
+      </c>
+      <c r="N134" s="9" t="inlineStr">
+        <is>
+          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
+        </is>
+      </c>
+      <c r="O134" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="124.15" customHeight="1" s="20">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>US-230</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Luna's SDL_GPU renderer</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>As the developer, I want Luna to draw through SDL_GPU with shaders, keeping the old renderer as a fallback, so that lighting and shadows become possible without changing game code.</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Same picture
+Given the demo level and the camp
+When they are drawn with the GPU and the old renderer
+Then the screenshots match pixel for pixel at 1x lighting
+Scenario: Fallback
+Given a PC where SDL_GPU cannot start
+When the game starts
+Then it uses the old renderer, says so in the log and plays
+Scenario: Game code
+Given every draw call in src/game/
+When the switch is made
+Then no game file changed its drawing code</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H135" s="9">
+        <f>VLOOKUP(G135,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I135" s="9">
+        <f>VLOOKUP(G135,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>M8b</t>
+        </is>
+      </c>
+      <c r="K135" s="9" t="inlineStr">
+        <is>
+          <t>US-020, D-42</t>
+        </is>
+      </c>
+      <c r="L135" s="9" t="inlineStr">
+        <is>
+          <t>ARC-11, ADR-021, ADR-003</t>
+        </is>
+      </c>
+      <c r="M135" s="9" t="inlineStr">
+        <is>
+          <t>Graphics pipelines, shaders and sprite batching</t>
+        </is>
+      </c>
+      <c r="N135" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O135" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="124.15" customHeight="1" s="20">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>US-231</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>960x540 and window modes</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want the game at 960x540 that fills my screen crisply in a window or full screen, so that it looks sharp on any monitor.</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Scale
+Given a 1920x1080 and a 3840x2160 screen
+When the game runs full screen
+Then it scales by 2 and by 4 with no blur and no border
+Scenario: Modes
+Given the settings screen
+When the player picks windowed (with sizes), borderless or exclusive full screen
+Then the mode changes at once and is saved
+Scenario: Odd sizes
+Given a 2560x1440 screen
+When the game runs
+Then it scales by 2 with a thin border, or fills the screen smoothly if the player chooses Fill</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H136" s="9">
+        <f>VLOOKUP(G136,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I136" s="9">
+        <f>VLOOKUP(G136,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>M8b</t>
+        </is>
+      </c>
+      <c r="K136" s="9" t="inlineStr">
+        <is>
+          <t>US-230, US-081</t>
+        </is>
+      </c>
+      <c r="L136" s="9" t="inlineStr">
+        <is>
+          <t>ENV-18, US-081</t>
+        </is>
+      </c>
+      <c r="M136" s="9" t="inlineStr">
+        <is>
+          <t>Viewports and scaling maths</t>
+        </is>
+      </c>
+      <c r="N136" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O136" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="124.15" customHeight="1" s="20">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>US-232</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Camera zoom and UI scale</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want to zoom the world and size the interface, so that I can see more of the land or read more easily.</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Zoom
+Given the default camera zoom of 2x
+When the player zooms out
+Then the view shows 1x (30 x 17 tiles) and back, around the hero
+Scenario: UI
+Given UI scale 1x and 2x
+When the player switches
+Then panels, the font and the hotbar resize and stay crisp
+Scenario: Pointer
+Given any zoom
+When the player aims and clicks
+Then the pointer hits the same world spot as before</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H137" s="9">
+        <f>VLOOKUP(G137,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I137" s="9">
+        <f>VLOOKUP(G137,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>M8b</t>
+        </is>
+      </c>
+      <c r="K137" s="9" t="inlineStr">
+        <is>
+          <t>US-231</t>
+        </is>
+      </c>
+      <c r="L137" s="9" t="inlineStr">
+        <is>
+          <t>ENV-18</t>
+        </is>
+      </c>
+      <c r="M137" s="9" t="inlineStr">
+        <is>
+          <t>Two coordinate systems: world and screen</t>
+        </is>
+      </c>
+      <c r="N137" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O137" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="124.15" customHeight="1" s="20">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>US-233</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Every screen at the new size</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want every screen, panel and editor laid out for 960x540, so that nothing is cramped or out of place.</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Screens
+Given the HUD, hotbar, menus, the run screens, the dialogue panel and the Editor's tool bar, palettes and properties
+When they are opened at 960x540
+Then they use the space, nothing overlaps and the text is legible
+Scenario: Tests
+Given the screenshot tests
+When they run
+Then they pass with the new reference pictures, reviewed by the owner
+Scenario: Old saves
+Given a save and a level from before
+When they load
+Then they play the same</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H138" s="9">
+        <f>VLOOKUP(G138,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I138" s="9">
+        <f>VLOOKUP(G138,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>M8b</t>
+        </is>
+      </c>
+      <c r="K138" s="9" t="inlineStr">
+        <is>
+          <t>US-232</t>
+        </is>
+      </c>
+      <c r="L138" s="9" t="inlineStr">
+        <is>
+          <t>ENV-18, EDT-01</t>
+        </is>
+      </c>
+      <c r="M138" s="9" t="inlineStr">
+        <is>
+          <t>Layout from data instead of fixed numbers</t>
+        </is>
+      </c>
+      <c r="N138" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O138" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="124.15" customHeight="1" s="20">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>US-234</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>Frame budget at the new size</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want the game smooth at 960x540, so that the bigger picture costs nothing in feel.</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Budget
+Given 500 simulated people in the region on the minimum PC (D-06)
+When the game runs for 10 minutes
+Then it holds 60 FPS
+Scenario: Overlay
+Given F3
+When it is pressed
+Then the overlay shows CPU and GPU frame times
+Scenario: Record
+Given the performance run
+When it ends
+Then its numbers are saved in docs/evidence/</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H139" s="9">
+        <f>VLOOKUP(G139,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I139" s="9">
+        <f>VLOOKUP(G139,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>M8b</t>
+        </is>
+      </c>
+      <c r="K139" s="9" t="inlineStr">
+        <is>
+          <t>US-233, D-06</t>
+        </is>
+      </c>
+      <c r="L139" s="9" t="inlineStr">
+        <is>
+          <t>NFR-03, MVP success criteria</t>
+        </is>
+      </c>
+      <c r="M139" s="9" t="inlineStr">
+        <is>
+          <t>Measuring GPU and CPU time</t>
+        </is>
+      </c>
+      <c r="N139" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O139" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="124.15" customHeight="1" s="20">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>US-240</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>The lighting pipeline</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>As the developer, I want a lit pass with ambient light, point lights and normal maps in the GPU renderer, so that the world can be lit from data.</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Ambient
+Given an ambient colour in lights.json
+When the scene is drawn
+Then every sprite is tinted by it
+Scenario: Point light
+Given a light with a colour, radius and strength
+When it is placed near a sprite
+Then the sprite's lit side faces the light, using its normal map
+Scenario: Budget
+Given 64 lights on screen
+When the scene is drawn
+Then the frame budget of US-234 still holds</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H140" s="9">
+        <f>VLOOKUP(G140,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I140" s="9">
+        <f>VLOOKUP(G140,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="K140" s="9" t="inlineStr">
+        <is>
+          <t>US-230</t>
+        </is>
+      </c>
+      <c r="L140" s="9" t="inlineStr">
+        <is>
+          <t>ENV-19, ADR-021</t>
+        </is>
+      </c>
+      <c r="M140" s="9" t="inlineStr">
+        <is>
+          <t>Shader inputs, uniform data and lighting maths</t>
+        </is>
+      </c>
+      <c r="N140" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O140" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="124.15" customHeight="1" s="20">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>US-241</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>Generated normal maps</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want normal maps made from my sprites by a tool, so that lights shade my art without painting a second image.</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Generate
+Given the atlases
+When the atlas tool runs with normal maps on
+Then every atlas gets a matching normal-map atlas
+Scenario: Missing
+Given a sprite without a normal map
+When it is lit
+Then it is lit flat, with no error
+Scenario: Own map
+Given a hand-made normal map named like the sprite
+When the tool runs
+Then the hand-made one is kept</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H141" s="9">
+        <f>VLOOKUP(G141,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I141" s="9">
+        <f>VLOOKUP(G141,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J141" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="K141" s="9" t="inlineStr">
+        <is>
+          <t>US-240, US-120</t>
+        </is>
+      </c>
+      <c r="L141" s="9" t="inlineStr">
+        <is>
+          <t>ENV-19, D-05</t>
+        </is>
+      </c>
+      <c r="M141" s="9" t="inlineStr">
+        <is>
+          <t>Image processing: height and slopes from pixels</t>
+        </is>
+      </c>
+      <c r="N141" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O141" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="124.15" customHeight="1" s="20">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>US-242</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>Day, night and seasons</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want dawn, day, dusk and night to follow the game clock, with longer summer days and short winter days, so that time feels real.</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Cycle
+Given the game clock running
+When a day passes
+Then the light goes through dawn, day, dusk and night colours from sky.json
+Scenario: Seasons
+Given midsummer and midwinter
+When the days are compared
+Then the summer day is longer, as calendar.json says
+Scenario: Moon
+Given night
+When it is drawn
+Then the moon gives a dim, blue light and a direction for shadows</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H142" s="9">
+        <f>VLOOKUP(G142,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I142" s="9">
+        <f>VLOOKUP(G142,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="K142" s="9" t="inlineStr">
+        <is>
+          <t>US-240, US-010</t>
+        </is>
+      </c>
+      <c r="L142" s="9" t="inlineStr">
+        <is>
+          <t>ENV-19, ENV-20</t>
+        </is>
+      </c>
+      <c r="M142" s="9" t="inlineStr">
+        <is>
+          <t>Interpolating curves over time</t>
+        </is>
+      </c>
+      <c r="N142" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O142" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="124.15" customHeight="1" s="20">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>US-243</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>Fires, torches and glowing effects</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want fires, torches, the sacred fire and elemental effects to light the night with a flicker, so that camps glow in the dark.</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Fire
+Given a lit fire pit at night
+When the scene is drawn
+Then it lights a circle around it with a flicker
+Scenario: Data
+Given a catalog entry with a light field
+When the thing is placed
+Then it emits that light; without the field, none
+Scenario: Torch
+Given a clan member carrying a torch
+When they walk at night
+Then the light moves with them</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H143" s="9">
+        <f>VLOOKUP(G143,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I143" s="9">
+        <f>VLOOKUP(G143,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J143" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="K143" s="9" t="inlineStr">
+        <is>
+          <t>US-240, US-132</t>
+        </is>
+      </c>
+      <c r="L143" s="9" t="inlineStr">
+        <is>
+          <t>ENV-19</t>
+        </is>
+      </c>
+      <c r="M143" s="9" t="inlineStr">
+        <is>
+          <t>Noise for natural flicker</t>
+        </is>
+      </c>
+      <c r="N143" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O143" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="124.15" customHeight="1" s="20">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>US-244</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Sun and moon shadows</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want characters, plants and buildings to cast shadows that turn and stretch with the sun and the moon, so that the world has depth.</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Day
+Given a tree at 9:00 and at 17:00
+When it is drawn
+Then its shadow points away from the sun and is longer in the morning and evening
+Scenario: Casters
+Given characters, plants and buildings
+When the sun shines
+Then each casts a shadow sized by its height in the catalog
+Scenario: Overcast
+Given fog or heavy cloud
+When it sets in
+Then the shadows fade</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H144" s="9">
+        <f>VLOOKUP(G144,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I144" s="9">
+        <f>VLOOKUP(G144,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="K144" s="9" t="inlineStr">
+        <is>
+          <t>US-242</t>
+        </is>
+      </c>
+      <c r="L144" s="9" t="inlineStr">
+        <is>
+          <t>ENV-21</t>
+        </is>
+      </c>
+      <c r="M144" s="9" t="inlineStr">
+        <is>
+          <t>Projecting silhouettes with a shear transform</t>
+        </is>
+      </c>
+      <c r="N144" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O144" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="124.15" customHeight="1" s="20">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>US-245</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>Shadows from fires</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want a fire to throw shadows of the people and things near it at night, so that night scenes feel alive.</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Fire shadow
+Given a person standing near a fire at night
+When it is drawn
+Then their shadow points away from the fire
+Scenario: Two fires
+Given a person between two fires
+When it is drawn
+Then they cast two faint shadows
+Scenario: Budget
+Given many fires
+When the scene is drawn
+Then only the nearest fires (from lights.json) cast shadows and the frame budget holds</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H145" s="9">
+        <f>VLOOKUP(G145,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I145" s="9">
+        <f>VLOOKUP(G145,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>US-244, US-243</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
+        <is>
+          <t>ENV-21</t>
+        </is>
+      </c>
+      <c r="M145" s="9" t="inlineStr">
+        <is>
+          <t>Choosing the nearest lights per object within a budget</t>
+        </is>
+      </c>
+      <c r="N145" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O145" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="124.15" customHeight="1" s="20">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>US-246</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>Weather and light</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want clouds, rain, fog and storms to darken and tint the world, with lightning flashes, so that weather changes the mood.</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Dim
+Given rain starting at noon
+When it fades in
+Then the light dims and cools over the same 3 s
+Scenario: Lightning
+Given a storm
+When lightning strikes
+Then the whole scene flashes for a moment
+Scenario: Data
+Given weather.json
+When the owner sets a weather's light
+Then the game uses it</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H146" s="9">
+        <f>VLOOKUP(G146,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I146" s="9">
+        <f>VLOOKUP(G146,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="K146" s="9" t="inlineStr">
+        <is>
+          <t>US-242, US-138</t>
+        </is>
+      </c>
+      <c r="L146" s="9" t="inlineStr">
+        <is>
+          <t>ENV-19</t>
+        </is>
+      </c>
+      <c r="M146" s="9" t="inlineStr">
+        <is>
+          <t>Blending light settings</t>
+        </is>
+      </c>
+      <c r="N146" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O146" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="124.15" customHeight="1" s="20">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>US-247</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Lighting in the Editor and quality settings</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to preview any time of day and place lights in the Editor, and players to choose lighting quality, so that levels look right and run everywhere.</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Preview
+Given the Editor
+When the owner drags the time-of-day slider
+Then the level is lit as at that hour
+Scenario: Place
+Given the light tool
+When the owner places a light and sets it
+Then it is saved in the level and shines in the game
+Scenario: Quality
+Given Low, Medium and High lighting
+When the player picks Low
+Then fire shadows and normal maps switch off and the frame time drops</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H147" s="9">
+        <f>VLOOKUP(G147,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I147" s="9">
+        <f>VLOOKUP(G147,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>M8c</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>US-243, US-244</t>
+        </is>
+      </c>
+      <c r="L147" s="9" t="inlineStr">
+        <is>
+          <t>ENV-19, EDT-01</t>
+        </is>
+      </c>
+      <c r="M147" s="9" t="inlineStr">
+        <is>
+          <t>Settings that change a pipeline</t>
+        </is>
+      </c>
+      <c r="N147" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O147" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="124.15" customHeight="1" s="20">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>US-250</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>Building pieces and building kinds as data</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want building pieces (walls, floors, roofs, doors, posts) and building kinds (layout, materials, build time, interior mode, uses) in data files, so that I can design buildings without code.</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Load
+Given pieces.json and buildings.json with a hut, a windbreak, a storage pit, a drying rack and a palisade
+When the game starts
+Then every kind and piece is known, with errors naming file, line and field
+Scenario: Own list
+Given buildings in a level
+When it is saved and loaded
+Then they are kept in their own list, not as plants (CI-008)
+Scenario: Uses
+Given a hut with shelter and sleep, a storage pit with storage
+When the data loads
+Then their interactions are offered</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H148" s="9">
+        <f>VLOOKUP(G148,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I148" s="9">
+        <f>VLOOKUP(G148,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>M8d</t>
+        </is>
+      </c>
+      <c r="K148" s="9" t="inlineStr">
+        <is>
+          <t>US-150, US-155</t>
+        </is>
+      </c>
+      <c r="L148" s="9" t="inlineStr">
+        <is>
+          <t>INT-07, EDT-07, ARC-08</t>
+        </is>
+      </c>
+      <c r="M148" s="9" t="inlineStr">
+        <is>
+          <t>Composite data: a whole made of parts</t>
+        </is>
+      </c>
+      <c r="N148" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O148" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="124.15" customHeight="1" s="20">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>US-251</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>Building from blueprints</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want to choose a building, place its blueprint, bring materials and build it over time, so that I can shape my camp.</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Place
+Given known blueprints
+When the player picks a hut and places it
+Then a see-through blueprint shows, red where it cannot stand
+Scenario: Build
+Given a placed blueprint
+When materials are brought and the hero works on it
+Then it rises in stages and is finished after its build time
+Scenario: Cancel
+Given a blueprint under way
+When the player cancels it
+Then the delivered materials are dropped on the site</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H149" s="9">
+        <f>VLOOKUP(G149,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I149" s="9">
+        <f>VLOOKUP(G149,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>M8d</t>
+        </is>
+      </c>
+      <c r="K149" s="9" t="inlineStr">
+        <is>
+          <t>US-250, US-153</t>
+        </is>
+      </c>
+      <c r="L149" s="9" t="inlineStr">
+        <is>
+          <t>INT-07</t>
+        </is>
+      </c>
+      <c r="M149" s="9" t="inlineStr">
+        <is>
+          <t>Placement validity on a grid</t>
+        </is>
+      </c>
+      <c r="N149" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O149" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="124.15" customHeight="1" s="20">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>US-252</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>Building piece by piece</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want to place walls, floors, roofs and doors one by one, so that I can build any shape.</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Pieces
+Given the build menu's pieces
+When the player places walls in a ring, a door and a roof
+Then each piece is built like a small blueprint
+Scenario: Room
+Given an enclosed, roofed space with a door
+When it is finished
+Then it counts as a room: warm, sheltered, with its own light
+Scenario: Paths
+Given a door
+When people walk to the room
+Then they go through the door, never through walls</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H150" s="9">
+        <f>VLOOKUP(G150,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I150" s="9">
+        <f>VLOOKUP(G150,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>M8d</t>
+        </is>
+      </c>
+      <c r="K150" s="9" t="inlineStr">
+        <is>
+          <t>US-251</t>
+        </is>
+      </c>
+      <c r="L150" s="9" t="inlineStr">
+        <is>
+          <t>INT-07</t>
+        </is>
+      </c>
+      <c r="M150" s="9" t="inlineStr">
+        <is>
+          <t>Flood fill to find enclosed rooms</t>
+        </is>
+      </c>
+      <c r="N150" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O150" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="124.15" customHeight="1" s="20">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>US-253</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>Clans build together</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want my clan members to help build and rival clans to grow their own camps, so that building is a shared life.</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Help
+Given a blueprint and idle clan members
+When time passes
+Then they bring materials and build, through the interaction system
+Scenario: Rivals
+Given a rival camp
+When a season passes
+Then it has built at least one building from its own blueprints
+Scenario: Deterministic
+Given the same seed and inputs
+When two runs
+Then the same buildings stand in the same places</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H151" s="9">
+        <f>VLOOKUP(G151,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I151" s="9">
+        <f>VLOOKUP(G151,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>M8e</t>
+        </is>
+      </c>
+      <c r="K151" s="9" t="inlineStr">
+        <is>
+          <t>US-251, US-154</t>
+        </is>
+      </c>
+      <c r="L151" s="9" t="inlineStr">
+        <is>
+          <t>INT-07, INT-05</t>
+        </is>
+      </c>
+      <c r="M151" s="9" t="inlineStr">
+        <is>
+          <t>Job queues for many workers</t>
+        </is>
+      </c>
+      <c r="N151" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O151" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="124.15" customHeight="1" s="20">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>US-254</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>Interiors: roof fade or interior map</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want to see inside buildings, either by the roof fading or by entering an interior, as the building says, so that houses are places to be.</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Fade
+Given a hut set to roof fade
+When the hero walks in
+Then the roof and the front walls fade and the inside shows, lit by its fire and door
+Scenario: Interior
+Given a lodge set to interior map
+When the hero uses its door
+Then the interior level loads and its door leads back outside
+Scenario: Setting
+Given a placed building
+When the owner switches its interior mode in the Editor
+Then the game follows it</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H152" s="9">
+        <f>VLOOKUP(G152,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I152" s="9">
+        <f>VLOOKUP(G152,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J152" s="9" t="inlineStr">
+        <is>
+          <t>M8e</t>
+        </is>
+      </c>
+      <c r="K152" s="9" t="inlineStr">
+        <is>
+          <t>US-252, US-122</t>
+        </is>
+      </c>
+      <c r="L152" s="9" t="inlineStr">
+        <is>
+          <t>ENV-20, EDT-07</t>
+        </is>
+      </c>
+      <c r="M152" s="9" t="inlineStr">
+        <is>
+          <t>Linking two maps by doors</t>
+        </is>
+      </c>
+      <c r="N152" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O152" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="124.15" customHeight="1" s="20">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>US-255</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Wear, repair, damage and fire</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want buildings to wear with weather, to be repaired, damaged and to burn, so that they need care.</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Wear
+Given a hut through a winter
+When the season passes
+Then its condition falls as the data says and Repair is offered
+Scenario: Fire
+Given a burning torch dropped by a wooden wall
+When time passes
+Then the wall catches fire, it spreads to wooden neighbours by their materials and ends in rubble
+Scenario: Damage
+Given an attack on a wall
+When it is hit
+Then the wall loses condition and falls at zero</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H153" s="9">
+        <f>VLOOKUP(G153,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I153" s="9">
+        <f>VLOOKUP(G153,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>M8e</t>
+        </is>
+      </c>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>US-251, US-029</t>
+        </is>
+      </c>
+      <c r="L153" s="9" t="inlineStr">
+        <is>
+          <t>INT-08, PHY-04</t>
+        </is>
+      </c>
+      <c r="M153" s="9" t="inlineStr">
+        <is>
+          <t>Spreading state across neighbours (cellular rules)</t>
+        </is>
+      </c>
+      <c r="N153" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O153" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="124.15" customHeight="1" s="20">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>US-256</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Prefab editor and placing buildings</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>As the owner, I want to compose buildings from pieces in the Editor, save them as prefabs with costs and interior mode, and place them whole, so that levels start with real camps.</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Compose
+Given the Prefab tab
+When the owner places pieces, sets materials, build time and interior mode, and saves
+Then a prefab file is written and appears in the palette
+Scenario: Place
+Given a prefab
+When the owner places it in a level
+Then the finished building stands there in the game
+Scenario: Blueprint
+Given a prefab marked buildable
+When a game starts
+Then the player can build it from the build menu</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H154" s="9">
+        <f>VLOOKUP(G154,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I154" s="9">
+        <f>VLOOKUP(G154,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>M8d</t>
+        </is>
+      </c>
+      <c r="K154" s="9" t="inlineStr">
+        <is>
+          <t>US-252, US-124</t>
+        </is>
+      </c>
+      <c r="L154" s="9" t="inlineStr">
+        <is>
+          <t>EDT-07</t>
+        </is>
+      </c>
+      <c r="M154" s="9" t="inlineStr">
+        <is>
+          <t>Saving a group of parts as one reusable asset</t>
+        </is>
+      </c>
+      <c r="N154" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O154" s="16" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="124.15" customHeight="1" s="20">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>US-257</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Buildings in the clan's life</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>As the player, I want buildings to matter to the clan: shelter and warmth, sleeping, storage and ownership, saved with the world, so that building changes how people live.</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>Scenario: Warmth
+Given a cold night
+When clan members sleep in a hut
+Then their Warmth need falls slower than outside
+Scenario: Storage
+Given a storage pit
+When food is put in
+Then it counts in the clan store and spoils slower
+Scenario: Saved
+Given buildings with owners, condition and contents
+When the game saves and loads
+Then everything is kept</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H155" s="9">
+        <f>VLOOKUP(G155,'Read Me'!$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I155" s="9">
+        <f>VLOOKUP(G155,'Read Me'!$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J155" s="9" t="inlineStr">
+        <is>
+          <t>M8e</t>
+        </is>
+      </c>
+      <c r="K155" s="9" t="inlineStr">
+        <is>
+          <t>US-253, US-011</t>
+        </is>
+      </c>
+      <c r="L155" s="9" t="inlineStr">
+        <is>
+          <t>INT-07, SDC-02</t>
+        </is>
+      </c>
+      <c r="M155" s="9" t="inlineStr">
+        <is>
+          <t>Linking world objects to simulation needs</t>
+        </is>
+      </c>
+      <c r="N155" s="9" t="inlineStr">
+        <is>
+          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
+        </is>
+      </c>
+      <c r="O155" s="16" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -12666,7 +19282,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -12704,7 +19319,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Ages 2-10, Mythic Strands, Phase 2 space</t>
+          <t>Ages 2-10, Mythic Strands 2-10, Phase 2 space</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -12738,17 +19353,17 @@
     <row r="8" ht="25.5" customHeight="1" s="20">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Military, Politics, Technology, Ideology pillars</t>
+          <t>Military, Ideology pillars</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Two pillars are enough to test 'many paths to dominance'; combat is the most expensive system.</t>
+          <t>Four pillars (Trade, Religion, Politics, Technology) are enough to test 'many paths to dominance'; combat as a pillar is the most expensive system. Politics (D-40) and Technology (D-41) returned to the MVP on 2026-10-01.</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Next (Politics), Later (others)</t>
+          <t>Later</t>
         </is>
       </c>
     </row>
@@ -12845,7 +19460,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Age 1 needs hit detection, ballistics, basic bodies and material properties only; the rest belongs to later Ages.</t>
+          <t>Age 1 needs hit detection, ballistics, basic bodies and material properties only; the rest belongs to later Ages. Exception (D-42): fire spreading between building pieces is in the MVP.</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -12885,7 +19500,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -12921,7 +19535,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>

--- a/docs/project/requirements/Project Odyssey - MVP Backlog - Copy.xlsx
+++ b/docs/project/requirements/Project Odyssey - MVP Backlog - Copy.xlsx
@@ -654,10 +654,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Working tracker for developers. The source of truth is Project Odyssey.docx v2.4, chapter 12; this workbook is generated from the same data. Updated 2026-10-01: M8d split into M8d and M8e (D-43); D-06 decided.</t>
-        </is>
-      </c>
-    </row>
+          <t>Working tracker for developers. The source of truth is Project Odyssey.docx v2.0, chapter 12; this workbook is generated from the same data. Updated 2026-10-01: M7-M9 added (D-34); statuses of built stories set to Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="15.75" customHeight="1" s="20">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -700,6 +701,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="15.75" customHeight="1" s="20">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -794,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -818,6 +820,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15.75" customHeight="1" s="20">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -832,6 +835,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="15.75" customHeight="1" s="20">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -1068,17 +1072,17 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Four pillars playable at region scale: Trade, Religion, Politics (D-40) and Technology (tech tree, research, workshops, espionage, the Ember Strand; D-41). Military and Ideology are shown as locked 'later Ages'.</t>
+          <t>Two pillars playable at region scale: Trade (barter and debts) and Religion (sacred fire and followers). The other four are shown as locked 'later Ages'.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Proposed</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>PIL-02, PIL-03, PIL-04, PIL-05, PIL-08, PIL-09, ENV-10</t>
+          <t>PIL-02, PIL-04, ENV-10</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1099,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Win: Dominion 60% in Trade, Religion or Politics; or the Ember Strand held with a 60% Technology share; or the four pillars averaging 50% (values in Game Rules). Lose: your hero dies before the Mantle moment, or your clan disbands.</t>
+          <t>Win: your clan leads the region (Dominion 60% in Trade or Religion, or 50% combined). Lose: your hero dies before the Mantle moment, or your clan disbands.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1149,7 +1153,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Layered 32 x 48 sprites with 3 outfits per body; programmer or placeholder art allowed; minimal sound effects. From M8b: 960x540 on the SDL_GPU renderer with global lighting and shadows (D-42).</t>
+          <t>Layered 32 x 48 sprites with 3 outfits per body; programmer or placeholder art allowed; minimal sound effects.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1244,239 +1248,185 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="38.25" customHeight="1" s="20">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>MVP-15</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Authoring</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>The Editor is the authoring tool for quests, story events, entities, mechanics, game rules, routines and the region with its clans and people; every result is a readable file (D-40, 2026-10-01).</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Decided</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>EDT-01..EDT-06, STO-04, STO-05, SDC-07, ADR-020</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="38.25" customHeight="1" s="20">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>MVP-16</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Buildings and light</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>960x540 on the GPU renderer; day, night, seasons and weather lighting; fire light; shadows from the sun, the moon and nearby fires; buildings from blueprints and pieces, built by the hero and the clans, with wear, repair, fire, interiors and Editor prefabs (D-42).</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Decided</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>ENV-18..ENV-21, ARC-11, INT-07, INT-08, EDT-07, ADR-021</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="51" customHeight="1" s="20"/>
+    <row r="23" ht="15.75" customHeight="1" s="20"/>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Success and kill criteria (decided before building)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1" s="20">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>How measured</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="63.75" customHeight="1" s="20">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Success and kill criteria (decided before building)</t>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Voluntary play time</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>5 of 8 playtesters play 30+ minutes without being asked to continue</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Observation + local session log (US-092)</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>M6</t>
         </is>
       </c>
     </row>
     <row r="27" ht="38.25" customHeight="1" s="20">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>How measured</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Gate</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Emergent story</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>3 of 8 can retell a story that came from the simulation, not from a script</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Post-play interview</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>M6</t>
         </is>
       </c>
     </row>
     <row r="28" ht="63.75" customHeight="1" s="20">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Voluntary play time</t>
+          <t>Chronicle interest (early)</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>5 of 8 playtesters play 30+ minutes without being asked to continue</t>
+          <t>2 of 3 readers find a story in the console chronicle</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Observation + local session log (US-092)</t>
+          <t>Show printed chronicle (M2: 3 readers, failed 2026-09-30; M2b retry: the owner reads and judges)</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M2, retried at M2b</t>
         </is>
       </c>
     </row>
     <row r="29" ht="51" customHeight="1" s="20">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Emergent story</t>
+          <t>Frame rate</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>3 of 8 can retell a story that came from the simulation, not from a script</t>
+          <t>60 FPS with 500 simulated agents in the region on the minimum PC (OPEN-19)</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Post-play interview</t>
+          <t>FPS overlay (US-082)</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M5</t>
         </is>
       </c>
     </row>
     <row r="30" ht="51" customHeight="1" s="20">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Chronicle interest (early)</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2 of 3 readers find a story in the console chronicle</t>
+          <t>Same seed + inputs give the same world hash after 10,000 ticks</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Show printed chronicle (M2: 3 readers, failed 2026-09-30; M2b retry: the owner reads and judges)</t>
+          <t>Automated test in CI</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>M2, retried at M2b</t>
+          <t>M2 onwards</t>
         </is>
       </c>
     </row>
     <row r="31" ht="63.75" customHeight="1" s="20">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Frame rate</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>60 FPS with 500 simulated agents in the region on the minimum PC (OPEN-19)</t>
+          <t>No crash in a 2-hour play session or a 100-year soak test</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>FPS overlay (US-082)</t>
+          <t>Soak test + crash log</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M5, M6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Kill / pivot rule</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Same seed + inputs give the same world hash after 10,000 ticks</t>
+          <t>If M2 or M6 fails: stop adding content; redesign the simulation or the loop first</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Automated test in CI</t>
+          <t>Owner decision, recorded</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>M2 onwards</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>No crash in a 2-hour play session or a 100-year soak test</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Soak test + crash log</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>M5, M6</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Kill / pivot rule</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>If M2 or M6 fails: stop adding content; redesign the simulation or the loop first</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Owner decision, recorded</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>M2, M6</t>
         </is>
@@ -1504,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JO36"/>
+  <dimension ref="A1:EY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="20" min="1" max="1"/>
@@ -1579,126 +1529,6 @@
     <col width="13" customWidth="1" style="20" min="153" max="153"/>
     <col width="13" customWidth="1" style="20" min="154" max="154"/>
     <col width="13" customWidth="1" style="20" min="155" max="155"/>
-    <col width="13" customWidth="1" style="20" min="156" max="156"/>
-    <col width="13" customWidth="1" style="20" min="157" max="157"/>
-    <col width="13" customWidth="1" style="20" min="158" max="158"/>
-    <col width="13" customWidth="1" style="20" min="159" max="159"/>
-    <col width="13" customWidth="1" style="20" min="160" max="160"/>
-    <col width="13" customWidth="1" style="20" min="161" max="161"/>
-    <col width="13" customWidth="1" style="20" min="162" max="162"/>
-    <col width="13" customWidth="1" style="20" min="163" max="163"/>
-    <col width="13" customWidth="1" style="20" min="164" max="164"/>
-    <col width="13" customWidth="1" style="20" min="165" max="165"/>
-    <col width="13" customWidth="1" style="20" min="166" max="166"/>
-    <col width="13" customWidth="1" style="20" min="167" max="167"/>
-    <col width="13" customWidth="1" style="20" min="168" max="168"/>
-    <col width="13" customWidth="1" style="20" min="169" max="169"/>
-    <col width="13" customWidth="1" style="20" min="170" max="170"/>
-    <col width="13" customWidth="1" style="20" min="171" max="171"/>
-    <col width="13" customWidth="1" style="20" min="172" max="172"/>
-    <col width="13" customWidth="1" style="20" min="173" max="173"/>
-    <col width="13" customWidth="1" style="20" min="174" max="174"/>
-    <col width="13" customWidth="1" style="20" min="175" max="175"/>
-    <col width="13" customWidth="1" style="20" min="176" max="176"/>
-    <col width="13" customWidth="1" style="20" min="177" max="177"/>
-    <col width="13" customWidth="1" style="20" min="178" max="178"/>
-    <col width="13" customWidth="1" style="20" min="179" max="179"/>
-    <col width="13" customWidth="1" style="20" min="180" max="180"/>
-    <col width="13" customWidth="1" style="20" min="181" max="181"/>
-    <col width="13" customWidth="1" style="20" min="182" max="182"/>
-    <col width="13" customWidth="1" style="20" min="183" max="183"/>
-    <col width="13" customWidth="1" style="20" min="184" max="184"/>
-    <col width="13" customWidth="1" style="20" min="185" max="185"/>
-    <col width="13" customWidth="1" style="20" min="186" max="186"/>
-    <col width="13" customWidth="1" style="20" min="187" max="187"/>
-    <col width="13" customWidth="1" style="20" min="188" max="188"/>
-    <col width="13" customWidth="1" style="20" min="189" max="189"/>
-    <col width="13" customWidth="1" style="20" min="190" max="190"/>
-    <col width="13" customWidth="1" style="20" min="191" max="191"/>
-    <col width="13" customWidth="1" style="20" min="192" max="192"/>
-    <col width="13" customWidth="1" style="20" min="193" max="193"/>
-    <col width="13" customWidth="1" style="20" min="194" max="194"/>
-    <col width="13" customWidth="1" style="20" min="195" max="195"/>
-    <col width="13" customWidth="1" style="20" min="196" max="196"/>
-    <col width="13" customWidth="1" style="20" min="197" max="197"/>
-    <col width="13" customWidth="1" style="20" min="198" max="198"/>
-    <col width="13" customWidth="1" style="20" min="199" max="199"/>
-    <col width="13" customWidth="1" style="20" min="200" max="200"/>
-    <col width="13" customWidth="1" style="20" min="201" max="201"/>
-    <col width="13" customWidth="1" style="20" min="202" max="202"/>
-    <col width="13" customWidth="1" style="20" min="203" max="203"/>
-    <col width="13" customWidth="1" style="20" min="204" max="204"/>
-    <col width="13" customWidth="1" style="20" min="205" max="205"/>
-    <col width="13" customWidth="1" style="20" min="206" max="206"/>
-    <col width="13" customWidth="1" style="20" min="207" max="207"/>
-    <col width="13" customWidth="1" style="20" min="208" max="208"/>
-    <col width="13" customWidth="1" style="20" min="209" max="209"/>
-    <col width="13" customWidth="1" style="20" min="210" max="210"/>
-    <col width="13" customWidth="1" style="20" min="211" max="211"/>
-    <col width="13" customWidth="1" style="20" min="212" max="212"/>
-    <col width="13" customWidth="1" style="20" min="213" max="213"/>
-    <col width="13" customWidth="1" style="20" min="214" max="214"/>
-    <col width="13" customWidth="1" style="20" min="215" max="215"/>
-    <col width="13" customWidth="1" style="20" min="216" max="216"/>
-    <col width="13" customWidth="1" style="20" min="217" max="217"/>
-    <col width="13" customWidth="1" style="20" min="218" max="218"/>
-    <col width="13" customWidth="1" style="20" min="219" max="219"/>
-    <col width="13" customWidth="1" style="20" min="220" max="220"/>
-    <col width="13" customWidth="1" style="20" min="221" max="221"/>
-    <col width="13" customWidth="1" style="20" min="222" max="222"/>
-    <col width="13" customWidth="1" style="20" min="223" max="223"/>
-    <col width="13" customWidth="1" style="20" min="224" max="224"/>
-    <col width="13" customWidth="1" style="20" min="225" max="225"/>
-    <col width="13" customWidth="1" style="20" min="226" max="226"/>
-    <col width="13" customWidth="1" style="20" min="227" max="227"/>
-    <col width="13" customWidth="1" style="20" min="228" max="228"/>
-    <col width="13" customWidth="1" style="20" min="229" max="229"/>
-    <col width="13" customWidth="1" style="20" min="230" max="230"/>
-    <col width="13" customWidth="1" style="20" min="231" max="231"/>
-    <col width="13" customWidth="1" style="20" min="232" max="232"/>
-    <col width="13" customWidth="1" style="20" min="233" max="233"/>
-    <col width="13" customWidth="1" style="20" min="234" max="234"/>
-    <col width="13" customWidth="1" style="20" min="235" max="235"/>
-    <col width="13" customWidth="1" style="20" min="236" max="236"/>
-    <col width="13" customWidth="1" style="20" min="237" max="237"/>
-    <col width="13" customWidth="1" style="20" min="238" max="238"/>
-    <col width="13" customWidth="1" style="20" min="239" max="239"/>
-    <col width="13" customWidth="1" style="20" min="240" max="240"/>
-    <col width="13" customWidth="1" style="20" min="241" max="241"/>
-    <col width="13" customWidth="1" style="20" min="242" max="242"/>
-    <col width="13" customWidth="1" style="20" min="243" max="243"/>
-    <col width="13" customWidth="1" style="20" min="244" max="244"/>
-    <col width="13" customWidth="1" style="20" min="245" max="245"/>
-    <col width="13" customWidth="1" style="20" min="246" max="246"/>
-    <col width="13" customWidth="1" style="20" min="247" max="247"/>
-    <col width="13" customWidth="1" style="20" min="248" max="248"/>
-    <col width="13" customWidth="1" style="20" min="249" max="249"/>
-    <col width="13" customWidth="1" style="20" min="250" max="250"/>
-    <col width="13" customWidth="1" style="20" min="251" max="251"/>
-    <col width="13" customWidth="1" style="20" min="252" max="252"/>
-    <col width="13" customWidth="1" style="20" min="253" max="253"/>
-    <col width="13" customWidth="1" style="20" min="254" max="254"/>
-    <col width="13" customWidth="1" style="20" min="255" max="255"/>
-    <col width="13" customWidth="1" style="20" min="256" max="256"/>
-    <col width="13" customWidth="1" style="20" min="257" max="257"/>
-    <col width="13" customWidth="1" style="20" min="258" max="258"/>
-    <col width="13" customWidth="1" style="20" min="259" max="259"/>
-    <col width="13" customWidth="1" style="20" min="260" max="260"/>
-    <col width="13" customWidth="1" style="20" min="261" max="261"/>
-    <col width="13" customWidth="1" style="20" min="262" max="262"/>
-    <col width="13" customWidth="1" style="20" min="263" max="263"/>
-    <col width="13" customWidth="1" style="20" min="264" max="264"/>
-    <col width="13" customWidth="1" style="20" min="265" max="265"/>
-    <col width="13" customWidth="1" style="20" min="266" max="266"/>
-    <col width="13" customWidth="1" style="20" min="267" max="267"/>
-    <col width="13" customWidth="1" style="20" min="268" max="268"/>
-    <col width="13" customWidth="1" style="20" min="269" max="269"/>
-    <col width="13" customWidth="1" style="20" min="270" max="270"/>
-    <col width="13" customWidth="1" style="20" min="271" max="271"/>
-    <col width="13" customWidth="1" style="20" min="272" max="272"/>
-    <col width="13" customWidth="1" style="20" min="273" max="273"/>
-    <col width="13" customWidth="1" style="20" min="274" max="274"/>
-    <col width="13" customWidth="1" style="20" min="275" max="275"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="20">
@@ -1715,6 +1545,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1725,6 +1556,7 @@
         <v>46300</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="38.25" customHeight="1" s="20">
       <c r="A6" s="6" t="inlineStr">
         <is>
@@ -2216,366 +2048,6 @@
       <c r="EY6" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="EZ6" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="FA6" s="12" t="n">
-        <v>142</v>
-      </c>
-      <c r="FB6" s="12" t="n">
-        <v>143</v>
-      </c>
-      <c r="FC6" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="FD6" s="12" t="n">
-        <v>145</v>
-      </c>
-      <c r="FE6" s="12" t="n">
-        <v>146</v>
-      </c>
-      <c r="FF6" s="12" t="n">
-        <v>147</v>
-      </c>
-      <c r="FG6" s="12" t="n">
-        <v>148</v>
-      </c>
-      <c r="FH6" s="12" t="n">
-        <v>149</v>
-      </c>
-      <c r="FI6" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="FJ6" s="12" t="n">
-        <v>151</v>
-      </c>
-      <c r="FK6" s="12" t="n">
-        <v>152</v>
-      </c>
-      <c r="FL6" s="12" t="n">
-        <v>153</v>
-      </c>
-      <c r="FM6" s="12" t="n">
-        <v>154</v>
-      </c>
-      <c r="FN6" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="FO6" s="12" t="n">
-        <v>156</v>
-      </c>
-      <c r="FP6" s="12" t="n">
-        <v>157</v>
-      </c>
-      <c r="FQ6" s="12" t="n">
-        <v>158</v>
-      </c>
-      <c r="FR6" s="12" t="n">
-        <v>159</v>
-      </c>
-      <c r="FS6" s="12" t="n">
-        <v>160</v>
-      </c>
-      <c r="FT6" s="12" t="n">
-        <v>161</v>
-      </c>
-      <c r="FU6" s="12" t="n">
-        <v>162</v>
-      </c>
-      <c r="FV6" s="12" t="n">
-        <v>163</v>
-      </c>
-      <c r="FW6" s="12" t="n">
-        <v>164</v>
-      </c>
-      <c r="FX6" s="12" t="n">
-        <v>165</v>
-      </c>
-      <c r="FY6" s="12" t="n">
-        <v>166</v>
-      </c>
-      <c r="FZ6" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="GA6" s="12" t="n">
-        <v>168</v>
-      </c>
-      <c r="GB6" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="GC6" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="GD6" s="12" t="n">
-        <v>171</v>
-      </c>
-      <c r="GE6" s="12" t="n">
-        <v>172</v>
-      </c>
-      <c r="GF6" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="GG6" s="12" t="n">
-        <v>174</v>
-      </c>
-      <c r="GH6" s="12" t="n">
-        <v>175</v>
-      </c>
-      <c r="GI6" s="12" t="n">
-        <v>176</v>
-      </c>
-      <c r="GJ6" s="12" t="n">
-        <v>177</v>
-      </c>
-      <c r="GK6" s="12" t="n">
-        <v>178</v>
-      </c>
-      <c r="GL6" s="12" t="n">
-        <v>179</v>
-      </c>
-      <c r="GM6" s="12" t="n">
-        <v>180</v>
-      </c>
-      <c r="GN6" s="12" t="n">
-        <v>181</v>
-      </c>
-      <c r="GO6" s="12" t="n">
-        <v>182</v>
-      </c>
-      <c r="GP6" s="12" t="n">
-        <v>183</v>
-      </c>
-      <c r="GQ6" s="12" t="n">
-        <v>184</v>
-      </c>
-      <c r="GR6" s="12" t="n">
-        <v>185</v>
-      </c>
-      <c r="GS6" s="12" t="n">
-        <v>186</v>
-      </c>
-      <c r="GT6" s="12" t="n">
-        <v>187</v>
-      </c>
-      <c r="GU6" s="12" t="n">
-        <v>188</v>
-      </c>
-      <c r="GV6" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="GW6" s="12" t="n">
-        <v>190</v>
-      </c>
-      <c r="GX6" s="12" t="n">
-        <v>191</v>
-      </c>
-      <c r="GY6" s="12" t="n">
-        <v>192</v>
-      </c>
-      <c r="GZ6" s="12" t="n">
-        <v>193</v>
-      </c>
-      <c r="HA6" s="12" t="n">
-        <v>194</v>
-      </c>
-      <c r="HB6" s="12" t="n">
-        <v>195</v>
-      </c>
-      <c r="HC6" s="12" t="n">
-        <v>196</v>
-      </c>
-      <c r="HD6" s="12" t="n">
-        <v>197</v>
-      </c>
-      <c r="HE6" s="12" t="n">
-        <v>198</v>
-      </c>
-      <c r="HF6" s="12" t="n">
-        <v>199</v>
-      </c>
-      <c r="HG6" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="HH6" s="12" t="n">
-        <v>201</v>
-      </c>
-      <c r="HI6" s="12" t="n">
-        <v>202</v>
-      </c>
-      <c r="HJ6" s="12" t="n">
-        <v>203</v>
-      </c>
-      <c r="HK6" s="12" t="n">
-        <v>204</v>
-      </c>
-      <c r="HL6" s="12" t="n">
-        <v>205</v>
-      </c>
-      <c r="HM6" s="12" t="n">
-        <v>206</v>
-      </c>
-      <c r="HN6" s="12" t="n">
-        <v>207</v>
-      </c>
-      <c r="HO6" s="12" t="n">
-        <v>208</v>
-      </c>
-      <c r="HP6" s="12" t="n">
-        <v>209</v>
-      </c>
-      <c r="HQ6" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="HR6" s="12" t="n">
-        <v>211</v>
-      </c>
-      <c r="HS6" s="12" t="n">
-        <v>212</v>
-      </c>
-      <c r="HT6" s="12" t="n">
-        <v>213</v>
-      </c>
-      <c r="HU6" s="12" t="n">
-        <v>214</v>
-      </c>
-      <c r="HV6" s="12" t="n">
-        <v>215</v>
-      </c>
-      <c r="HW6" s="12" t="n">
-        <v>216</v>
-      </c>
-      <c r="HX6" s="12" t="n">
-        <v>217</v>
-      </c>
-      <c r="HY6" s="12" t="n">
-        <v>218</v>
-      </c>
-      <c r="HZ6" s="12" t="n">
-        <v>219</v>
-      </c>
-      <c r="IA6" s="12" t="n">
-        <v>220</v>
-      </c>
-      <c r="IB6" s="12" t="n">
-        <v>221</v>
-      </c>
-      <c r="IC6" s="12" t="n">
-        <v>222</v>
-      </c>
-      <c r="ID6" s="12" t="n">
-        <v>223</v>
-      </c>
-      <c r="IE6" s="12" t="n">
-        <v>224</v>
-      </c>
-      <c r="IF6" s="12" t="n">
-        <v>225</v>
-      </c>
-      <c r="IG6" s="12" t="n">
-        <v>226</v>
-      </c>
-      <c r="IH6" s="12" t="n">
-        <v>227</v>
-      </c>
-      <c r="II6" s="12" t="n">
-        <v>228</v>
-      </c>
-      <c r="IJ6" s="12" t="n">
-        <v>229</v>
-      </c>
-      <c r="IK6" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="IL6" s="12" t="n">
-        <v>231</v>
-      </c>
-      <c r="IM6" s="12" t="n">
-        <v>232</v>
-      </c>
-      <c r="IN6" s="12" t="n">
-        <v>233</v>
-      </c>
-      <c r="IO6" s="12" t="n">
-        <v>234</v>
-      </c>
-      <c r="IP6" s="12" t="n">
-        <v>235</v>
-      </c>
-      <c r="IQ6" s="12" t="n">
-        <v>236</v>
-      </c>
-      <c r="IR6" s="12" t="n">
-        <v>237</v>
-      </c>
-      <c r="IS6" s="12" t="n">
-        <v>238</v>
-      </c>
-      <c r="IT6" s="12" t="n">
-        <v>239</v>
-      </c>
-      <c r="IU6" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="IV6" s="12" t="n">
-        <v>241</v>
-      </c>
-      <c r="IW6" s="12" t="n">
-        <v>242</v>
-      </c>
-      <c r="IX6" s="12" t="n">
-        <v>243</v>
-      </c>
-      <c r="IY6" s="12" t="n">
-        <v>244</v>
-      </c>
-      <c r="IZ6" s="12" t="n">
-        <v>245</v>
-      </c>
-      <c r="JA6" s="12" t="n">
-        <v>246</v>
-      </c>
-      <c r="JB6" s="12" t="n">
-        <v>247</v>
-      </c>
-      <c r="JC6" s="12" t="n">
-        <v>248</v>
-      </c>
-      <c r="JD6" s="12" t="n">
-        <v>249</v>
-      </c>
-      <c r="JE6" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="JF6" s="12" t="n">
-        <v>251</v>
-      </c>
-      <c r="JG6" s="12" t="n">
-        <v>252</v>
-      </c>
-      <c r="JH6" s="12" t="n">
-        <v>253</v>
-      </c>
-      <c r="JI6" s="12" t="n">
-        <v>254</v>
-      </c>
-      <c r="JJ6" s="12" t="n">
-        <v>255</v>
-      </c>
-      <c r="JK6" s="12" t="n">
-        <v>256</v>
-      </c>
-      <c r="JL6" s="12" t="n">
-        <v>257</v>
-      </c>
-      <c r="JM6" s="12" t="n">
-        <v>258</v>
-      </c>
-      <c r="JN6" s="12" t="n">
-        <v>259</v>
-      </c>
-      <c r="JO6" s="12" t="n">
-        <v>260</v>
-      </c>
     </row>
     <row r="7" ht="42" customHeight="1" s="20">
       <c r="A7" s="7" t="inlineStr">
@@ -3299,12 +2771,12 @@
     <row r="19" ht="25.5" customHeight="1" s="20">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>M8b</t>
+          <t>M9</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Resolution and GPU renderer</t>
+          <t>Interaction and dialogue editor</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -3313,10 +2785,10 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F19" s="9">
         <f>ROUND((D19+E19)/2,0)</f>
@@ -3352,19 +2824,19 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>The game renders at 960x540 through Luna's SDL_GPU renderer (with the old renderer as fallback) and looks the same at 2x camera zoom; windowed sizes, borderless and exclusive full screen work; every screen and editor panel is laid out for the new size; the frame budget holds.</t>
+          <t>The owner opens any dialogue or interaction in the Editor as a graph, edits it, test-plays it and saves it, and the file still reads well in a text editor.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25.5" customHeight="1" s="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>M8c</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Lighting and shadows</t>
+          <t>Playtest and go/no-go (KILL GATE 2)</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -3373,10 +2845,10 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F20" s="9">
         <f>ROUND((D20+E20)/2,0)</f>
@@ -3412,657 +2884,116 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>The world is lit by the sun and moon through the day and the seasons, by fires, torches and effects at night, and dimmed by weather; sprites are shaded with generated normal maps; characters, plants and buildings cast shadows from the sun, the moon and nearby fires; the Editor previews any time of day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25.5" customHeight="1" s="20">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>M8d</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Buildings</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="F21" s="9">
-        <f>ROUND((D21+E21)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="9">
-        <f>H20+1</f>
-        <v/>
-      </c>
-      <c r="H21" s="9">
-        <f>G21+F21-1</f>
-        <v/>
-      </c>
-      <c r="I21" s="14">
-        <f>$B$4+(G21-1)*7</f>
-        <v/>
-      </c>
-      <c r="J21" s="14">
-        <f>$B$4+H21*7-1</f>
-        <v/>
-      </c>
-      <c r="K21" s="14">
-        <f>$B$4+SUM($D$7:D21)*7-1</f>
-        <v/>
-      </c>
-      <c r="L21" s="14">
-        <f>$B$4+SUM($E$7:E21)*7-1</f>
-        <v/>
-      </c>
-      <c r="M21" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A21,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A21,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N21" s="9" t="inlineStr">
-        <is>
-          <t>The hero builds from blueprints and piece by piece on a building grid, and rooms form; the owner composes prefabs from pieces in the Editor and places them in levels; prefabs marked buildable are offered as blueprints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25.5" customHeight="1" s="20">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>M8e</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Building life</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="F22" s="9">
-        <f>ROUND((D22+E22)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="9">
-        <f>H21+1</f>
-        <v/>
-      </c>
-      <c r="H22" s="9">
-        <f>G22+F22-1</f>
-        <v/>
-      </c>
-      <c r="I22" s="14">
-        <f>$B$4+(G22-1)*7</f>
-        <v/>
-      </c>
-      <c r="J22" s="14">
-        <f>$B$4+H22*7-1</f>
-        <v/>
-      </c>
-      <c r="K22" s="14">
-        <f>$B$4+SUM($D$7:D22)*7-1</f>
-        <v/>
-      </c>
-      <c r="L22" s="14">
-        <f>$B$4+SUM($E$7:E22)*7-1</f>
-        <v/>
-      </c>
-      <c r="M22" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A22,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A22,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N22" s="9" t="inlineStr">
-        <is>
-          <t>Clan members help build and rival clans build; each building fades its roof or opens an interior map as set in the Editor; buildings wear, are repaired, take damage, burn and fall; they shelter, warm and store for the clan and are saved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25.5" customHeight="1" s="20">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Interaction and dialogue editor</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="F23" s="9">
-        <f>ROUND((D23+E23)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
-        <f>H22+1</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>G23+F23-1</f>
-        <v/>
-      </c>
-      <c r="I23" s="14">
-        <f>$B$4+(G23-1)*7</f>
-        <v/>
-      </c>
-      <c r="J23" s="14">
-        <f>$B$4+H23*7-1</f>
-        <v/>
-      </c>
-      <c r="K23" s="14">
-        <f>$B$4+SUM($D$7:D23)*7-1</f>
-        <v/>
-      </c>
-      <c r="L23" s="14">
-        <f>$B$4+SUM($E$7:E23)*7-1</f>
-        <v/>
-      </c>
-      <c r="M23" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A23,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A23,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
-        <is>
-          <t>The owner opens any dialogue or interaction in the Editor as a graph, edits it, test-plays it and saves it, and the file still reads well in a text editor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25.5" customHeight="1" s="20">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Quests and story authoring</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F24" s="9">
-        <f>ROUND((D24+E24)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="9">
-        <f>H23+1</f>
-        <v/>
-      </c>
-      <c r="H24" s="9">
-        <f>G24+F24-1</f>
-        <v/>
-      </c>
-      <c r="I24" s="14">
-        <f>$B$4+(G24-1)*7</f>
-        <v/>
-      </c>
-      <c r="J24" s="14">
-        <f>$B$4+H24*7-1</f>
-        <v/>
-      </c>
-      <c r="K24" s="14">
-        <f>$B$4+SUM($D$7:D24)*7-1</f>
-        <v/>
-      </c>
-      <c r="L24" s="14">
-        <f>$B$4+SUM($E$7:E24)*7-1</f>
-        <v/>
-      </c>
-      <c r="M24" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A24,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A24,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
-        <is>
-          <t>The owner writes a quest in the Editor's graph (or offline in JSON), test-plays it with the debugger and saves it; a player gets it from an NPC, follows it in the journal, tracker and markers, and finishes it; the elder tutorial is a quest and crossroads events are edited as story events.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25.5" customHeight="1" s="20">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Data editors</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F25" s="9">
-        <f>ROUND((D25+E25)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="9">
-        <f>H24+1</f>
-        <v/>
-      </c>
-      <c r="H25" s="9">
-        <f>G25+F25-1</f>
-        <v/>
-      </c>
-      <c r="I25" s="14">
-        <f>$B$4+(G25-1)*7</f>
-        <v/>
-      </c>
-      <c r="J25" s="14">
-        <f>$B$4+H25*7-1</f>
-        <v/>
-      </c>
-      <c r="K25" s="14">
-        <f>$B$4+SUM($D$7:D25)*7-1</f>
-        <v/>
-      </c>
-      <c r="L25" s="14">
-        <f>$B$4+SUM($E$7:E25)*7-1</f>
-        <v/>
-      </c>
-      <c r="M25" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A25,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A25,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N25" s="9" t="inlineStr">
-        <is>
-          <t>Every data file has a schema; the owner edits any entity, mechanic, story tuning value, game rule and daily routine in Editor forms with pickers and validation, and the running game reloads it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="25.5" customHeight="1" s="20">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>World editing</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="9">
-        <f>ROUND((D26+E26)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G26" s="9">
-        <f>H25+1</f>
-        <v/>
-      </c>
-      <c r="H26" s="9">
-        <f>G26+F26-1</f>
-        <v/>
-      </c>
-      <c r="I26" s="14">
-        <f>$B$4+(G26-1)*7</f>
-        <v/>
-      </c>
-      <c r="J26" s="14">
-        <f>$B$4+H26*7-1</f>
-        <v/>
-      </c>
-      <c r="K26" s="14">
-        <f>$B$4+SUM($D$7:D26)*7-1</f>
-        <v/>
-      </c>
-      <c r="L26" s="14">
-        <f>$B$4+SUM($E$7:E26)*7-1</f>
-        <v/>
-      </c>
-      <c r="M26" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A26,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A26,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N26" s="9" t="inlineStr">
-        <is>
-          <t>The owner opens the procedural region in the Editor, tunes the generator with a live preview, paints terrain, water and mountains, places things, people and camps, and edits each clan's and person's relations, economy, routines and actions; edits are saved on top of the seed and a new game plays them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="25.5" customHeight="1" s="20">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Politics</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F27" s="9">
-        <f>ROUND((D27+E27)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="9">
-        <f>H26+1</f>
-        <v/>
-      </c>
-      <c r="H27" s="9">
-        <f>G27+F27-1</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>$B$4+(G27-1)*7</f>
-        <v/>
-      </c>
-      <c r="J27" s="14">
-        <f>$B$4+H27*7-1</f>
-        <v/>
-      </c>
-      <c r="K27" s="14">
-        <f>$B$4+SUM($D$7:D27)*7-1</f>
-        <v/>
-      </c>
-      <c r="L27" s="14">
-        <f>$B$4+SUM($E$7:E27)*7-1</f>
-        <v/>
-      </c>
-      <c r="M27" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A27,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A27,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N27" s="9" t="inlineStr">
-        <is>
-          <t>Clans form alliances and vassal oaths, hold elders' councils, bind themselves by marriage, challenge leaders and use trade and craft knowledge as levers; the player can win the region through Politics; every political rule is editable in the Editor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="25.5" customHeight="1" s="20">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F28" s="9">
-        <f>ROUND((D28+E28)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="9">
-        <f>H27+1</f>
-        <v/>
-      </c>
-      <c r="H28" s="9">
-        <f>G28+F28-1</f>
-        <v/>
-      </c>
-      <c r="I28" s="14">
-        <f>$B$4+(G28-1)*7</f>
-        <v/>
-      </c>
-      <c r="J28" s="14">
-        <f>$B$4+H28*7-1</f>
-        <v/>
-      </c>
-      <c r="K28" s="14">
-        <f>$B$4+SUM($D$7:D28)*7-1</f>
-        <v/>
-      </c>
-      <c r="L28" s="14">
-        <f>$B$4+SUM($E$7:E28)*7-1</f>
-        <v/>
-      </c>
-      <c r="M28" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A28,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A28,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N28" s="9" t="inlineStr">
-        <is>
-          <t>Clans research by doing in workshops with inventors, pass knowledge by teaching, steal and guard secrets, and unlock recipes, interactions and professions from an editable tech tree; the player can win by forging the Ember Strand while leading in known technologies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="25.5" customHeight="1" s="20">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Playtest and go/no-go (KILL GATE 2)</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="9">
-        <f>ROUND((D29+E29)/2,0)</f>
-        <v/>
-      </c>
-      <c r="G29" s="9">
-        <f>H28+1</f>
-        <v/>
-      </c>
-      <c r="H29" s="9">
-        <f>G29+F29-1</f>
-        <v/>
-      </c>
-      <c r="I29" s="14">
-        <f>$B$4+(G29-1)*7</f>
-        <v/>
-      </c>
-      <c r="J29" s="14">
-        <f>$B$4+H29*7-1</f>
-        <v/>
-      </c>
-      <c r="K29" s="14">
-        <f>$B$4+SUM($D$7:D29)*7-1</f>
-        <v/>
-      </c>
-      <c r="L29" s="14">
-        <f>$B$4+SUM($E$7:E29)*7-1</f>
-        <v/>
-      </c>
-      <c r="M29" s="9">
-        <f>SUMIFS('User Stories'!$H$5:$H$200,'User Stories'!$J$5:$J$200,A29,'User Stories'!$F$5:$F$200,"Must")&amp;" - "&amp;SUMIFS('User Stories'!$I$5:$I$200,'User Stories'!$J$5:$J$200,A29,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="N29" s="9" t="inlineStr">
-        <is>
-          <t>8 outside playtesters play; success criteria measured; go/no-go decision recorded. Held after M14 (owner, 2026-10-01, D-41).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" s="20">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="inlineStr">
+          <t>8 outside playtesters play; success criteria measured; go/no-go decision recorded. Held after M9 (owner, 2026-10-01, D-34).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" s="20">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>MVP total</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7">
-        <f>SUM(D7:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="7">
-        <f>SUM(E7:E29)</f>
-        <v/>
-      </c>
-      <c r="F30" s="7">
-        <f>SUM(F7:F29)</f>
-        <v/>
-      </c>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7">
-        <f>H29</f>
-        <v/>
-      </c>
-      <c r="I30" s="15">
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7">
+        <f>SUM(D7:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="7">
+        <f>SUM(E7:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="7">
+        <f>SUM(F7:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7">
+        <f>H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="15">
         <f>I7</f>
         <v/>
       </c>
-      <c r="J30" s="15">
-        <f>J29</f>
-        <v/>
-      </c>
-      <c r="K30" s="15">
-        <f>K29</f>
-        <v/>
-      </c>
-      <c r="L30" s="15">
-        <f>L29</f>
-        <v/>
-      </c>
-      <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="inlineStr">
+      <c r="J21" s="15">
+        <f>J20</f>
+        <v/>
+      </c>
+      <c r="K21" s="15">
+        <f>K20</f>
+        <v/>
+      </c>
+      <c r="L21" s="15">
+        <f>L20</f>
+        <v/>
+      </c>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>Months (likely) = weeks / 4.33</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="27.95" customHeight="1" s="20">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="inlineStr">
+    <row r="22" ht="27.95" customHeight="1" s="20">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>In months</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7">
-        <f>ROUND(D30/4.33,1)</f>
-        <v/>
-      </c>
-      <c r="E31" s="7">
-        <f>ROUND(E30/4.33,1)</f>
-        <v/>
-      </c>
-      <c r="F31" s="7">
-        <f>ROUND(F30/4.33,1)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-    </row>
-    <row r="32" ht="27.95" customHeight="1" s="20"/>
-    <row r="33" ht="27.95" customHeight="1" s="20">
-      <c r="B33" s="19" t="inlineStr">
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7">
+        <f>ROUND(D21/4.33,1)</f>
+        <v/>
+      </c>
+      <c r="E22" s="7">
+        <f>ROUND(E21/4.33,1)</f>
+        <v/>
+      </c>
+      <c r="F22" s="7">
+        <f>ROUND(F21/4.33,1)</f>
+        <v/>
+      </c>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="27.95" customHeight="1" s="20"/>
+    <row r="24" ht="27.95" customHeight="1" s="20">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Why the estimate grew: the learning path (requirements, section 8.3) estimated 9-13 months top-down. The bottom-up sum of the MVP stories is higher; this sheet uses the bottom-up figure.</t>
         </is>
       </c>
     </row>
-    <row r="34" s="20">
-      <c r="B34" s="19" t="inlineStr">
+    <row r="25" s="20">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Buffer: the 'Should' stories are the cut list if time runs short. Cutting all of them saves about 5-11 weeks.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="102" customHeight="1" s="20">
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Kill gates: M2 (failed 2026-09-30, passed at the M2b retry) and M6 (do playtesters stay?), held after M14 (D-41). Critical path: M0 &gt; M1 &gt; M1b &gt; M2 &gt; M2b &gt; M2c &gt; M2d &gt; M3 &gt; M4 &gt; M5 &gt; M7 &gt; M8 &gt; M8b &gt; M8c &gt; M8d &gt; M8e &gt; M9 &gt; M10 &gt; M11 &gt; M12 &gt; M13 &gt; M14 &gt; M6. Dates of M2c onwards are not re-planned yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+    <row r="26" ht="102" customHeight="1" s="20">
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Kill gates: M2 (is the console chronicle interesting? failed 2026-09-30, passed at the M2b retry) and M6 (do playtesters stay?), held after M9 (D-34). Critical path: M0 &gt; M1 &gt; M1b &gt; M2 &gt; M2b &gt; M2c &gt; M2d &gt; M3 &gt; M4 &gt; M5 &gt; M7 &gt; M8 &gt; M9 &gt; M6. Dates of M2c onwards are not re-planned yet.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B25:N25"/>
+    <mergeCell ref="B24:N24"/>
+    <mergeCell ref="B26:N26"/>
   </mergeCells>
-  <conditionalFormatting sqref="P7:JO29">
+  <conditionalFormatting sqref="P7:EY20">
     <cfRule type="expression" priority="1" dxfId="10">
       <formula>AND(P$6&gt;=$G7,P$6&lt;=$H7)</formula>
     </cfRule>
@@ -4077,7 +3008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="20" min="1" max="1"/>
@@ -4103,6 +3034,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4333,7 +3265,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Minimum PC spec (OPEN-19). Mid-range PC (owner, 2026-10-01): 6-core CPU, 16 GB RAM, RX 6600 / RTX 3060 class GPU (8 GB) with DirectX 12, Windows 10/11; 60 FPS at 1080p on High lighting, Low for weaker PCs. Development PC: RX 7900 XTX, 32 GB RAM, 6-core CPU.</t>
+          <t>Minimum PC spec (OPEN-19)</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4343,12 +3275,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>M8b</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>US-082, US-234</t>
+          <t>US-082</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -4358,7 +3290,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4666,7 +3598,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Technical chain: M0 &gt; M1 &gt; M1b &gt; M2 &gt; M2b &gt; M2c &gt; M2d &gt; M3 &gt; M4 &gt; M5 &gt; M7 &gt; M8 &gt; M8b &gt; M8c &gt; M8d &gt; M8e &gt; M9 &gt; M10 &gt; M11 &gt; M12 &gt; M13 &gt; M14 &gt; M6 (each milestone needs the previous one)</t>
+          <t>Technical chain: M0 &gt; M1 &gt; M1b &gt; M2 &gt; M2b &gt; M2c &gt; M2d &gt; M3 &gt; M4 &gt; M5 &gt; M7 &gt; M8 &gt; M9 &gt; M6 (each milestone needs the previous one)</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -4949,154 +3881,6 @@
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>Decided</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="25.5" customHeight="1" s="20">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>D-40</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (Round 14): M10 Quests (authored only, JSON + quest graph, flat with prerequisites, journal + tracker + markers, tutorial as a quest, story events), M11 Data editors (schema forms, Game Rules with system switches, daily routines), M12 World editing (generator settings with preview, overrides on the seed, per clan and person setup), M13 Politics (third pillar with victory); play-in-editor debugger; kill gate 2 after M13</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Design decision</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>US-180..US-216</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>Decided</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="25.5" customHeight="1" s="20">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>D-41</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Technology pillar (M14: tech tree as data, research by doing, workshops and inventors, espionage and theft; victory = Ember held + 60% Technology share or the four-pillar 50% average); Politics victory confirmed (60% / 50%); Game Rules default standard.json, levels may name their own; M10-M14: Dominus decides design questions (delegated) and tests run at exit reviews; kill gate 2 after M14</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Design decision</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>US-180..US-226</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>Decided</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="25.5" customHeight="1" s="20">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>D-42</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (Round 16): 960x540 with window modes, camera zoom, UI scale; SDL_GPU shaders; sun, moon, fire, torch and effect lights, seasonal day length, weather light; shadows from sun, moon and nearby fires; generated normal maps; buildings from blueprints and pieces, clans build, wear, repair, fire; interiors per building (roof fade or interior map); prefabs in the Editor; M8b, M8c, M8d right after M8</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Design decision</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>M8b</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>US-230..US-257</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>Decided</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="25.5" customHeight="1" s="20">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>D-43</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Assembly of M8b-M8e (Round 17): M8d split into M8d Buildings (US-250, 251, 252, 256) and M8e Building life (US-253, 254, 255, 257); US-256 no longer waits for US-254; M7-M9 assembly rules (D-35) apply; D-06 answered</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Design decision</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>M8b</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>US-230..US-257</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
@@ -5132,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="20" min="1" max="1"/>
@@ -5160,6 +3944,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="25.5" customHeight="1" s="20">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -5994,451 +4779,37 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="25.5" customHeight="1" s="20">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Quests</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>The owner writes quests in the Editor and offline; players get, follow and finish them with a journal, a tracker and markers.</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="E22" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A22,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G22" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A22,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H22" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A22,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I22" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A22,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J22" s="17">
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7">
+        <f>SUM(E5:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="7">
+        <f>SUM(F5:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="7">
+        <f>SUM(G5:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="7">
+        <f>SUM(H5:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="7">
+        <f>SUM(I5:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="18">
         <f>IFERROR(I22/E22,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="25.5" customHeight="1" s="20">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Data editors</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Every data file (entities, mechanics, story tuning, game rules, daily routines) is edited in the Editor through forms built from schemas.</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="E23" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A23,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A23,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A23,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I23" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A23,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J23" s="17">
-        <f>IFERROR(I23/E23,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="25.5" customHeight="1" s="20">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>World editing</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>The owner shapes the procedural region and its clans, people, economy and relations in the Editor, on top of the seed.</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="E24" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A24)</f>
-        <v/>
-      </c>
-      <c r="F24" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A24,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G24" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A24,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H24" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A24,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I24" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A24,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J24" s="17">
-        <f>IFERROR(I24/E24,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="25.5" customHeight="1" s="20">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Politics</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Clans ally, swear and break oaths, marry, vote and challenge leaders; the player can win the region through Politics.</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="E25" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A25)</f>
-        <v/>
-      </c>
-      <c r="F25" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A25,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G25" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A25,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H25" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A25,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I25" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A25,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J25" s="17">
-        <f>IFERROR(I25/E25,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="25.5" customHeight="1" s="20">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Clans discover, teach, guard and steal technologies; the player can win the region by forging the Ember Strand while leading in know-how.</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="E26" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A26)</f>
-        <v/>
-      </c>
-      <c r="F26" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A26,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G26" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A26,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H26" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A26,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I26" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A26,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J26" s="17">
-        <f>IFERROR(I26/E26,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="25.5" customHeight="1" s="20">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>E22</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Resolution and GPU renderer</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>The game renders at 960x540 on Luna's new SDL_GPU renderer, in any window size or full screen, and every screen and editor has room to breathe.</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>M8b</t>
-        </is>
-      </c>
-      <c r="E27" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A27)</f>
-        <v/>
-      </c>
-      <c r="F27" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A27,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G27" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A27,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H27" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A27,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I27" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A27,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J27" s="17">
-        <f>IFERROR(I27/E27,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="25.5" customHeight="1" s="20">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Lighting and shadows</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Days and nights, seasons and weather light the world; fires glow; characters, plants and buildings cast shadows that move with the sun, the moon and nearby fires.</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="E28" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A28)</f>
-        <v/>
-      </c>
-      <c r="F28" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A28,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G28" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A28,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H28" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A28,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I28" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A28,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J28" s="17">
-        <f>IFERROR(I28/E28,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="25.5" customHeight="1" s="20">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>E24</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Buildings</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>The hero builds from whole blueprints and piece by piece; the owner composes pre-made buildings in the Editor and places them.</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>M8d</t>
-        </is>
-      </c>
-      <c r="E29" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A29)</f>
-        <v/>
-      </c>
-      <c r="F29" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A29,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G29" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A29,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H29" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A29,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I29" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A29,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J29" s="17">
-        <f>IFERROR(I29/E29,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="25.5" customHeight="1" s="20">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>E25</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Building life</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Clans build together; interiors by roof fade or interior map; wear, repair, damage and fire; shelter, warmth and storage for the clan.</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>M8e</t>
-        </is>
-      </c>
-      <c r="E30" s="9">
-        <f>COUNTIF('User Stories'!$B$5:$B$200,A30)</f>
-        <v/>
-      </c>
-      <c r="F30" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A30,'User Stories'!$F$5:$F$200,"Must")</f>
-        <v/>
-      </c>
-      <c r="G30" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A30,'User Stories'!$H$5:$H$200)</f>
-        <v/>
-      </c>
-      <c r="H30" s="9">
-        <f>SUMIF('User Stories'!$B$5:$B$200,A30,'User Stories'!$I$5:$I$200)</f>
-        <v/>
-      </c>
-      <c r="I30" s="9">
-        <f>COUNTIFS('User Stories'!$B$5:$B$200,A30,'User Stories'!$O$5:$O$200,"Done")</f>
-        <v/>
-      </c>
-      <c r="J30" s="17">
-        <f>IFERROR(I30/E30,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7">
-        <f>SUM(E5:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="7">
-        <f>SUM(F5:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="7">
-        <f>SUM(G5:G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="7">
-        <f>SUM(H5:H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="7">
-        <f>SUM(I5:I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="18">
-        <f>IFERROR(I31/E31,0)</f>
         <v/>
       </c>
     </row>
@@ -6453,7 +4824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O155"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="20" min="1" max="1"/>
@@ -6486,6 +4857,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="25.5" customHeight="1" s="20">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -12681,7 +11053,7 @@
       </c>
       <c r="O79" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -12767,7 +11139,7 @@
       </c>
       <c r="O80" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -12853,7 +11225,7 @@
       </c>
       <c r="O81" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -12939,7 +11311,7 @@
       </c>
       <c r="O82" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -13025,7 +11397,7 @@
       </c>
       <c r="O83" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -13111,7 +11483,7 @@
       </c>
       <c r="O84" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -13197,7 +11569,7 @@
       </c>
       <c r="O85" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -13283,7 +11655,7 @@
       </c>
       <c r="O86" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -13369,7 +11741,7 @@
       </c>
       <c r="O87" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -13455,7 +11827,7 @@
       </c>
       <c r="O88" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To do</t>
         </is>
       </c>
     </row>
@@ -14228,4994 +12600,6 @@
         </is>
       </c>
       <c r="O97" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="124.15" customHeight="1" s="20">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>US-180</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Quest data and runtime</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want quests as JSON files with steps, objectives, conditions, rewards and prerequisites, so that I can write quests offline and the game runs them.</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Load
-Given a quest file with two steps, a branch and a reward
-When the game starts
-Then the quest is available once its prerequisites hold
-Scenario: Progress
-Given an active quest
-When its step's objective is met
-Then the next step starts and the reward is given at the end
-Scenario: Error
-Given a quest whose step points to a missing step on line 14
-When the data loads
-Then the error reads 'quests/&lt;file&gt;.json:14: unknown step' and the rest loads</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H98" s="9">
-        <f>VLOOKUP(G98,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I98" s="9">
-        <f>VLOOKUP(G98,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J98" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="K98" s="9" t="inlineStr">
-        <is>
-          <t>US-150, US-164, D-40</t>
-        </is>
-      </c>
-      <c r="L98" s="9" t="inlineStr">
-        <is>
-          <t>STO-04, ADR-019</t>
-        </is>
-      </c>
-      <c r="M98" s="9" t="inlineStr">
-        <is>
-          <t>State machines over data; saving progress</t>
-        </is>
-      </c>
-      <c r="N98" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O98" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="124.15" customHeight="1" s="20">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>US-181</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>Objectives from world events</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want my actions in the world to count toward quests, so that quests follow what I really do.</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Count
-Given an objective 'gather 5 berries'
-When the hero gathers 5 berries
-Then the objective is complete
-Scenario: Kinds
-Given objectives talk, go to, gather, give, craft, interact, defeat, wait and flag
-When each happens
-Then each is detected
-Scenario: Not mine
-Given an NPC gathering berries
-When it happens
-Then the hero's quest does not count it</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H99" s="9">
-        <f>VLOOKUP(G99,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I99" s="9">
-        <f>VLOOKUP(G99,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="K99" s="9" t="inlineStr">
-        <is>
-          <t>US-180</t>
-        </is>
-      </c>
-      <c r="L99" s="9" t="inlineStr">
-        <is>
-          <t>STO-04, INT-01</t>
-        </is>
-      </c>
-      <c r="M99" s="9" t="inlineStr">
-        <is>
-          <t>An event bus (observer pattern)</t>
-        </is>
-      </c>
-      <c r="N99" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O99" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="124.15" customHeight="1" s="20">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>US-182</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Getting and handing in quests</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want NPCs to offer quests in conversation and take them back when done, so that quests belong to people.</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Offer
-Given an NPC with an available quest
-When the hero is near
-Then a quest sign shows over the NPC and Talk offers the quest
-Scenario: Accept
-Given the offer in a .dlg choice with {quest start &lt;id&gt;}
-When the player picks it
-Then the quest is active
-Scenario: Hand in
-Given a finished quest and its giver
-When the player talks to the giver
-Then the turn-in line plays and the reward is given</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H100" s="9">
-        <f>VLOOKUP(G100,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I100" s="9">
-        <f>VLOOKUP(G100,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J100" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="K100" s="9" t="inlineStr">
-        <is>
-          <t>US-180, US-161</t>
-        </is>
-      </c>
-      <c r="L100" s="9" t="inlineStr">
-        <is>
-          <t>STO-04, SDC-03</t>
-        </is>
-      </c>
-      <c r="M100" s="9" t="inlineStr">
-        <is>
-          <t>Linking two data systems through ids</t>
-        </is>
-      </c>
-      <c r="N100" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O100" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="124.15" customHeight="1" s="20">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>US-183</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>Journal, tracker and markers</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want a journal, an on-screen tracker and markers over targets, so that I always know what to do next.</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Journal
-Given two active, one done and one failed quest
-When the player opens the journal
-Then they are listed in their groups with each step's text and log
-Scenario: Tracker
-Given an active quest
-When its step changes
-Then the tracker shows the new step at once
-Scenario: Markers
-Given markers on in settings
-When a step targets a person or place
-Then a marker shows over it; with markers off, none shows</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H101" s="9">
-        <f>VLOOKUP(G101,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I101" s="9">
-        <f>VLOOKUP(G101,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr">
-        <is>
-          <t>US-180</t>
-        </is>
-      </c>
-      <c r="L101" s="9" t="inlineStr">
-        <is>
-          <t>STO-04</t>
-        </is>
-      </c>
-      <c r="M101" s="9" t="inlineStr">
-        <is>
-          <t>Immediate-mode UI lists</t>
-        </is>
-      </c>
-      <c r="N101" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O101" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="124.15" customHeight="1" s="20">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>US-184</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>Quest graph editor</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to build quests as graphs in the Editor, so that I can see and change their steps, branches and prerequisites.</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Steps
-Given a quest open in the Editor
-When the owner adds a step and wires a branch
-Then the graph and the saved JSON show them
-Scenario: Blocks
-Given a step selected
-When the owner adds an objective, a condition and a reward
-Then pickers offer items, people, places, tags and quests
-Scenario: Prerequisites
-Given the quest list view
-When the owner links quest B after quest A
-Then B's prerequisites name A and the view draws the link</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H102" s="9">
-        <f>VLOOKUP(G102,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I102" s="9">
-        <f>VLOOKUP(G102,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J102" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="K102" s="9" t="inlineStr">
-        <is>
-          <t>US-180, US-170</t>
-        </is>
-      </c>
-      <c r="L102" s="9" t="inlineStr">
-        <is>
-          <t>STO-04, EDT-01</t>
-        </is>
-      </c>
-      <c r="M102" s="9" t="inlineStr">
-        <is>
-          <t>Reusing a generic widget for a new data type</t>
-        </is>
-      </c>
-      <c r="N102" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O102" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="124.15" customHeight="1" s="20">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>US-185</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>The tutorial as a quest; story events</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want the elder tutorial rebuilt as the first quest and the crossroads events edited as story events, so that all story content is authored in one place.</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Tutorial
-Given a new game with the tutorial on
-When the player starts
-Then the elder quest guides gather, eat and tend the fire as before, with the hint after 2 minutes
-Scenario: Story events
-Given a crossroads event
-When the owner opens it in the Editor
-Then its trigger, text and options with effects are edited and saved
-Scenario: Same game
-Given the M5 and M6 tests
-When they run
-Then they pass</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H103" s="9">
-        <f>VLOOKUP(G103,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I103" s="9">
-        <f>VLOOKUP(G103,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="K103" s="9" t="inlineStr">
-        <is>
-          <t>US-184, US-090</t>
-        </is>
-      </c>
-      <c r="L103" s="9" t="inlineStr">
-        <is>
-          <t>STO-05, EDT-01</t>
-        </is>
-      </c>
-      <c r="M103" s="9" t="inlineStr">
-        <is>
-          <t>Migrating data without changing behaviour</t>
-        </is>
-      </c>
-      <c r="N103" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O103" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="124.15" customHeight="1" s="20">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>US-186</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>Play-in-editor debugger</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to play from any spot in the Editor with a debug panel, so that I can test quests and content in minutes.</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Play here
-Given the Editor open
-When the owner chooses Play here
-Then the hero starts at the cursor and Esc returns to the Editor unchanged
-Scenario: Control
-Given the debug panel
-When the owner starts, completes or resets a quest, sets a flag, an item or an opinion, jumps time or teleports
-Then the game reflects it at once
-Scenario: Why not
-Given a quest step that does not complete
-When the owner selects it in the panel
-Then the failing condition and its current values are shown</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H104" s="9">
-        <f>VLOOKUP(G104,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I104" s="9">
-        <f>VLOOKUP(G104,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J104" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="K104" s="9" t="inlineStr">
-        <is>
-          <t>US-180</t>
-        </is>
-      </c>
-      <c r="L104" s="9" t="inlineStr">
-        <is>
-          <t>EDT-06</t>
-        </is>
-      </c>
-      <c r="M104" s="9" t="inlineStr">
-        <is>
-          <t>Debug-only code paths</t>
-        </is>
-      </c>
-      <c r="N104" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O104" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="124.15" customHeight="1" s="20">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>US-187</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>Quest validation</t>
-        </is>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want broken quests found before players see them, so that no quest can get stuck.</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Unreachable
-Given a step no branch leads to
-When validation runs
-Then it is listed and clicking it selects it
-Scenario: Impossible
-Given an objective naming an unknown item, person or place
-When validation runs
-Then it is listed
-Scenario: Cycle
-Given quests that require each other
-When validation runs
-Then the prerequisite cycle is listed</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H105" s="9">
-        <f>VLOOKUP(G105,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I105" s="9">
-        <f>VLOOKUP(G105,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J105" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="K105" s="9" t="inlineStr">
-        <is>
-          <t>US-184</t>
-        </is>
-      </c>
-      <c r="L105" s="9" t="inlineStr">
-        <is>
-          <t>STO-04, EDT-01</t>
-        </is>
-      </c>
-      <c r="M105" s="9" t="inlineStr">
-        <is>
-          <t>Cycle detection in a graph</t>
-        </is>
-      </c>
-      <c r="N105" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O105" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="124.15" customHeight="1" s="20">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>US-190</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>Schemas for every data file</t>
-        </is>
-      </c>
-      <c r="D106" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want every data file described by a schema with types, ranges, choices, links and help text, so that the Editor and the validator know what each field means.</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Coverage
-Given every file under assets/data/
-When the schema check runs in CI
-Then each file has a schema and passes it
-Scenario: Errors
-Given a value out of its range
-When the game loads it
-Then the error names file, line, field and the allowed range
-Scenario: Links
-Given a recipe naming an item no catalog has
-When the check runs
-Then the broken link is listed</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G106" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H106" s="9">
-        <f>VLOOKUP(G106,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I106" s="9">
-        <f>VLOOKUP(G106,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J106" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="K106" s="9" t="inlineStr">
-        <is>
-          <t>US-150</t>
-        </is>
-      </c>
-      <c r="L106" s="9" t="inlineStr">
-        <is>
-          <t>EDT-02, ADR-020</t>
-        </is>
-      </c>
-      <c r="M106" s="9" t="inlineStr">
-        <is>
-          <t>Describing data with data (a schema interpreter)</t>
-        </is>
-      </c>
-      <c r="N106" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O106" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="124.15" customHeight="1" s="20">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>US-191</t>
-        </is>
-      </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>Schema-driven form editor</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want a Data tab where any file opens as forms built from its schema, so that I can edit everything without touching JSON.</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Open
-Given weapons.json
-When the owner opens it in the Data tab
-Then entries are listed with search, and a form shows the selected entry's fields with help text
-Scenario: Edit
-Given a damage value changed and Ctrl+S
-When the file is saved
-Then only that value changes in the file, note fields stay, and the running game uses it
-Scenario: Undo
-Given five form edits
-When Ctrl+Z five times
-Then the data is as before</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H107" s="9">
-        <f>VLOOKUP(G107,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I107" s="9">
-        <f>VLOOKUP(G107,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="K107" s="9" t="inlineStr">
-        <is>
-          <t>US-190, US-121</t>
-        </is>
-      </c>
-      <c r="L107" s="9" t="inlineStr">
-        <is>
-          <t>EDT-02</t>
-        </is>
-      </c>
-      <c r="M107" s="9" t="inlineStr">
-        <is>
-          <t>Building UI from a description at run time</t>
-        </is>
-      </c>
-      <c r="N107" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O107" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="124.15" customHeight="1" s="20">
-      <c r="A108" s="7" t="inlineStr">
-        <is>
-          <t>US-192</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>Picture pickers and cutting frames</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to pick sprites, animations and effects by picture and cut new frames from my sheets in the Editor, so that new content gets its art without the command line.</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Pick
-Given a field holding an atlas frame
-When the owner opens its picker
-Then frames are shown as pictures and the choice is saved
-Scenario: Preview
-Given an effect or an animation
-When it is selected
-Then it plays in the form
-Scenario: Cut
-Given a sheet in assets/sprites/
-When the owner draws a rectangle and names it
-Then cuts.json gains the cut and the atlas is rebuilt</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H108" s="9">
-        <f>VLOOKUP(G108,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I108" s="9">
-        <f>VLOOKUP(G108,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J108" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="K108" s="9" t="inlineStr">
-        <is>
-          <t>US-191, US-120</t>
-        </is>
-      </c>
-      <c r="L108" s="9" t="inlineStr">
-        <is>
-          <t>EDT-02, D-05</t>
-        </is>
-      </c>
-      <c r="M108" s="9" t="inlineStr">
-        <is>
-          <t>Image regions and previews</t>
-        </is>
-      </c>
-      <c r="N108" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O108" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="124.15" customHeight="1" s="20">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>US-193</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>Entity editor</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to create, copy, rename and delete kinds of weapons, plants, animals, characters, objects and items, with their tags, states and interactions, so that new entities need no code.</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Create
-Given the plants catalog
-When the owner copies a bush, renames it and changes its tags
-Then the new plant appears in the Editor palette and offers its interactions
-Scenario: Rename
-Given an item used by recipes and quests
-When the owner renames it
-Then every reference is updated and listed
-Scenario: Delete
-Given a kind that is still used
-When the owner deletes it
-Then the uses are listed and the delete waits for confirmation</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H109" s="9">
-        <f>VLOOKUP(G109,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I109" s="9">
-        <f>VLOOKUP(G109,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="K109" s="9" t="inlineStr">
-        <is>
-          <t>US-191, US-172</t>
-        </is>
-      </c>
-      <c r="L109" s="9" t="inlineStr">
-        <is>
-          <t>EDT-02, INT-02</t>
-        </is>
-      </c>
-      <c r="M109" s="9" t="inlineStr">
-        <is>
-          <t>Keeping references consistent (rename refactoring)</t>
-        </is>
-      </c>
-      <c r="N109" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O109" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="124.15" customHeight="1" s="20">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>US-194</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>Mechanics and story tuning with a quick check</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want needs, actions, life, social, story, calendar, professions, recipes and hero data in forms, and a quick headless run to see the effect, so that I can tune mechanics safely.</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Forms
-Given every mechanics and story file
-When the owner opens it
-Then it shows as forms
-Scenario: Quick check
-Given a changed hunger rate
-When the owner runs the 20-year check
-Then a summary shows population, deaths by cause and episodes, next to the last run
-Scenario: Determinism
-Given the same data and seed
-When the check runs twice
-Then the summaries are the same</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H110" s="9">
-        <f>VLOOKUP(G110,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I110" s="9">
-        <f>VLOOKUP(G110,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J110" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="K110" s="9" t="inlineStr">
-        <is>
-          <t>US-191</t>
-        </is>
-      </c>
-      <c r="L110" s="9" t="inlineStr">
-        <is>
-          <t>EDT-02, STO-02</t>
-        </is>
-      </c>
-      <c r="M110" s="9" t="inlineStr">
-        <is>
-          <t>Running the simulation headless from the game</t>
-        </is>
-      </c>
-      <c r="N110" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O110" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="124.15" customHeight="1" s="20">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>US-195</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>Game Rules page</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want one page for New Game presets, comfort, victory thresholds and switches for whole systems, so that I can set up how a game plays.</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Switches
-Given weather, combat, rival clans, tutorial, markers, chronicle and politics switches
-When the owner turns weather off and starts a game
-Then no weather happens
-Scenario: Rules sets
-Given two rules files
-When a new game or a level picks one
-Then its values are used
-Scenario: Thresholds
-Given a victory threshold changed
-When a game reaches it
-Then victory follows the new value</t>
-        </is>
-      </c>
-      <c r="F111" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H111" s="9">
-        <f>VLOOKUP(G111,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I111" s="9">
-        <f>VLOOKUP(G111,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J111" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="K111" s="9" t="inlineStr">
-        <is>
-          <t>US-191</t>
-        </is>
-      </c>
-      <c r="L111" s="9" t="inlineStr">
-        <is>
-          <t>EDT-03, MVP-09</t>
-        </is>
-      </c>
-      <c r="M111" s="9" t="inlineStr">
-        <is>
-          <t>Feature flags read once at start</t>
-        </is>
-      </c>
-      <c r="N111" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O111" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="124.15" customHeight="1" s="20">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>US-196</t>
-        </is>
-      </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>Daily routines as data</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want daily routines per role and per person (sleep, work, meals, gatherings at the fire), so that clan life has a rhythm I can shape.</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Routine
-Given the hunters' routine with work from 6 to 14
-When a day passes
-Then hunters choose work interactions in that block more often than at other times
-Scenario: Edit
-Given the Routines editor
-When the owner drags a block on the day timeline
-Then the routine file is saved and used
-Scenario: Needs win
-Given a starving hunter in a work block
-When time passes
-Then they eat first</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H112" s="9">
-        <f>VLOOKUP(G112,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I112" s="9">
-        <f>VLOOKUP(G112,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J112" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="K112" s="9" t="inlineStr">
-        <is>
-          <t>US-154, US-191</t>
-        </is>
-      </c>
-      <c r="L112" s="9" t="inlineStr">
-        <is>
-          <t>SDC-07, INT-05</t>
-        </is>
-      </c>
-      <c r="M112" s="9" t="inlineStr">
-        <is>
-          <t>Time blocks and weighting a utility AI</t>
-        </is>
-      </c>
-      <c r="N112" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O112" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="124.15" customHeight="1" s="20">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>US-200</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>The region in the Editor</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to open the procedural region in the Editor with a zoomable map, so that I can work on the whole world.</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Open
-Given a seed
-When the owner opens the region
-Then it shows at any zoom from the whole 256 x 256 map to single tiles, at a smooth frame rate
-Scenario: Layers
-Given the layer switches
-When the owner hides plants and people
-Then only terrain shows
-Scenario: Same world
-Given the region opened in the Editor
-When it is compared to the game's
-Then they are identical</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H113" s="9">
-        <f>VLOOKUP(G113,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I113" s="9">
-        <f>VLOOKUP(G113,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J113" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="K113" s="9" t="inlineStr">
-        <is>
-          <t>US-040, US-123</t>
-        </is>
-      </c>
-      <c r="L113" s="9" t="inlineStr">
-        <is>
-          <t>EDT-04</t>
-        </is>
-      </c>
-      <c r="M113" s="9" t="inlineStr">
-        <is>
-          <t>Streaming chunks and level of detail</t>
-        </is>
-      </c>
-      <c r="N113" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O113" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="124.15" customHeight="1" s="20">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>US-201</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>Generator settings with live preview</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want every generator setting in forms with a preview map, so that I can shape a region before committing to it.</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Preview
-Given the biome mix changed
-When the owner presses Preview
-Then a new map shows within a few seconds beside the old one
-Scenario: Apply
-Given a preview the owner likes
-When Apply
-Then the region and region.json use the new settings
-Scenario: Keep edits
-Given hand edits on the region
-When the settings change
-Then the edits stay and conflicts are listed</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H114" s="9">
-        <f>VLOOKUP(G114,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I114" s="9">
-        <f>VLOOKUP(G114,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="K114" s="9" t="inlineStr">
-        <is>
-          <t>US-200, US-191</t>
-        </is>
-      </c>
-      <c r="L114" s="9" t="inlineStr">
-        <is>
-          <t>EDT-04</t>
-        </is>
-      </c>
-      <c r="M114" s="9" t="inlineStr">
-        <is>
-          <t>Pure functions of a seed</t>
-        </is>
-      </c>
-      <c r="N114" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O114" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="124.15" customHeight="1" s="20">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>US-202</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>Hand edits on top of the seed</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to paint terrain and biomes on the region and keep them on top of the seed, so that the world is generated and hand-made at once.</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Paint
-Given the brush on the region
-When the owner paints a meadow into a forest
-Then the change shows and is saved as an override of those chunks
-Scenario: Small saves
-Given 100 painted tiles
-When the region is saved
-Then the file holds the seed plus the changed tiles, not the whole map
-Scenario: Undo
-Given region edits
-When Ctrl+Z
-Then they are undone as in the level editor</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H115" s="9">
-        <f>VLOOKUP(G115,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I115" s="9">
-        <f>VLOOKUP(G115,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="K115" s="9" t="inlineStr">
-        <is>
-          <t>US-200</t>
-        </is>
-      </c>
-      <c r="L115" s="9" t="inlineStr">
-        <is>
-          <t>EDT-04, ADR-010</t>
-        </is>
-      </c>
-      <c r="M115" s="9" t="inlineStr">
-        <is>
-          <t>Storing differences (overlays) instead of copies</t>
-        </is>
-      </c>
-      <c r="N115" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O115" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="124.15" customHeight="1" s="20">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>US-203</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>Water and mountains</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to draw and remove rivers, lakes, cliffs and caves, so that I can shape the land.</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: River
-Given the river tool
-When the owner draws a river
-Then it flows from start to end and blocks walking except at fords
-Scenario: Cave
-Given a cliff
-When the owner places a cave mouth
-Then the cave can be entered in the game
-Scenario: Remove
-Given a generated lake
-When the owner removes it
-Then land replaces it and the change is an override</t>
-        </is>
-      </c>
-      <c r="F116" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H116" s="9">
-        <f>VLOOKUP(G116,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I116" s="9">
-        <f>VLOOKUP(G116,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J116" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="K116" s="9" t="inlineStr">
-        <is>
-          <t>US-202</t>
-        </is>
-      </c>
-      <c r="L116" s="9" t="inlineStr">
-        <is>
-          <t>EDT-04</t>
-        </is>
-      </c>
-      <c r="M116" s="9" t="inlineStr">
-        <is>
-          <t>Path tools and connected areas</t>
-        </is>
-      </c>
-      <c r="N116" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O116" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="124.15" customHeight="1" s="20">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>US-204</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>Things, people and places in the region</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to place plants, animals, objects, people and named places in the region, so that quests and stories have their spots.</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Place
-Given the palettes
-When the owner places a fire pit and an NPC
-Then they are saved as region overrides and appear in the game
-Scenario: Places
-Given a named place 'Red Cliff'
-When a quest step targets it
-Then the quest marker points to it
-Scenario: Pickers
-Given a quest or dialogue field
-When the owner picks a person or place
-Then region people and places are offered</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H117" s="9">
-        <f>VLOOKUP(G117,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I117" s="9">
-        <f>VLOOKUP(G117,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J117" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="K117" s="9" t="inlineStr">
-        <is>
-          <t>US-202, US-155</t>
-        </is>
-      </c>
-      <c r="L117" s="9" t="inlineStr">
-        <is>
-          <t>EDT-04, STO-04</t>
-        </is>
-      </c>
-      <c r="M117" s="9" t="inlineStr">
-        <is>
-          <t>Ids that survive regeneration</t>
-        </is>
-      </c>
-      <c r="N117" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O117" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="124.15" customHeight="1" s="20">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>US-205</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>Camps and resources</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to move the player and rival camps and set resource spots and amounts, so that I control the region's balance.</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Camps
-Given a rival camp
-When the owner moves it
-Then the rival clan lives there in the game
-Scenario: Resources
-Given a flint spot
-When the owner sets it to 50
-Then 50 flint can be taken there
-Scenario: Rules
-Given a camp placed in water
-When the owner tries
-Then it is refused with the reason</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H118" s="9">
-        <f>VLOOKUP(G118,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I118" s="9">
-        <f>VLOOKUP(G118,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="K118" s="9" t="inlineStr">
-        <is>
-          <t>US-202, US-041</t>
-        </is>
-      </c>
-      <c r="L118" s="9" t="inlineStr">
-        <is>
-          <t>EDT-04, MVP-10</t>
-        </is>
-      </c>
-      <c r="M118" s="9" t="inlineStr">
-        <is>
-          <t>Validating placements against rules</t>
-        </is>
-      </c>
-      <c r="N118" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O118" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="124.15" customHeight="1" s="20">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>US-206</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>Clans and people inspector</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to edit each clan and person in the world: members, kinship, leader, opinions and grudges, rival stance, owned items, stores, debts, trade partners, routine and allowed actions, so that I set up the social, economic and political world.</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Social
-Given two people selected
-When the owner sets their opinion to -50 and adds a grudge with a reason
-Then the game starts with that grudge and the chronicle can tell it
-Scenario: Economy
-Given a clan selected
-When the owner fills its store and adds a debt to a rival
-Then the game starts with that store and debt
-Scenario: Overrides
-Given a person selected
-When the owner removes Barter from their actions and changes their HP
-Then only that person changes</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H119" s="9">
-        <f>VLOOKUP(G119,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I119" s="9">
-        <f>VLOOKUP(G119,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J119" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="K119" s="9" t="inlineStr">
-        <is>
-          <t>US-204, US-196, US-173</t>
-        </is>
-      </c>
-      <c r="L119" s="9" t="inlineStr">
-        <is>
-          <t>EDT-05, SDC-07, PIL-08</t>
-        </is>
-      </c>
-      <c r="M119" s="9" t="inlineStr">
-        <is>
-          <t>Editing a graph of relations safely</t>
-        </is>
-      </c>
-      <c r="N119" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O119" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="124.15" customHeight="1" s="20">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>US-207</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>Play the edited region</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to start a new game on my edited region or play it from the Editor, so that my world is the game.</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: New game
-Given an edited region saved as a world file
-When the player starts a new game from it
-Then every edit is there
-Scenario: Play here
-Given the region in the Editor
-When the owner chooses Play here
-Then the game starts on the edited region at the cursor
-Scenario: Old saves
-Given a save from before region editing
-When it loads
-Then it still works</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H120" s="9">
-        <f>VLOOKUP(G120,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I120" s="9">
-        <f>VLOOKUP(G120,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="K120" s="9" t="inlineStr">
-        <is>
-          <t>US-206, US-186</t>
-        </is>
-      </c>
-      <c r="L120" s="9" t="inlineStr">
-        <is>
-          <t>EDT-04, EDT-06</t>
-        </is>
-      </c>
-      <c r="M120" s="9" t="inlineStr">
-        <is>
-          <t>Versioned save formats</t>
-        </is>
-      </c>
-      <c r="N120" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O120" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="124.15" customHeight="1" s="20">
-      <c r="A121" s="7" t="inlineStr">
-        <is>
-          <t>US-210</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>The political model</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want clans as political actors with relations, alliances, vassal ties and a Politics share of the region, all as editable data, so that politics is part of the simulation.</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Relations
-Given three clans
-When the simulation runs
-Then each pair has a stance from -100 to 100 that moves with events, with reasons
-Scenario: Share
-Given one rival a vassal of the player's clan
-When the dominion screen opens
-Then Politics shows that clan's share of the region's people
-Scenario: Data
-Given politics.json
-When the owner opens it in the Data tab
-Then every political rule is a form</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H121" s="9">
-        <f>VLOOKUP(G121,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I121" s="9">
-        <f>VLOOKUP(G121,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="K121" s="9" t="inlineStr">
-        <is>
-          <t>US-206, US-195</t>
-        </is>
-      </c>
-      <c r="L121" s="9" t="inlineStr">
-        <is>
-          <t>PIL-03, PIL-08</t>
-        </is>
-      </c>
-      <c r="M121" s="9" t="inlineStr">
-        <is>
-          <t>Modelling relations between groups</t>
-        </is>
-      </c>
-      <c r="N121" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O121" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="124.15" customHeight="1" s="20">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>US-211</t>
-        </is>
-      </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>Alliances and vassal oaths</t>
-        </is>
-      </c>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want to ally with clans, take tribute and make them swear vassal oaths, which can break, so that I can bind the region to my clan.</t>
-        </is>
-      </c>
-      <c r="E122" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Alliance
-Given a rival with a good stance
-When the hero proposes an alliance
-Then it is accepted or refused with a reason
-Scenario: Oath
-Given an allied clan that is weaker and indebted
-When the hero asks for a vassal oath
-Then it swears and pays tribute each season
-Scenario: Break
-Given a vassal whose stance falls below its limit
-When a season passes
-Then it may break the oath, and the chronicle says why</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H122" s="9">
-        <f>VLOOKUP(G122,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I122" s="9">
-        <f>VLOOKUP(G122,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J122" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="K122" s="9" t="inlineStr">
-        <is>
-          <t>US-210</t>
-        </is>
-      </c>
-      <c r="L122" s="9" t="inlineStr">
-        <is>
-          <t>PIL-03, PIL-08</t>
-        </is>
-      </c>
-      <c r="M122" s="9" t="inlineStr">
-        <is>
-          <t>Contracts as data with conditions</t>
-        </is>
-      </c>
-      <c r="N122" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O122" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="124.15" customHeight="1" s="20">
-      <c r="A123" s="7" t="inlineStr">
-        <is>
-          <t>US-212</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="C123" s="9" t="inlineStr">
-        <is>
-          <t>Elders' council</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want clan decisions voted by the elders and to sway them, so that leading a clan means persuading people.</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Vote
-Given a decision to move camp
-When the council meets
-Then each elder votes by needs, traits and opinion, and the result is shown
-Scenario: Sway
-Given the hero talks to an elder before the vote
-When a persuasion choice succeeds
-Then that elder's vote changes
-Scenario: Record
-Given a council decision
-When it is taken
-Then the chronicle records it with the votes</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G123" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H123" s="9">
-        <f>VLOOKUP(G123,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I123" s="9">
-        <f>VLOOKUP(G123,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="K123" s="9" t="inlineStr">
-        <is>
-          <t>US-210</t>
-        </is>
-      </c>
-      <c r="L123" s="9" t="inlineStr">
-        <is>
-          <t>PIL-08, SDC-02</t>
-        </is>
-      </c>
-      <c r="M123" s="9" t="inlineStr">
-        <is>
-          <t>Simple voting rules and weights</t>
-        </is>
-      </c>
-      <c r="N123" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O123" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="124.15" customHeight="1" s="20">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>US-213</t>
-        </is>
-      </c>
-      <c r="B124" s="9" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>Marriage ties</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want marriages between clans to bind them, so that love and politics meet.</t>
-        </is>
-      </c>
-      <c r="E124" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Tie
-Given a courtship between two clans' members
-When they marry
-Then the clans' stance rises and a marriage tie is recorded
-Scenario: Alliance
-Given a marriage tie
-When an alliance is proposed
-Then acceptance is more likely
-Scenario: Parting
-Given a married couple parts
-When it happens
-Then the tie weakens and the stance falls</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G124" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H124" s="9">
-        <f>VLOOKUP(G124,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I124" s="9">
-        <f>VLOOKUP(G124,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J124" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="K124" s="9" t="inlineStr">
-        <is>
-          <t>US-210, US-113</t>
-        </is>
-      </c>
-      <c r="L124" s="9" t="inlineStr">
-        <is>
-          <t>PIL-08, SDC-02</t>
-        </is>
-      </c>
-      <c r="M124" s="9" t="inlineStr">
-        <is>
-          <t>Events that affect two systems</t>
-        </is>
-      </c>
-      <c r="N124" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O124" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="124.15" customHeight="1" s="20">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t>US-214</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>Leadership challenges</t>
-        </is>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want leaders to be challenged when their people turn against them, and to challenge or back a leader myself, so that power can change hands.</t>
-        </is>
-      </c>
-      <c r="E125" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Challenge
-Given a leader whose clan opinion is below the limit
-When time passes
-Then a challenger rises and the council or a contest decides
-Scenario: Hero
-Given the hero with enough support
-When the hero challenges the leader
-Then the outcome follows the rules and the chronicle tells it
-Scenario: Succession
-Given a leader dies
-When it happens
-Then succession is contested between candidates with reasons</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H125" s="9">
-        <f>VLOOKUP(G125,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I125" s="9">
-        <f>VLOOKUP(G125,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J125" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="K125" s="9" t="inlineStr">
-        <is>
-          <t>US-212</t>
-        </is>
-      </c>
-      <c r="L125" s="9" t="inlineStr">
-        <is>
-          <t>PIL-08</t>
-        </is>
-      </c>
-      <c r="M125" s="9" t="inlineStr">
-        <is>
-          <t>State transitions with guards</t>
-        </is>
-      </c>
-      <c r="N125" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O125" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="124.15" customHeight="1" s="20">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>US-215</t>
-        </is>
-      </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t>Economic and technological levers</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want trade pacts, tribute in goods, embargoes and sharing crafts with allies as political tools, so that wealth and know-how buy influence.</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Pact
-Given two allied clans
-When a trade pact is made
-Then barter between them is cheaper and stance rises
-Scenario: Embargo
-Given a rival under embargo
-When it tries to trade with the hero's allies
-Then it is refused and stance falls
-Scenario: Know-how
-Given the hero teaches an ally a recipe
-When it happens
-Then the ally can craft it and its stance and dependence rise</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H126" s="9">
-        <f>VLOOKUP(G126,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I126" s="9">
-        <f>VLOOKUP(G126,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J126" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="K126" s="9" t="inlineStr">
-        <is>
-          <t>US-211, US-062</t>
-        </is>
-      </c>
-      <c r="L126" s="9" t="inlineStr">
-        <is>
-          <t>PIL-08, PIL-02</t>
-        </is>
-      </c>
-      <c r="M126" s="9" t="inlineStr">
-        <is>
-          <t>Interfaces between subsystems</t>
-        </is>
-      </c>
-      <c r="N126" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O126" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="124.15" customHeight="1" s="20">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>US-216</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="C127" s="9" t="inlineStr">
-        <is>
-          <t>Political victory and diplomacy</t>
-        </is>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want to win the region through Politics and to do diplomacy in conversation, so that Politics is a full path to victory.</t>
-        </is>
-      </c>
-      <c r="E127" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Victory
-Given vassals holding 60% of the region's people (Game Rules value)
-When the share is reached
-Then the game ends in a Political victory with the chronicle
-Scenario: Combined
-Given Trade, Religion and Politics shares
-When they reach the combined threshold
-Then victory follows the Game Rules
-Scenario: Diplomacy
-Given a clan leader
-When the hero talks to them
-Then alliance, oath, pact and embargo choices are offered in the conversation</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H127" s="9">
-        <f>VLOOKUP(G127,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I127" s="9">
-        <f>VLOOKUP(G127,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J127" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="K127" s="9" t="inlineStr">
-        <is>
-          <t>US-211, US-195, US-161</t>
-        </is>
-      </c>
-      <c r="L127" s="9" t="inlineStr">
-        <is>
-          <t>PIL-03, PIL-08, MVP-08, MVP-09</t>
-        </is>
-      </c>
-      <c r="M127" s="9" t="inlineStr">
-        <is>
-          <t>Combining scores from several systems</t>
-        </is>
-      </c>
-      <c r="N127" s="9" t="inlineStr">
-        <is>
-          <t>Authoring tools and Politics (owner, 2026-10-01, D-40)</t>
-        </is>
-      </c>
-      <c r="O127" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="124.15" customHeight="1" s="20">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>US-220</t>
-        </is>
-      </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>The tech tree as data</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want Age 1 technologies with prerequisites, discovery rules and unlocks in a data file shown as a tree in the Editor, so that I can design how know-how grows.</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Load
-Given technologies.json with fire mastery, hafted spears, sewing and ochre
-When the game starts
-Then each technology's prerequisites and unlocks (recipes, interactions, professions, objects) are known
-Scenario: Editor
-Given the tech tree view
-When the owner adds a technology and links it after another
-Then the tree and the saved file show it
-Scenario: Cycle
-Given two technologies that require each other
-When validation runs
-Then the cycle is listed</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G128" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H128" s="9">
-        <f>VLOOKUP(G128,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I128" s="9">
-        <f>VLOOKUP(G128,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J128" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="K128" s="9" t="inlineStr">
-        <is>
-          <t>US-191, US-170, D-41</t>
-        </is>
-      </c>
-      <c r="L128" s="9" t="inlineStr">
-        <is>
-          <t>PIL-05, PIL-09, EDT-02</t>
-        </is>
-      </c>
-      <c r="M128" s="9" t="inlineStr">
-        <is>
-          <t>Directed acyclic graphs and topological order</t>
-        </is>
-      </c>
-      <c r="N128" s="9" t="inlineStr">
-        <is>
-          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
-        </is>
-      </c>
-      <c r="O128" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="124.15" customHeight="1" s="20">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>US-221</t>
-        </is>
-      </c>
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="inlineStr">
-        <is>
-          <t>Research by doing</t>
-        </is>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want my clan to discover technologies by using skills and materials, so that progress grows out of daily life.</t>
-        </is>
-      </c>
-      <c r="E129" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Discover
-Given a clan that knaps flint every day
-When enough research has built up
-Then the next flint technology is discovered and its recipes unlock
-Scenario: Chronicle
-Given a discovery
-When it happens
-Then the chronicle says who discovered it and how
-Scenario: Locked
-Given a technology whose prerequisite is unknown
-When the work happens
-Then it is not discovered</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G129" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H129" s="9">
-        <f>VLOOKUP(G129,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I129" s="9">
-        <f>VLOOKUP(G129,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J129" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="K129" s="9" t="inlineStr">
-        <is>
-          <t>US-220</t>
-        </is>
-      </c>
-      <c r="L129" s="9" t="inlineStr">
-        <is>
-          <t>PIL-09</t>
-        </is>
-      </c>
-      <c r="M129" s="9" t="inlineStr">
-        <is>
-          <t>Accumulators and thresholds</t>
-        </is>
-      </c>
-      <c r="N129" s="9" t="inlineStr">
-        <is>
-          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
-        </is>
-      </c>
-      <c r="O129" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="124.15" customHeight="1" s="20">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>US-222</t>
-        </is>
-      </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>Workshops, inventors and teaching</t>
-        </is>
-      </c>
-      <c r="D130" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want workshops and inventive people to speed research and teaching to spread knowledge, so that who works where matters.</t>
-        </is>
-      </c>
-      <c r="E130" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Workshop
-Given knapping at a knapping stone versus in the open
-When a day passes
-Then the workshop gives more research, by the data's factor
-Scenario: Inventor
-Given an NPC with the inventive trait
-When they work
-Then they add research faster and can discover alone
-Scenario: Teach
-Given a known technology
-When a member teaches another clan's member (an ally)
-Then that clan knows it after the teaching time</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G130" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H130" s="9">
-        <f>VLOOKUP(G130,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I130" s="9">
-        <f>VLOOKUP(G130,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J130" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="K130" s="9" t="inlineStr">
-        <is>
-          <t>US-221, US-155</t>
-        </is>
-      </c>
-      <c r="L130" s="9" t="inlineStr">
-        <is>
-          <t>PIL-09, US-215</t>
-        </is>
-      </c>
-      <c r="M130" s="9" t="inlineStr">
-        <is>
-          <t>Modifiers that stack in a defined order</t>
-        </is>
-      </c>
-      <c r="N130" s="9" t="inlineStr">
-        <is>
-          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
-        </is>
-      </c>
-      <c r="O130" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="124.15" customHeight="1" s="20">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>US-223</t>
-        </is>
-      </c>
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>Espionage, theft and secrets</t>
-        </is>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want rivals to steal or copy know-how and to guard my own, so that knowledge is power to protect.</t>
-        </is>
-      </c>
-      <c r="E131" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Steal
-Given a rival watching our workshop or trading with us
-When time passes
-Then it may learn one of our technologies, and stance falls if caught
-Scenario: Guard
-Given a technology marked secret
-When a rival tries to learn it
-Then the chance is lower and secret-keepers can catch the spy
-Scenario: Repeat
-Given the same seed and inputs
-When two runs
-Then the same thefts happen</t>
-        </is>
-      </c>
-      <c r="F131" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G131" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H131" s="9">
-        <f>VLOOKUP(G131,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I131" s="9">
-        <f>VLOOKUP(G131,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J131" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="K131" s="9" t="inlineStr">
-        <is>
-          <t>US-222, US-210</t>
-        </is>
-      </c>
-      <c r="L131" s="9" t="inlineStr">
-        <is>
-          <t>PIL-09, PIL-08</t>
-        </is>
-      </c>
-      <c r="M131" s="9" t="inlineStr">
-        <is>
-          <t>Probabilities from a seeded stream</t>
-        </is>
-      </c>
-      <c r="N131" s="9" t="inlineStr">
-        <is>
-          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
-        </is>
-      </c>
-      <c r="O131" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="124.15" customHeight="1" s="20">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>US-224</t>
-        </is>
-      </c>
-      <c r="B132" s="9" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="C132" s="9" t="inlineStr">
-        <is>
-          <t>Rival research and the Technology share</t>
-        </is>
-      </c>
-      <c r="D132" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want rival clans to research too and to see who leads in know-how, so that Technology is a race.</t>
-        </is>
-      </c>
-      <c r="E132" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Rivals
-Given two rival clans
-When a year passes
-Then each has discovered technologies by its own priorities
-Scenario: Share
-Given the dominion screen
-When the player opens it
-Then Technology shows each clan's share of the Age 1 technologies known
-Scenario: Data
-Given rival priorities
-When the owner edits them in forms
-Then rivals follow the new priorities</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G132" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H132" s="9">
-        <f>VLOOKUP(G132,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I132" s="9">
-        <f>VLOOKUP(G132,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J132" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="K132" s="9" t="inlineStr">
-        <is>
-          <t>US-221</t>
-        </is>
-      </c>
-      <c r="L132" s="9" t="inlineStr">
-        <is>
-          <t>PIL-09, ENV-10</t>
-        </is>
-      </c>
-      <c r="M132" s="9" t="inlineStr">
-        <is>
-          <t>Comparing scores across actors</t>
-        </is>
-      </c>
-      <c r="N132" s="9" t="inlineStr">
-        <is>
-          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
-        </is>
-      </c>
-      <c r="O132" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="124.15" customHeight="1" s="20">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>US-225</t>
-        </is>
-      </c>
-      <c r="B133" s="9" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="C133" s="9" t="inlineStr">
-        <is>
-          <t>The Ember Strand and Technology victory</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want to forge the Ember Strand at the end of a long chain of discoveries and win when I hold it and lead in know-how, so that Technology is a full path to victory.</t>
-        </is>
-      </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Chain
-Given the Ember chain in technologies.json and recipes.json
-When the clan discovers every step and gathers the materials
-Then the Ember Strand can be forged at the sacred fire
-Scenario: Victory
-Given the Ember Strand held and a Technology share at or above the Game Rules value (60%)
-When both are true
-Then the game ends in a Technology victory with the chronicle
-Scenario: Rival forges
-Given a rival forges Ember first
-When it happens
-Then the chronicle tells it and the player can still win another way or take it</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H133" s="9">
-        <f>VLOOKUP(G133,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I133" s="9">
-        <f>VLOOKUP(G133,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J133" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="K133" s="9" t="inlineStr">
-        <is>
-          <t>US-224, US-195, US-062</t>
-        </is>
-      </c>
-      <c r="L133" s="9" t="inlineStr">
-        <is>
-          <t>PIL-05, PIL-09, MVP-08, MVP-09</t>
-        </is>
-      </c>
-      <c r="M133" s="9" t="inlineStr">
-        <is>
-          <t>Long multi-step goals as data</t>
-        </is>
-      </c>
-      <c r="N133" s="9" t="inlineStr">
-        <is>
-          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
-        </is>
-      </c>
-      <c r="O133" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="124.15" customHeight="1" s="20">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>US-226</t>
-        </is>
-      </c>
-      <c r="B134" s="9" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="C134" s="9" t="inlineStr">
-        <is>
-          <t>The technology screen</t>
-        </is>
-      </c>
-      <c r="D134" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want a screen with what my clan knows, what is next and what each discovery unlocks, so that I can plan research.</t>
-        </is>
-      </c>
-      <c r="E134" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Tree
-Given a clan with some technologies
-When the player opens the screen
-Then known, reachable and locked technologies are shown as a tree
-Scenario: Detail
-Given a technology selected
-When it is shown
-Then its discovery rule, progress and unlocks are listed
-Scenario: Secrets
-Given a technology marked secret
-When it is shown
-Then who else is known to have it is listed</t>
-        </is>
-      </c>
-      <c r="F134" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G134" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H134" s="9">
-        <f>VLOOKUP(G134,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I134" s="9">
-        <f>VLOOKUP(G134,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J134" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="K134" s="9" t="inlineStr">
-        <is>
-          <t>US-220</t>
-        </is>
-      </c>
-      <c r="L134" s="9" t="inlineStr">
-        <is>
-          <t>PIL-09, PIL-07</t>
-        </is>
-      </c>
-      <c r="M134" s="9" t="inlineStr">
-        <is>
-          <t>Laying out a tree for reading</t>
-        </is>
-      </c>
-      <c r="N134" s="9" t="inlineStr">
-        <is>
-          <t>Technology pillar (owner, 2026-10-01, D-41)</t>
-        </is>
-      </c>
-      <c r="O134" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="124.15" customHeight="1" s="20">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>US-230</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="inlineStr">
-        <is>
-          <t>E22</t>
-        </is>
-      </c>
-      <c r="C135" s="9" t="inlineStr">
-        <is>
-          <t>Luna's SDL_GPU renderer</t>
-        </is>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>As the developer, I want Luna to draw through SDL_GPU with shaders, keeping the old renderer as a fallback, so that lighting and shadows become possible without changing game code.</t>
-        </is>
-      </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Same picture
-Given the demo level and the camp
-When they are drawn with the GPU and the old renderer
-Then the screenshots match pixel for pixel at 1x lighting
-Scenario: Fallback
-Given a PC where SDL_GPU cannot start
-When the game starts
-Then it uses the old renderer, says so in the log and plays
-Scenario: Game code
-Given every draw call in src/game/
-When the switch is made
-Then no game file changed its drawing code</t>
-        </is>
-      </c>
-      <c r="F135" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G135" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H135" s="9">
-        <f>VLOOKUP(G135,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I135" s="9">
-        <f>VLOOKUP(G135,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J135" s="9" t="inlineStr">
-        <is>
-          <t>M8b</t>
-        </is>
-      </c>
-      <c r="K135" s="9" t="inlineStr">
-        <is>
-          <t>US-020, D-42</t>
-        </is>
-      </c>
-      <c r="L135" s="9" t="inlineStr">
-        <is>
-          <t>ARC-11, ADR-021, ADR-003</t>
-        </is>
-      </c>
-      <c r="M135" s="9" t="inlineStr">
-        <is>
-          <t>Graphics pipelines, shaders and sprite batching</t>
-        </is>
-      </c>
-      <c r="N135" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O135" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="124.15" customHeight="1" s="20">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>US-231</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="inlineStr">
-        <is>
-          <t>E22</t>
-        </is>
-      </c>
-      <c r="C136" s="9" t="inlineStr">
-        <is>
-          <t>960x540 and window modes</t>
-        </is>
-      </c>
-      <c r="D136" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want the game at 960x540 that fills my screen crisply in a window or full screen, so that it looks sharp on any monitor.</t>
-        </is>
-      </c>
-      <c r="E136" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Scale
-Given a 1920x1080 and a 3840x2160 screen
-When the game runs full screen
-Then it scales by 2 and by 4 with no blur and no border
-Scenario: Modes
-Given the settings screen
-When the player picks windowed (with sizes), borderless or exclusive full screen
-Then the mode changes at once and is saved
-Scenario: Odd sizes
-Given a 2560x1440 screen
-When the game runs
-Then it scales by 2 with a thin border, or fills the screen smoothly if the player chooses Fill</t>
-        </is>
-      </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G136" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H136" s="9">
-        <f>VLOOKUP(G136,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I136" s="9">
-        <f>VLOOKUP(G136,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J136" s="9" t="inlineStr">
-        <is>
-          <t>M8b</t>
-        </is>
-      </c>
-      <c r="K136" s="9" t="inlineStr">
-        <is>
-          <t>US-230, US-081</t>
-        </is>
-      </c>
-      <c r="L136" s="9" t="inlineStr">
-        <is>
-          <t>ENV-18, US-081</t>
-        </is>
-      </c>
-      <c r="M136" s="9" t="inlineStr">
-        <is>
-          <t>Viewports and scaling maths</t>
-        </is>
-      </c>
-      <c r="N136" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O136" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="124.15" customHeight="1" s="20">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>US-232</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="inlineStr">
-        <is>
-          <t>E22</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>Camera zoom and UI scale</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want to zoom the world and size the interface, so that I can see more of the land or read more easily.</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Zoom
-Given the default camera zoom of 2x
-When the player zooms out
-Then the view shows 1x (30 x 17 tiles) and back, around the hero
-Scenario: UI
-Given UI scale 1x and 2x
-When the player switches
-Then panels, the font and the hotbar resize and stay crisp
-Scenario: Pointer
-Given any zoom
-When the player aims and clicks
-Then the pointer hits the same world spot as before</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H137" s="9">
-        <f>VLOOKUP(G137,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I137" s="9">
-        <f>VLOOKUP(G137,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J137" s="9" t="inlineStr">
-        <is>
-          <t>M8b</t>
-        </is>
-      </c>
-      <c r="K137" s="9" t="inlineStr">
-        <is>
-          <t>US-231</t>
-        </is>
-      </c>
-      <c r="L137" s="9" t="inlineStr">
-        <is>
-          <t>ENV-18</t>
-        </is>
-      </c>
-      <c r="M137" s="9" t="inlineStr">
-        <is>
-          <t>Two coordinate systems: world and screen</t>
-        </is>
-      </c>
-      <c r="N137" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O137" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="124.15" customHeight="1" s="20">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>US-233</t>
-        </is>
-      </c>
-      <c r="B138" s="9" t="inlineStr">
-        <is>
-          <t>E22</t>
-        </is>
-      </c>
-      <c r="C138" s="9" t="inlineStr">
-        <is>
-          <t>Every screen at the new size</t>
-        </is>
-      </c>
-      <c r="D138" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want every screen, panel and editor laid out for 960x540, so that nothing is cramped or out of place.</t>
-        </is>
-      </c>
-      <c r="E138" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Screens
-Given the HUD, hotbar, menus, the run screens, the dialogue panel and the Editor's tool bar, palettes and properties
-When they are opened at 960x540
-Then they use the space, nothing overlaps and the text is legible
-Scenario: Tests
-Given the screenshot tests
-When they run
-Then they pass with the new reference pictures, reviewed by the owner
-Scenario: Old saves
-Given a save and a level from before
-When they load
-Then they play the same</t>
-        </is>
-      </c>
-      <c r="F138" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G138" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H138" s="9">
-        <f>VLOOKUP(G138,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I138" s="9">
-        <f>VLOOKUP(G138,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J138" s="9" t="inlineStr">
-        <is>
-          <t>M8b</t>
-        </is>
-      </c>
-      <c r="K138" s="9" t="inlineStr">
-        <is>
-          <t>US-232</t>
-        </is>
-      </c>
-      <c r="L138" s="9" t="inlineStr">
-        <is>
-          <t>ENV-18, EDT-01</t>
-        </is>
-      </c>
-      <c r="M138" s="9" t="inlineStr">
-        <is>
-          <t>Layout from data instead of fixed numbers</t>
-        </is>
-      </c>
-      <c r="N138" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O138" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="124.15" customHeight="1" s="20">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>US-234</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="inlineStr">
-        <is>
-          <t>E22</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>Frame budget at the new size</t>
-        </is>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want the game smooth at 960x540, so that the bigger picture costs nothing in feel.</t>
-        </is>
-      </c>
-      <c r="E139" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Budget
-Given 500 simulated people in the region on the minimum PC (D-06)
-When the game runs for 10 minutes
-Then it holds 60 FPS
-Scenario: Overlay
-Given F3
-When it is pressed
-Then the overlay shows CPU and GPU frame times
-Scenario: Record
-Given the performance run
-When it ends
-Then its numbers are saved in docs/evidence/</t>
-        </is>
-      </c>
-      <c r="F139" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G139" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H139" s="9">
-        <f>VLOOKUP(G139,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I139" s="9">
-        <f>VLOOKUP(G139,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J139" s="9" t="inlineStr">
-        <is>
-          <t>M8b</t>
-        </is>
-      </c>
-      <c r="K139" s="9" t="inlineStr">
-        <is>
-          <t>US-233, D-06</t>
-        </is>
-      </c>
-      <c r="L139" s="9" t="inlineStr">
-        <is>
-          <t>NFR-03, MVP success criteria</t>
-        </is>
-      </c>
-      <c r="M139" s="9" t="inlineStr">
-        <is>
-          <t>Measuring GPU and CPU time</t>
-        </is>
-      </c>
-      <c r="N139" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O139" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="124.15" customHeight="1" s="20">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>US-240</t>
-        </is>
-      </c>
-      <c r="B140" s="9" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="inlineStr">
-        <is>
-          <t>The lighting pipeline</t>
-        </is>
-      </c>
-      <c r="D140" s="9" t="inlineStr">
-        <is>
-          <t>As the developer, I want a lit pass with ambient light, point lights and normal maps in the GPU renderer, so that the world can be lit from data.</t>
-        </is>
-      </c>
-      <c r="E140" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Ambient
-Given an ambient colour in lights.json
-When the scene is drawn
-Then every sprite is tinted by it
-Scenario: Point light
-Given a light with a colour, radius and strength
-When it is placed near a sprite
-Then the sprite's lit side faces the light, using its normal map
-Scenario: Budget
-Given 64 lights on screen
-When the scene is drawn
-Then the frame budget of US-234 still holds</t>
-        </is>
-      </c>
-      <c r="F140" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G140" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H140" s="9">
-        <f>VLOOKUP(G140,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I140" s="9">
-        <f>VLOOKUP(G140,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J140" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="K140" s="9" t="inlineStr">
-        <is>
-          <t>US-230</t>
-        </is>
-      </c>
-      <c r="L140" s="9" t="inlineStr">
-        <is>
-          <t>ENV-19, ADR-021</t>
-        </is>
-      </c>
-      <c r="M140" s="9" t="inlineStr">
-        <is>
-          <t>Shader inputs, uniform data and lighting maths</t>
-        </is>
-      </c>
-      <c r="N140" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O140" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="124.15" customHeight="1" s="20">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>US-241</t>
-        </is>
-      </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>Generated normal maps</t>
-        </is>
-      </c>
-      <c r="D141" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want normal maps made from my sprites by a tool, so that lights shade my art without painting a second image.</t>
-        </is>
-      </c>
-      <c r="E141" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Generate
-Given the atlases
-When the atlas tool runs with normal maps on
-Then every atlas gets a matching normal-map atlas
-Scenario: Missing
-Given a sprite without a normal map
-When it is lit
-Then it is lit flat, with no error
-Scenario: Own map
-Given a hand-made normal map named like the sprite
-When the tool runs
-Then the hand-made one is kept</t>
-        </is>
-      </c>
-      <c r="F141" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G141" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H141" s="9">
-        <f>VLOOKUP(G141,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I141" s="9">
-        <f>VLOOKUP(G141,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J141" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="K141" s="9" t="inlineStr">
-        <is>
-          <t>US-240, US-120</t>
-        </is>
-      </c>
-      <c r="L141" s="9" t="inlineStr">
-        <is>
-          <t>ENV-19, D-05</t>
-        </is>
-      </c>
-      <c r="M141" s="9" t="inlineStr">
-        <is>
-          <t>Image processing: height and slopes from pixels</t>
-        </is>
-      </c>
-      <c r="N141" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O141" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="124.15" customHeight="1" s="20">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>US-242</t>
-        </is>
-      </c>
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>Day, night and seasons</t>
-        </is>
-      </c>
-      <c r="D142" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want dawn, day, dusk and night to follow the game clock, with longer summer days and short winter days, so that time feels real.</t>
-        </is>
-      </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Cycle
-Given the game clock running
-When a day passes
-Then the light goes through dawn, day, dusk and night colours from sky.json
-Scenario: Seasons
-Given midsummer and midwinter
-When the days are compared
-Then the summer day is longer, as calendar.json says
-Scenario: Moon
-Given night
-When it is drawn
-Then the moon gives a dim, blue light and a direction for shadows</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G142" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H142" s="9">
-        <f>VLOOKUP(G142,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I142" s="9">
-        <f>VLOOKUP(G142,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J142" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="K142" s="9" t="inlineStr">
-        <is>
-          <t>US-240, US-010</t>
-        </is>
-      </c>
-      <c r="L142" s="9" t="inlineStr">
-        <is>
-          <t>ENV-19, ENV-20</t>
-        </is>
-      </c>
-      <c r="M142" s="9" t="inlineStr">
-        <is>
-          <t>Interpolating curves over time</t>
-        </is>
-      </c>
-      <c r="N142" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O142" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="124.15" customHeight="1" s="20">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>US-243</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>Fires, torches and glowing effects</t>
-        </is>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want fires, torches, the sacred fire and elemental effects to light the night with a flicker, so that camps glow in the dark.</t>
-        </is>
-      </c>
-      <c r="E143" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Fire
-Given a lit fire pit at night
-When the scene is drawn
-Then it lights a circle around it with a flicker
-Scenario: Data
-Given a catalog entry with a light field
-When the thing is placed
-Then it emits that light; without the field, none
-Scenario: Torch
-Given a clan member carrying a torch
-When they walk at night
-Then the light moves with them</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G143" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H143" s="9">
-        <f>VLOOKUP(G143,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I143" s="9">
-        <f>VLOOKUP(G143,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J143" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="K143" s="9" t="inlineStr">
-        <is>
-          <t>US-240, US-132</t>
-        </is>
-      </c>
-      <c r="L143" s="9" t="inlineStr">
-        <is>
-          <t>ENV-19</t>
-        </is>
-      </c>
-      <c r="M143" s="9" t="inlineStr">
-        <is>
-          <t>Noise for natural flicker</t>
-        </is>
-      </c>
-      <c r="N143" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O143" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="124.15" customHeight="1" s="20">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>US-244</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="inlineStr">
-        <is>
-          <t>Sun and moon shadows</t>
-        </is>
-      </c>
-      <c r="D144" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want characters, plants and buildings to cast shadows that turn and stretch with the sun and the moon, so that the world has depth.</t>
-        </is>
-      </c>
-      <c r="E144" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Day
-Given a tree at 9:00 and at 17:00
-When it is drawn
-Then its shadow points away from the sun and is longer in the morning and evening
-Scenario: Casters
-Given characters, plants and buildings
-When the sun shines
-Then each casts a shadow sized by its height in the catalog
-Scenario: Overcast
-Given fog or heavy cloud
-When it sets in
-Then the shadows fade</t>
-        </is>
-      </c>
-      <c r="F144" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G144" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H144" s="9">
-        <f>VLOOKUP(G144,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I144" s="9">
-        <f>VLOOKUP(G144,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J144" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="K144" s="9" t="inlineStr">
-        <is>
-          <t>US-242</t>
-        </is>
-      </c>
-      <c r="L144" s="9" t="inlineStr">
-        <is>
-          <t>ENV-21</t>
-        </is>
-      </c>
-      <c r="M144" s="9" t="inlineStr">
-        <is>
-          <t>Projecting silhouettes with a shear transform</t>
-        </is>
-      </c>
-      <c r="N144" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O144" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="124.15" customHeight="1" s="20">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>US-245</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>Shadows from fires</t>
-        </is>
-      </c>
-      <c r="D145" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want a fire to throw shadows of the people and things near it at night, so that night scenes feel alive.</t>
-        </is>
-      </c>
-      <c r="E145" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Fire shadow
-Given a person standing near a fire at night
-When it is drawn
-Then their shadow points away from the fire
-Scenario: Two fires
-Given a person between two fires
-When it is drawn
-Then they cast two faint shadows
-Scenario: Budget
-Given many fires
-When the scene is drawn
-Then only the nearest fires (from lights.json) cast shadows and the frame budget holds</t>
-        </is>
-      </c>
-      <c r="F145" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G145" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H145" s="9">
-        <f>VLOOKUP(G145,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I145" s="9">
-        <f>VLOOKUP(G145,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J145" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="K145" s="9" t="inlineStr">
-        <is>
-          <t>US-244, US-243</t>
-        </is>
-      </c>
-      <c r="L145" s="9" t="inlineStr">
-        <is>
-          <t>ENV-21</t>
-        </is>
-      </c>
-      <c r="M145" s="9" t="inlineStr">
-        <is>
-          <t>Choosing the nearest lights per object within a budget</t>
-        </is>
-      </c>
-      <c r="N145" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O145" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="124.15" customHeight="1" s="20">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>US-246</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="C146" s="9" t="inlineStr">
-        <is>
-          <t>Weather and light</t>
-        </is>
-      </c>
-      <c r="D146" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want clouds, rain, fog and storms to darken and tint the world, with lightning flashes, so that weather changes the mood.</t>
-        </is>
-      </c>
-      <c r="E146" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Dim
-Given rain starting at noon
-When it fades in
-Then the light dims and cools over the same 3 s
-Scenario: Lightning
-Given a storm
-When lightning strikes
-Then the whole scene flashes for a moment
-Scenario: Data
-Given weather.json
-When the owner sets a weather's light
-Then the game uses it</t>
-        </is>
-      </c>
-      <c r="F146" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G146" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H146" s="9">
-        <f>VLOOKUP(G146,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I146" s="9">
-        <f>VLOOKUP(G146,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J146" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="K146" s="9" t="inlineStr">
-        <is>
-          <t>US-242, US-138</t>
-        </is>
-      </c>
-      <c r="L146" s="9" t="inlineStr">
-        <is>
-          <t>ENV-19</t>
-        </is>
-      </c>
-      <c r="M146" s="9" t="inlineStr">
-        <is>
-          <t>Blending light settings</t>
-        </is>
-      </c>
-      <c r="N146" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O146" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="124.15" customHeight="1" s="20">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>US-247</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="C147" s="9" t="inlineStr">
-        <is>
-          <t>Lighting in the Editor and quality settings</t>
-        </is>
-      </c>
-      <c r="D147" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to preview any time of day and place lights in the Editor, and players to choose lighting quality, so that levels look right and run everywhere.</t>
-        </is>
-      </c>
-      <c r="E147" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Preview
-Given the Editor
-When the owner drags the time-of-day slider
-Then the level is lit as at that hour
-Scenario: Place
-Given the light tool
-When the owner places a light and sets it
-Then it is saved in the level and shines in the game
-Scenario: Quality
-Given Low, Medium and High lighting
-When the player picks Low
-Then fire shadows and normal maps switch off and the frame time drops</t>
-        </is>
-      </c>
-      <c r="F147" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G147" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H147" s="9">
-        <f>VLOOKUP(G147,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I147" s="9">
-        <f>VLOOKUP(G147,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J147" s="9" t="inlineStr">
-        <is>
-          <t>M8c</t>
-        </is>
-      </c>
-      <c r="K147" s="9" t="inlineStr">
-        <is>
-          <t>US-243, US-244</t>
-        </is>
-      </c>
-      <c r="L147" s="9" t="inlineStr">
-        <is>
-          <t>ENV-19, EDT-01</t>
-        </is>
-      </c>
-      <c r="M147" s="9" t="inlineStr">
-        <is>
-          <t>Settings that change a pipeline</t>
-        </is>
-      </c>
-      <c r="N147" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O147" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="124.15" customHeight="1" s="20">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t>US-250</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="inlineStr">
-        <is>
-          <t>E24</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>Building pieces and building kinds as data</t>
-        </is>
-      </c>
-      <c r="D148" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want building pieces (walls, floors, roofs, doors, posts) and building kinds (layout, materials, build time, interior mode, uses) in data files, so that I can design buildings without code.</t>
-        </is>
-      </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Load
-Given pieces.json and buildings.json with a hut, a windbreak, a storage pit, a drying rack and a palisade
-When the game starts
-Then every kind and piece is known, with errors naming file, line and field
-Scenario: Own list
-Given buildings in a level
-When it is saved and loaded
-Then they are kept in their own list, not as plants (CI-008)
-Scenario: Uses
-Given a hut with shelter and sleep, a storage pit with storage
-When the data loads
-Then their interactions are offered</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G148" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H148" s="9">
-        <f>VLOOKUP(G148,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I148" s="9">
-        <f>VLOOKUP(G148,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>M8d</t>
-        </is>
-      </c>
-      <c r="K148" s="9" t="inlineStr">
-        <is>
-          <t>US-150, US-155</t>
-        </is>
-      </c>
-      <c r="L148" s="9" t="inlineStr">
-        <is>
-          <t>INT-07, EDT-07, ARC-08</t>
-        </is>
-      </c>
-      <c r="M148" s="9" t="inlineStr">
-        <is>
-          <t>Composite data: a whole made of parts</t>
-        </is>
-      </c>
-      <c r="N148" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O148" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="124.15" customHeight="1" s="20">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>US-251</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>E24</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>Building from blueprints</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want to choose a building, place its blueprint, bring materials and build it over time, so that I can shape my camp.</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Place
-Given known blueprints
-When the player picks a hut and places it
-Then a see-through blueprint shows, red where it cannot stand
-Scenario: Build
-Given a placed blueprint
-When materials are brought and the hero works on it
-Then it rises in stages and is finished after its build time
-Scenario: Cancel
-Given a blueprint under way
-When the player cancels it
-Then the delivered materials are dropped on the site</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H149" s="9">
-        <f>VLOOKUP(G149,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I149" s="9">
-        <f>VLOOKUP(G149,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J149" s="9" t="inlineStr">
-        <is>
-          <t>M8d</t>
-        </is>
-      </c>
-      <c r="K149" s="9" t="inlineStr">
-        <is>
-          <t>US-250, US-153</t>
-        </is>
-      </c>
-      <c r="L149" s="9" t="inlineStr">
-        <is>
-          <t>INT-07</t>
-        </is>
-      </c>
-      <c r="M149" s="9" t="inlineStr">
-        <is>
-          <t>Placement validity on a grid</t>
-        </is>
-      </c>
-      <c r="N149" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O149" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="124.15" customHeight="1" s="20">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t>US-252</t>
-        </is>
-      </c>
-      <c r="B150" s="9" t="inlineStr">
-        <is>
-          <t>E24</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="inlineStr">
-        <is>
-          <t>Building piece by piece</t>
-        </is>
-      </c>
-      <c r="D150" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want to place walls, floors, roofs and doors one by one, so that I can build any shape.</t>
-        </is>
-      </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Pieces
-Given the build menu's pieces
-When the player places walls in a ring, a door and a roof
-Then each piece is built like a small blueprint
-Scenario: Room
-Given an enclosed, roofed space with a door
-When it is finished
-Then it counts as a room: warm, sheltered, with its own light
-Scenario: Paths
-Given a door
-When people walk to the room
-Then they go through the door, never through walls</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G150" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H150" s="9">
-        <f>VLOOKUP(G150,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I150" s="9">
-        <f>VLOOKUP(G150,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J150" s="9" t="inlineStr">
-        <is>
-          <t>M8d</t>
-        </is>
-      </c>
-      <c r="K150" s="9" t="inlineStr">
-        <is>
-          <t>US-251</t>
-        </is>
-      </c>
-      <c r="L150" s="9" t="inlineStr">
-        <is>
-          <t>INT-07</t>
-        </is>
-      </c>
-      <c r="M150" s="9" t="inlineStr">
-        <is>
-          <t>Flood fill to find enclosed rooms</t>
-        </is>
-      </c>
-      <c r="N150" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O150" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="124.15" customHeight="1" s="20">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>US-253</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t>E25</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>Clans build together</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want my clan members to help build and rival clans to grow their own camps, so that building is a shared life.</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Help
-Given a blueprint and idle clan members
-When time passes
-Then they bring materials and build, through the interaction system
-Scenario: Rivals
-Given a rival camp
-When a season passes
-Then it has built at least one building from its own blueprints
-Scenario: Deterministic
-Given the same seed and inputs
-When two runs
-Then the same buildings stand in the same places</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G151" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H151" s="9">
-        <f>VLOOKUP(G151,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I151" s="9">
-        <f>VLOOKUP(G151,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J151" s="9" t="inlineStr">
-        <is>
-          <t>M8e</t>
-        </is>
-      </c>
-      <c r="K151" s="9" t="inlineStr">
-        <is>
-          <t>US-251, US-154</t>
-        </is>
-      </c>
-      <c r="L151" s="9" t="inlineStr">
-        <is>
-          <t>INT-07, INT-05</t>
-        </is>
-      </c>
-      <c r="M151" s="9" t="inlineStr">
-        <is>
-          <t>Job queues for many workers</t>
-        </is>
-      </c>
-      <c r="N151" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O151" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="124.15" customHeight="1" s="20">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>US-254</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>E25</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>Interiors: roof fade or interior map</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want to see inside buildings, either by the roof fading or by entering an interior, as the building says, so that houses are places to be.</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Fade
-Given a hut set to roof fade
-When the hero walks in
-Then the roof and the front walls fade and the inside shows, lit by its fire and door
-Scenario: Interior
-Given a lodge set to interior map
-When the hero uses its door
-Then the interior level loads and its door leads back outside
-Scenario: Setting
-Given a placed building
-When the owner switches its interior mode in the Editor
-Then the game follows it</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H152" s="9">
-        <f>VLOOKUP(G152,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I152" s="9">
-        <f>VLOOKUP(G152,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J152" s="9" t="inlineStr">
-        <is>
-          <t>M8e</t>
-        </is>
-      </c>
-      <c r="K152" s="9" t="inlineStr">
-        <is>
-          <t>US-252, US-122</t>
-        </is>
-      </c>
-      <c r="L152" s="9" t="inlineStr">
-        <is>
-          <t>ENV-20, EDT-07</t>
-        </is>
-      </c>
-      <c r="M152" s="9" t="inlineStr">
-        <is>
-          <t>Linking two maps by doors</t>
-        </is>
-      </c>
-      <c r="N152" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O152" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="124.15" customHeight="1" s="20">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>US-255</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="inlineStr">
-        <is>
-          <t>E25</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>Wear, repair, damage and fire</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want buildings to wear with weather, to be repaired, damaged and to burn, so that they need care.</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Wear
-Given a hut through a winter
-When the season passes
-Then its condition falls as the data says and Repair is offered
-Scenario: Fire
-Given a burning torch dropped by a wooden wall
-When time passes
-Then the wall catches fire, it spreads to wooden neighbours by their materials and ends in rubble
-Scenario: Damage
-Given an attack on a wall
-When it is hit
-Then the wall loses condition and falls at zero</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G153" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H153" s="9">
-        <f>VLOOKUP(G153,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I153" s="9">
-        <f>VLOOKUP(G153,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J153" s="9" t="inlineStr">
-        <is>
-          <t>M8e</t>
-        </is>
-      </c>
-      <c r="K153" s="9" t="inlineStr">
-        <is>
-          <t>US-251, US-029</t>
-        </is>
-      </c>
-      <c r="L153" s="9" t="inlineStr">
-        <is>
-          <t>INT-08, PHY-04</t>
-        </is>
-      </c>
-      <c r="M153" s="9" t="inlineStr">
-        <is>
-          <t>Spreading state across neighbours (cellular rules)</t>
-        </is>
-      </c>
-      <c r="N153" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O153" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="124.15" customHeight="1" s="20">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>US-256</t>
-        </is>
-      </c>
-      <c r="B154" s="9" t="inlineStr">
-        <is>
-          <t>E24</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>Prefab editor and placing buildings</t>
-        </is>
-      </c>
-      <c r="D154" s="9" t="inlineStr">
-        <is>
-          <t>As the owner, I want to compose buildings from pieces in the Editor, save them as prefabs with costs and interior mode, and place them whole, so that levels start with real camps.</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Compose
-Given the Prefab tab
-When the owner places pieces, sets materials, build time and interior mode, and saves
-Then a prefab file is written and appears in the palette
-Scenario: Place
-Given a prefab
-When the owner places it in a level
-Then the finished building stands there in the game
-Scenario: Blueprint
-Given a prefab marked buildable
-When a game starts
-Then the player can build it from the build menu</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G154" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H154" s="9">
-        <f>VLOOKUP(G154,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I154" s="9">
-        <f>VLOOKUP(G154,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J154" s="9" t="inlineStr">
-        <is>
-          <t>M8d</t>
-        </is>
-      </c>
-      <c r="K154" s="9" t="inlineStr">
-        <is>
-          <t>US-252, US-124</t>
-        </is>
-      </c>
-      <c r="L154" s="9" t="inlineStr">
-        <is>
-          <t>EDT-07</t>
-        </is>
-      </c>
-      <c r="M154" s="9" t="inlineStr">
-        <is>
-          <t>Saving a group of parts as one reusable asset</t>
-        </is>
-      </c>
-      <c r="N154" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O154" s="16" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="124.15" customHeight="1" s="20">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>US-257</t>
-        </is>
-      </c>
-      <c r="B155" s="9" t="inlineStr">
-        <is>
-          <t>E25</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
-        <is>
-          <t>Buildings in the clan's life</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>As the player, I want buildings to matter to the clan: shelter and warmth, sleeping, storage and ownership, saved with the world, so that building changes how people live.</t>
-        </is>
-      </c>
-      <c r="E155" s="9" t="inlineStr">
-        <is>
-          <t>Scenario: Warmth
-Given a cold night
-When clan members sleep in a hut
-Then their Warmth need falls slower than outside
-Scenario: Storage
-Given a storage pit
-When food is put in
-Then it counts in the clan store and spoils slower
-Scenario: Saved
-Given buildings with owners, condition and contents
-When the game saves and loads
-Then everything is kept</t>
-        </is>
-      </c>
-      <c r="F155" s="9" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H155" s="9">
-        <f>VLOOKUP(G155,'Read Me'!$A$13:$C$15,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I155" s="9">
-        <f>VLOOKUP(G155,'Read Me'!$A$13:$C$15,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J155" s="9" t="inlineStr">
-        <is>
-          <t>M8e</t>
-        </is>
-      </c>
-      <c r="K155" s="9" t="inlineStr">
-        <is>
-          <t>US-253, US-011</t>
-        </is>
-      </c>
-      <c r="L155" s="9" t="inlineStr">
-        <is>
-          <t>INT-07, SDC-02</t>
-        </is>
-      </c>
-      <c r="M155" s="9" t="inlineStr">
-        <is>
-          <t>Linking world objects to simulation needs</t>
-        </is>
-      </c>
-      <c r="N155" s="9" t="inlineStr">
-        <is>
-          <t>Resolution, lighting and buildings (owner, 2026-10-01, D-42)</t>
-        </is>
-      </c>
-      <c r="O155" s="16" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -19282,6 +12666,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -19319,7 +12704,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Ages 2-10, Mythic Strands 2-10, Phase 2 space</t>
+          <t>Ages 2-10, Mythic Strands, Phase 2 space</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -19353,17 +12738,17 @@
     <row r="8" ht="25.5" customHeight="1" s="20">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Military, Ideology pillars</t>
+          <t>Military, Politics, Technology, Ideology pillars</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Four pillars (Trade, Religion, Politics, Technology) are enough to test 'many paths to dominance'; combat as a pillar is the most expensive system. Politics (D-40) and Technology (D-41) returned to the MVP on 2026-10-01.</t>
+          <t>Two pillars are enough to test 'many paths to dominance'; combat is the most expensive system.</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Next (Politics), Later (others)</t>
         </is>
       </c>
     </row>
@@ -19460,7 +12845,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Age 1 needs hit detection, ballistics, basic bodies and material properties only; the rest belongs to later Ages. Exception (D-42): fire spreading between building pieces is in the MVP.</t>
+          <t>Age 1 needs hit detection, ballistics, basic bodies and material properties only; the rest belongs to later Ages.</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -19500,6 +12885,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -19535,6 +12921,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
